--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -18792,6 +18792,11 @@
       <c r="J228" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>16#300</t>
+        </is>
+      </c>
       <c r="L228" s="0" t="inlineStr">
         <is>
           <t>16#300|80001#1</t>
@@ -21299,7 +21304,7 @@
       </c>
       <c r="K257" s="0" t="inlineStr">
         <is>
-          <t>16#60</t>
+          <t>16#1100</t>
         </is>
       </c>
       <c r="L257" s="0" t="inlineStr">
@@ -49284,12 +49289,12 @@
       </c>
       <c r="L572" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72005#40|72004#150|72001#300|6000124#1280</t>
+          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280</t>
         </is>
       </c>
       <c r="M572" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72005#40|72004#150|72001#300</t>
+          <t>16#1619|72005#40|72004#150|72001#300</t>
         </is>
       </c>
       <c r="Q572" s="0" t="n">
@@ -49373,12 +49378,12 @@
       </c>
       <c r="L573" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60403#2|60402#10|72001#300|6000124#1280</t>
+          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280</t>
         </is>
       </c>
       <c r="M573" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60403#2|60402#10|72001#300</t>
+          <t>16#1619|60403#2|60402#10|72001#300</t>
         </is>
       </c>
       <c r="Q573" s="0" t="n">
@@ -49462,12 +49467,12 @@
       </c>
       <c r="L574" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72005#60|72004#275|72001#450|6000124#1980</t>
+          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980</t>
         </is>
       </c>
       <c r="M574" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72005#60|72004#275|72001#450</t>
+          <t>16#2624|72005#60|72004#275|72001#450</t>
         </is>
       </c>
       <c r="Q574" s="0" t="n">
@@ -49551,12 +49556,12 @@
       </c>
       <c r="L575" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60403#4|60402#15|72001#450|6000124#1980</t>
+          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980</t>
         </is>
       </c>
       <c r="M575" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60403#4|60402#15|72001#450</t>
+          <t>16#2624|60403#4|60402#15|72001#450</t>
         </is>
       </c>
       <c r="Q575" s="0" t="n">
@@ -49640,12 +49645,12 @@
       </c>
       <c r="L576" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|72005#80|72004#400|6000124#3280</t>
+          <t>16#4592|60417#1|72005#80|72004#400|6000124#3280</t>
         </is>
       </c>
       <c r="M576" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|72005#80|72004#400</t>
+          <t>16#4592|60417#1|72005#80|72004#400</t>
         </is>
       </c>
       <c r="Q576" s="0" t="n">
@@ -49729,12 +49734,12 @@
       </c>
       <c r="L577" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|60403#6|60402#20|6000124#3280</t>
+          <t>16#4592|60417#1|60403#6|60402#20|6000124#3280</t>
         </is>
       </c>
       <c r="M577" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|60403#6|60402#20</t>
+          <t>16#4592|60417#1|60403#6|60402#20</t>
         </is>
       </c>
       <c r="Q577" s="0" t="n">
@@ -49818,12 +49823,12 @@
       </c>
       <c r="L578" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|4#10000|6000124#6480</t>
+          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M578" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|4#10000</t>
+          <t>16#9558|60403#18|60402#18|4#10000</t>
         </is>
       </c>
       <c r="Q578" s="0" t="n">
@@ -49907,12 +49912,12 @@
       </c>
       <c r="L579" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#10000|6000124#6480</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M579" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#10000</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000</t>
         </is>
       </c>
       <c r="Q579" s="0" t="n">
@@ -49996,12 +50001,12 @@
       </c>
       <c r="L580" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|4#10000|6000124#6480</t>
+          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M580" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|4#10000</t>
+          <t>16#9720|60403#18|60402#18|4#10000</t>
         </is>
       </c>
       <c r="Q580" s="0" t="n">
@@ -50085,12 +50090,12 @@
       </c>
       <c r="L581" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#20000|6000124#6480</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480</t>
         </is>
       </c>
       <c r="M581" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#20000</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000</t>
         </is>
       </c>
       <c r="Q581" s="0" t="n">
@@ -50174,12 +50179,12 @@
       </c>
       <c r="L582" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#30000|6000124#6480</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480</t>
         </is>
       </c>
       <c r="M582" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60403#18|60402#18|6000110#30000</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000</t>
         </is>
       </c>
       <c r="Q582" s="0" t="n">
@@ -50530,12 +50535,12 @@
       </c>
       <c r="L586" s="0" t="inlineStr">
         <is>
-          <t>16#2218|17012#100|17011#300|19#12|6000124#1980</t>
+          <t>16#2475|17012#100|17011#300|19#12|6000124#1980</t>
         </is>
       </c>
       <c r="M586" s="0" t="inlineStr">
         <is>
-          <t>16#2218|17012#100|17011#300|19#12</t>
+          <t>16#2475|17012#100|17011#300|19#12</t>
         </is>
       </c>
       <c r="Q586" s="0" t="n">
@@ -50797,12 +50802,12 @@
       </c>
       <c r="L589" s="0" t="inlineStr">
         <is>
-          <t>16#7452|6000097#100|6000098#200|6000095#130|6000124#6480</t>
+          <t>16#8748|6000097#100|6000098#200|6000095#130|6000124#6480</t>
         </is>
       </c>
       <c r="M589" s="0" t="inlineStr">
         <is>
-          <t>16#7452|6000097#100|6000098#200|6000095#130</t>
+          <t>16#8748|6000097#100|6000098#200|6000095#130</t>
         </is>
       </c>
       <c r="Q589" s="0" t="n">
@@ -51420,12 +51425,12 @@
       </c>
       <c r="L596" s="0" t="inlineStr">
         <is>
-          <t>16#1472|10443#200|6000104#40|14#8000000|6000124#1280</t>
+          <t>16#1555|10443#200|6000104#40|14#8000000|6000124#1280</t>
         </is>
       </c>
       <c r="M596" s="0" t="inlineStr">
         <is>
-          <t>16#1472|10443#200|6000104#40|14#8000000</t>
+          <t>16#1555|10443#200|6000104#40|14#8000000</t>
         </is>
       </c>
       <c r="Q596" s="0" t="n">
@@ -51509,12 +51514,12 @@
       </c>
       <c r="L597" s="0" t="inlineStr">
         <is>
-          <t>16#3674|10443#500|6000104#100|14#50000000|6000124#3280</t>
+          <t>16#4264|10443#500|6000104#100|14#50000000|6000124#3280</t>
         </is>
       </c>
       <c r="M597" s="0" t="inlineStr">
         <is>
-          <t>16#3674|10443#500|6000104#100|14#50000000</t>
+          <t>16#4264|10443#500|6000104#100|14#50000000</t>
         </is>
       </c>
       <c r="Q597" s="0" t="n">
@@ -52666,12 +52671,12 @@
       </c>
       <c r="L610" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
+          <t>16#1176|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
         </is>
       </c>
       <c r="M610" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
+          <t>16#1176|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
         </is>
       </c>
       <c r="Q610" s="0" t="n">
@@ -52755,12 +52760,12 @@
       </c>
       <c r="L611" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
+          <t>16#1555|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M611" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
+          <t>16#1555|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
         </is>
       </c>
       <c r="Q611" s="0" t="n">
@@ -52844,12 +52849,12 @@
       </c>
       <c r="L612" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
+          <t>16#2475|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
         </is>
       </c>
       <c r="M612" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
+          <t>16#2475|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
         </is>
       </c>
       <c r="Q612" s="0" t="n">
@@ -52933,12 +52938,12 @@
       </c>
       <c r="L613" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
+          <t>16#4264|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
         </is>
       </c>
       <c r="M613" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
+          <t>16#4264|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
         </is>
       </c>
       <c r="Q613" s="0" t="n">
@@ -53111,12 +53116,12 @@
       </c>
       <c r="L615" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|20#10|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000|6000124#3280</t>
+          <t>16#4264|81148#100|20#10|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000|6000124#3280</t>
         </is>
       </c>
       <c r="M615" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|20#10|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000</t>
+          <t>16#4264|81148#100|20#10|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000</t>
         </is>
       </c>
       <c r="Q615" s="0" t="n">
@@ -54891,12 +54896,12 @@
       </c>
       <c r="L635" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#2000|6000110#1500|72001#200|6000124#980</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200|6000124#980</t>
         </is>
       </c>
       <c r="M635" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#2000|6000110#1500|72001#200</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200</t>
         </is>
       </c>
       <c r="Q635" s="0" t="n">
@@ -54980,12 +54985,12 @@
       </c>
       <c r="L636" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#2500|6000110#2000|72001#250|6000124#1280</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280</t>
         </is>
       </c>
       <c r="M636" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#2500|6000110#2000|72001#250</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250</t>
         </is>
       </c>
       <c r="Q636" s="0" t="n">
@@ -55069,12 +55074,12 @@
       </c>
       <c r="L637" s="0" t="inlineStr">
         <is>
-          <t>16#1472|81004#1|4#5000|3#5000000|6000124#1280</t>
+          <t>16#1555|81004#1|4#5000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M637" s="0" t="inlineStr">
         <is>
-          <t>16#1472|81004#1|4#5000|3#5000000</t>
+          <t>16#1555|81004#1|4#5000|3#5000000</t>
         </is>
       </c>
       <c r="Q637" s="0" t="n">
@@ -55158,12 +55163,12 @@
       </c>
       <c r="L638" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|20#3|19#30|6000124#1980</t>
+          <t>16#2475|60415#1|20#3|19#30|6000124#1980</t>
         </is>
       </c>
       <c r="M638" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|20#3|19#30</t>
+          <t>16#2475|60415#1|20#3|19#30</t>
         </is>
       </c>
       <c r="Q638" s="0" t="n">
@@ -55247,12 +55252,12 @@
       </c>
       <c r="L639" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|6000110#5000|6000124#1980</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980</t>
         </is>
       </c>
       <c r="M639" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|6000110#5000</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000</t>
         </is>
       </c>
       <c r="Q639" s="0" t="n">
@@ -55336,12 +55341,12 @@
       </c>
       <c r="L640" s="0" t="inlineStr">
         <is>
-          <t>16#1472|17012#30|17011#120|17009#60|6000124#1280</t>
+          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280</t>
         </is>
       </c>
       <c r="M640" s="0" t="inlineStr">
         <is>
-          <t>16#1472|17012#30|17011#120|17009#60</t>
+          <t>16#1555|17012#30|17011#120|17009#60</t>
         </is>
       </c>
       <c r="Q640" s="0" t="n">
@@ -55425,12 +55430,12 @@
       </c>
       <c r="L641" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|6000110#5000|6000124#1980</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980</t>
         </is>
       </c>
       <c r="M641" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|6000110#5000</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000</t>
         </is>
       </c>
       <c r="Q641" s="0" t="n">
@@ -55514,12 +55519,12 @@
       </c>
       <c r="L642" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|6000089#1|6000110#5000|6000124#1980</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980</t>
         </is>
       </c>
       <c r="M642" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|6000089#1|6000110#5000</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000</t>
         </is>
       </c>
       <c r="Q642" s="0" t="n">
@@ -55603,12 +55608,12 @@
       </c>
       <c r="L643" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000097#15|6000098#60|6000092#120|6000124#1280</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280</t>
         </is>
       </c>
       <c r="M643" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000097#15|6000098#60|6000092#120</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120</t>
         </is>
       </c>
       <c r="Q643" s="0" t="n">
@@ -55692,12 +55697,12 @@
       </c>
       <c r="L644" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#10|19#50|61#5|6000124#3280</t>
+          <t>16#4264|20#10|19#50|61#5|6000124#3280</t>
         </is>
       </c>
       <c r="M644" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#10|19#50|61#5</t>
+          <t>16#4264|20#10|19#50|61#5</t>
         </is>
       </c>
       <c r="Q644" s="0" t="n">
@@ -55781,12 +55786,12 @@
       </c>
       <c r="L645" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99002#1|10442#25|10441#150|6000124#3280</t>
+          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280</t>
         </is>
       </c>
       <c r="M645" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99002#1|10442#25|10441#150</t>
+          <t>16#4264|99002#1|10442#25|10441#150</t>
         </is>
       </c>
       <c r="Q645" s="0" t="n">
@@ -55870,12 +55875,12 @@
       </c>
       <c r="L646" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60411#20|6000124#3280</t>
+          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280</t>
         </is>
       </c>
       <c r="M646" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60411#20</t>
+          <t>16#4264|81148#100|60412#10|60411#20</t>
         </is>
       </c>
       <c r="Q646" s="0" t="n">
@@ -55959,12 +55964,12 @@
       </c>
       <c r="L647" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#15|6000110#5000|14#30000000|6000124#3280</t>
+          <t>16#4264|20#15|6000110#5000|14#30000000|6000124#3280</t>
         </is>
       </c>
       <c r="M647" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#15|6000110#5000|14#30000000</t>
+          <t>16#4264|20#15|6000110#5000|14#30000000</t>
         </is>
       </c>
       <c r="Q647" s="0" t="n">
@@ -56048,12 +56053,12 @@
       </c>
       <c r="L648" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#2|60411#10|14#5000000|6000124#980</t>
+          <t>16#1176|60412#2|60411#10|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M648" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#2|60411#10|14#5000000</t>
+          <t>16#1176|60412#2|60411#10|14#5000000</t>
         </is>
       </c>
       <c r="Q648" s="0" t="n">
@@ -56137,12 +56142,12 @@
       </c>
       <c r="L649" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60412#3|60411#15|14#8000000|6000124#1280</t>
+          <t>16#1555|60412#3|60411#15|14#8000000|6000124#1280</t>
         </is>
       </c>
       <c r="M649" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60412#3|60411#15|14#8000000</t>
+          <t>16#1555|60412#3|60411#15|14#8000000</t>
         </is>
       </c>
       <c r="Q649" s="0" t="n">
@@ -56226,12 +56231,12 @@
       </c>
       <c r="L650" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60412#5|60411#20|14#15000000|6000124#1980</t>
+          <t>16#2475|60412#5|60411#20|14#15000000|6000124#1980</t>
         </is>
       </c>
       <c r="M650" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60412#5|60411#20|14#15000000</t>
+          <t>16#2475|60412#5|60411#20|14#15000000</t>
         </is>
       </c>
       <c r="Q650" s="0" t="n">
@@ -56315,12 +56320,12 @@
       </c>
       <c r="L651" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99005#1|3#4000000|4#2000|6000124#1280</t>
+          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M651" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99005#1|3#4000000|4#2000</t>
+          <t>16#1555|99005#1|3#4000000|4#2000</t>
         </is>
       </c>
       <c r="Q651" s="0" t="n">
@@ -56404,12 +56409,12 @@
       </c>
       <c r="L652" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99005#1|3#10000000|4#5000|6000124#3280</t>
+          <t>16#4264|99005#1|3#10000000|4#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M652" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99005#1|3#10000000|4#5000</t>
+          <t>16#4264|99005#1|3#10000000|4#5000</t>
         </is>
       </c>
       <c r="Q652" s="0" t="n">
@@ -56493,12 +56498,12 @@
       </c>
       <c r="L653" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99005#1|3#15000000|4#10000|6000124#6480</t>
+          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M653" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99005#1|3#15000000|4#10000</t>
+          <t>16#8748|99005#1|3#15000000|4#10000</t>
         </is>
       </c>
       <c r="Q653" s="0" t="n">
@@ -56671,12 +56676,12 @@
       </c>
       <c r="L655" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99006#1|3#4000000|4#2000|6000124#1280</t>
+          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M655" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99006#1|3#4000000|4#2000</t>
+          <t>16#1555|99006#1|3#4000000|4#2000</t>
         </is>
       </c>
       <c r="Q655" s="0" t="n">
@@ -56760,12 +56765,12 @@
       </c>
       <c r="L656" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99006#1|3#10000000|4#5000|6000124#3280</t>
+          <t>16#4264|99006#1|3#10000000|4#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M656" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99006#1|3#10000000|4#5000</t>
+          <t>16#4264|99006#1|3#10000000|4#5000</t>
         </is>
       </c>
       <c r="Q656" s="0" t="n">
@@ -56849,12 +56854,12 @@
       </c>
       <c r="L657" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99006#1|3#15000000|4#10000|6000124#6480</t>
+          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M657" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99006#1|3#15000000|4#10000</t>
+          <t>16#8748|99006#1|3#15000000|4#10000</t>
         </is>
       </c>
       <c r="Q657" s="0" t="n">
@@ -57027,12 +57032,12 @@
       </c>
       <c r="L659" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99007#1|3#4000000|4#2000|6000124#1280</t>
+          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M659" s="0" t="inlineStr">
         <is>
-          <t>16#1472|99007#1|3#4000000|4#2000</t>
+          <t>16#1555|99007#1|3#4000000|4#2000</t>
         </is>
       </c>
       <c r="Q659" s="0" t="n">
@@ -57116,12 +57121,12 @@
       </c>
       <c r="L660" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99007#1|3#10000000|4#5000|6000124#3280</t>
+          <t>16#4264|99007#1|3#10000000|4#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M660" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99007#1|3#10000000|4#5000</t>
+          <t>16#4264|99007#1|3#10000000|4#5000</t>
         </is>
       </c>
       <c r="Q660" s="0" t="n">
@@ -57205,12 +57210,12 @@
       </c>
       <c r="L661" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99007#1|3#15000000|4#10000|6000124#6480</t>
+          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M661" s="0" t="inlineStr">
         <is>
-          <t>16#7452|99007#1|3#15000000|4#10000</t>
+          <t>16#8748|99007#1|3#15000000|4#10000</t>
         </is>
       </c>
       <c r="Q661" s="0" t="n">
@@ -57294,12 +57299,12 @@
       </c>
       <c r="L662" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#3000|6000088#1|6000110#3000|6000124#1280</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280</t>
         </is>
       </c>
       <c r="M662" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#3000|6000088#1|6000110#3000</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000</t>
         </is>
       </c>
       <c r="Q662" s="0" t="n">
@@ -57383,12 +57388,12 @@
       </c>
       <c r="L663" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#3000|6000110#2000|72001#200|6000124#1980</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980</t>
         </is>
       </c>
       <c r="M663" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#3000|6000110#2000|72001#200</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200</t>
         </is>
       </c>
       <c r="Q663" s="0" t="n">
@@ -57472,12 +57477,12 @@
       </c>
       <c r="L664" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#5000|6000110#3000|72001#250|6000124#3280</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250|6000124#3280</t>
         </is>
       </c>
       <c r="M664" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#5000|6000110#3000|72001#250</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250</t>
         </is>
       </c>
       <c r="Q664" s="0" t="n">
@@ -57561,12 +57566,12 @@
       </c>
       <c r="L665" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#3000|99000#1|6000110#3000|6000124#1280</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280</t>
         </is>
       </c>
       <c r="M665" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#3000|99000#1|6000110#3000</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000</t>
         </is>
       </c>
       <c r="Q665" s="0" t="n">
@@ -57650,12 +57655,12 @@
       </c>
       <c r="L666" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#4000|99001#1|6000110#4000|6000124#1980</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980</t>
         </is>
       </c>
       <c r="M666" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#4000|99001#1|6000110#4000</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000</t>
         </is>
       </c>
       <c r="Q666" s="0" t="n">
@@ -57739,12 +57744,12 @@
       </c>
       <c r="L667" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#5000|99002#1|6000110#5000|6000124#3280</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M667" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#5000|99002#1|6000110#5000</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000</t>
         </is>
       </c>
       <c r="Q667" s="0" t="n">
@@ -57828,12 +57833,12 @@
       </c>
       <c r="L668" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#2000|60411#8|60412#2|6000124#980</t>
+          <t>16#1176|4#2000|60411#8|60412#2|6000124#980</t>
         </is>
       </c>
       <c r="M668" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#2000|60411#8|60412#2</t>
+          <t>16#1176|4#2000|60411#8|60412#2</t>
         </is>
       </c>
       <c r="Q668" s="0" t="n">
@@ -57917,12 +57922,12 @@
       </c>
       <c r="L669" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#2500|60411#10|60412#3|6000124#1280</t>
+          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280</t>
         </is>
       </c>
       <c r="M669" s="0" t="inlineStr">
         <is>
-          <t>16#1472|4#2500|60411#10|60412#3</t>
+          <t>16#1555|4#2500|60411#10|60412#3</t>
         </is>
       </c>
       <c r="Q669" s="0" t="n">
@@ -58006,12 +58011,12 @@
       </c>
       <c r="L670" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#3000|60411#12|6000088#1|6000124#1980</t>
+          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980</t>
         </is>
       </c>
       <c r="M670" s="0" t="inlineStr">
         <is>
-          <t>16#2218|4#3000|60411#12|6000088#1</t>
+          <t>16#2475|4#3000|60411#12|6000088#1</t>
         </is>
       </c>
       <c r="Q670" s="0" t="n">
@@ -58095,12 +58100,12 @@
       </c>
       <c r="L671" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#4000|60411#15|6000088#2|6000124#3280</t>
+          <t>16#4264|4#4000|60411#15|6000088#2|6000124#3280</t>
         </is>
       </c>
       <c r="M671" s="0" t="inlineStr">
         <is>
-          <t>16#3674|4#4000|60411#15|6000088#2</t>
+          <t>16#4264|4#4000|60411#15|6000088#2</t>
         </is>
       </c>
       <c r="Q671" s="0" t="n">
@@ -58184,12 +58189,12 @@
       </c>
       <c r="L672" s="0" t="inlineStr">
         <is>
-          <t>16#5612|4#4500|60411#20|6000089#1|6000124#4880</t>
+          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880</t>
         </is>
       </c>
       <c r="M672" s="0" t="inlineStr">
         <is>
-          <t>16#5612|4#4500|60411#20|6000089#1</t>
+          <t>16#6466|4#4500|60411#20|6000089#1</t>
         </is>
       </c>
       <c r="Q672" s="0" t="n">
@@ -58273,12 +58278,12 @@
       </c>
       <c r="L673" s="0" t="inlineStr">
         <is>
-          <t>16#7452|4#5000|60412#3|6000090#1|6000124#6480</t>
+          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480</t>
         </is>
       </c>
       <c r="M673" s="0" t="inlineStr">
         <is>
-          <t>16#7452|4#5000|60412#3|6000090#1</t>
+          <t>16#8748|4#5000|60412#3|6000090#1</t>
         </is>
       </c>
       <c r="Q673" s="0" t="n">
@@ -58362,12 +58367,12 @@
       </c>
       <c r="L674" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72001#200|60411#10|60412#3|6000124#1280</t>
+          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280</t>
         </is>
       </c>
       <c r="M674" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72001#200|60411#10|60412#3</t>
+          <t>16#1555|72001#200|60411#10|60412#3</t>
         </is>
       </c>
       <c r="Q674" s="0" t="n">
@@ -58451,12 +58456,12 @@
       </c>
       <c r="L675" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72001#300|60411#15|60412#4|6000124#1980</t>
+          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980</t>
         </is>
       </c>
       <c r="M675" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72001#300|60411#15|60412#4</t>
+          <t>16#2475|72001#300|60411#15|60412#4</t>
         </is>
       </c>
       <c r="Q675" s="0" t="n">
@@ -58540,12 +58545,12 @@
       </c>
       <c r="L676" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72001#500|60411#25|60412#6|6000124#3280</t>
+          <t>16#4264|72001#500|60411#25|60412#6|6000124#3280</t>
         </is>
       </c>
       <c r="M676" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72001#500|60411#25|60412#6</t>
+          <t>16#4264|72001#500|60411#25|60412#6</t>
         </is>
       </c>
       <c r="Q676" s="0" t="n">
@@ -58629,12 +58634,12 @@
       </c>
       <c r="L677" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72001#450|60411#15|60412#4|6000124#3280</t>
+          <t>16#4264|72001#450|60411#15|60412#4|6000124#3280</t>
         </is>
       </c>
       <c r="M677" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72001#450|60411#15|60412#4</t>
+          <t>16#4264|72001#450|60411#15|60412#4</t>
         </is>
       </c>
       <c r="Q677" s="0" t="n">
@@ -58718,12 +58723,12 @@
       </c>
       <c r="L678" s="0" t="inlineStr">
         <is>
-          <t>16#5612|72001#500|60411#20|60412#5|6000124#4880</t>
+          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880</t>
         </is>
       </c>
       <c r="M678" s="0" t="inlineStr">
         <is>
-          <t>16#5612|72001#500|60411#20|60412#5</t>
+          <t>16#6466|72001#500|60411#20|60412#5</t>
         </is>
       </c>
       <c r="Q678" s="0" t="n">
@@ -58807,12 +58812,12 @@
       </c>
       <c r="L679" s="0" t="inlineStr">
         <is>
-          <t>16#7452|72001#550|60411#25|60412#5|6000124#6480</t>
+          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480</t>
         </is>
       </c>
       <c r="M679" s="0" t="inlineStr">
         <is>
-          <t>16#7452|72001#550|60411#25|60412#5</t>
+          <t>16#8748|72001#550|60411#25|60412#5</t>
         </is>
       </c>
       <c r="Q679" s="0" t="n">
@@ -58896,12 +58901,12 @@
       </c>
       <c r="L680" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|60411#8|60412#2|6000124#1280</t>
+          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280</t>
         </is>
       </c>
       <c r="M680" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|60411#8|60412#2</t>
+          <t>16#1555|60417#1|60411#8|60412#2</t>
         </is>
       </c>
       <c r="Q680" s="0" t="n">
@@ -58985,12 +58990,12 @@
       </c>
       <c r="L681" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60417#1|60411#15|60412#4|6000124#1980</t>
+          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980</t>
         </is>
       </c>
       <c r="M681" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60417#1|60411#15|60412#4</t>
+          <t>16#2475|60417#1|60411#15|60412#4</t>
         </is>
       </c>
       <c r="Q681" s="0" t="n">
@@ -59074,12 +59079,12 @@
       </c>
       <c r="L682" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|60411#25|60412#6|6000124#3280</t>
+          <t>16#4264|60417#1|60411#25|60412#6|6000124#3280</t>
         </is>
       </c>
       <c r="M682" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60417#1|60411#25|60412#6</t>
+          <t>16#4264|60417#1|60411#25|60412#6</t>
         </is>
       </c>
       <c r="Q682" s="0" t="n">
@@ -59163,12 +59168,12 @@
       </c>
       <c r="L683" s="0" t="inlineStr">
         <is>
-          <t>16#1472|17012#30|17011#120|17009#60|6000124#1280</t>
+          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280</t>
         </is>
       </c>
       <c r="M683" s="0" t="inlineStr">
         <is>
-          <t>16#1472|17012#30|17011#120|17009#60</t>
+          <t>16#1555|17012#30|17011#120|17009#60</t>
         </is>
       </c>
       <c r="Q683" s="0" t="n">
@@ -59252,12 +59257,12 @@
       </c>
       <c r="L684" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|3#8000000|6000124#1980</t>
+          <t>16#2475|60415#1|6000089#1|3#8000000|6000124#1980</t>
         </is>
       </c>
       <c r="M684" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60415#1|6000089#1|3#8000000</t>
+          <t>16#2475|60415#1|6000089#1|3#8000000</t>
         </is>
       </c>
       <c r="Q684" s="0" t="n">
@@ -59341,12 +59346,12 @@
       </c>
       <c r="L685" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000097#15|6000098#60|6000092#120|6000124#1280</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280</t>
         </is>
       </c>
       <c r="M685" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000097#15|6000098#60|6000092#120</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120</t>
         </is>
       </c>
       <c r="Q685" s="0" t="n">
@@ -59430,12 +59435,12 @@
       </c>
       <c r="L686" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|6000089#1|6000110#5000|6000124#1980</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980</t>
         </is>
       </c>
       <c r="M686" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|6000089#1|6000110#5000</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000</t>
         </is>
       </c>
       <c r="Q686" s="0" t="n">
@@ -59519,12 +59524,12 @@
       </c>
       <c r="L687" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99002#1|10442#25|10441#150|6000124#3280</t>
+          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280</t>
         </is>
       </c>
       <c r="M687" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99002#1|10442#25|10441#150</t>
+          <t>16#4264|99002#1|10442#25|10441#150</t>
         </is>
       </c>
       <c r="Q687" s="0" t="n">
@@ -59608,12 +59613,12 @@
       </c>
       <c r="L688" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60411#20|6000124#3280</t>
+          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280</t>
         </is>
       </c>
       <c r="M688" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60411#20</t>
+          <t>16#4264|81148#100|60412#10|60411#20</t>
         </is>
       </c>
       <c r="Q688" s="0" t="n">
@@ -59697,12 +59702,12 @@
       </c>
       <c r="L689" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#12|6000110#3000|14#3000000|6000124#3280</t>
+          <t>16#4264|20#12|6000110#3000|14#3000000|6000124#3280</t>
         </is>
       </c>
       <c r="M689" s="0" t="inlineStr">
         <is>
-          <t>16#3674|20#12|6000110#3000|14#3000000</t>
+          <t>16#4264|20#12|6000110#3000|14#3000000</t>
         </is>
       </c>
       <c r="Q689" s="0" t="n">
@@ -59786,12 +59791,12 @@
       </c>
       <c r="L690" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60406#1|10423#10|10425#600|6000124#6480</t>
+          <t>16#8748|60406#1|10423#10|10425#600|6000124#6480</t>
         </is>
       </c>
       <c r="M690" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60406#1|10423#10|10425#600</t>
+          <t>16#8748|60406#1|10423#10|10425#600</t>
         </is>
       </c>
       <c r="Q690" s="0" t="n">
@@ -60043,12 +60048,12 @@
       </c>
       <c r="L693" s="0" t="inlineStr">
         <is>
-          <t>16#1127|81148#50|3#1000000|14#2200000|6000124#980</t>
+          <t>16#1176|81148#50|3#1000000|14#2200000|6000124#980</t>
         </is>
       </c>
       <c r="M693" s="0" t="inlineStr">
         <is>
-          <t>16#1127|81148#50|3#1000000|14#2200000</t>
+          <t>16#1176|81148#50|3#1000000|14#2200000</t>
         </is>
       </c>
       <c r="Q693" s="0" t="n">
@@ -60127,12 +60132,12 @@
       </c>
       <c r="L694" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#4|14#4400000|6000124#980</t>
+          <t>16#1176|20#4|14#4400000|6000124#980</t>
         </is>
       </c>
       <c r="M694" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#4|14#4400000</t>
+          <t>16#1176|20#4|14#4400000</t>
         </is>
       </c>
       <c r="Q694" s="0" t="n">
@@ -60211,12 +60216,12 @@
       </c>
       <c r="L695" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60415#1|19#10|3#1000000|6000124#1280</t>
+          <t>16#1555|60415#1|19#10|3#1000000|6000124#1280</t>
         </is>
       </c>
       <c r="M695" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60415#1|19#10|3#1000000</t>
+          <t>16#1555|60415#1|19#10|3#1000000</t>
         </is>
       </c>
       <c r="Q695" s="0" t="n">
@@ -60295,12 +60300,12 @@
       </c>
       <c r="L696" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#5|6000110#2000|6000124#1280</t>
+          <t>16#1555|20#5|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M696" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#5|6000110#2000</t>
+          <t>16#1555|20#5|6000110#2000</t>
         </is>
       </c>
       <c r="Q696" s="0" t="n">
@@ -60379,12 +60384,12 @@
       </c>
       <c r="L697" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|3#2000000|14#4000000|6000124#1280</t>
+          <t>16#1555|19#30|3#2000000|14#4000000|6000124#1280</t>
         </is>
       </c>
       <c r="M697" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|3#2000000|14#4000000</t>
+          <t>16#1555|19#30|3#2000000|14#4000000</t>
         </is>
       </c>
       <c r="Q697" s="0" t="n">
@@ -60463,12 +60468,12 @@
       </c>
       <c r="L698" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|19#20|3#2000000|6000124#1980</t>
+          <t>16#2475|60416#1|19#20|3#2000000|6000124#1980</t>
         </is>
       </c>
       <c r="M698" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60416#1|19#20|3#2000000</t>
+          <t>16#2475|60416#1|19#20|3#2000000</t>
         </is>
       </c>
       <c r="Q698" s="0" t="n">
@@ -60547,12 +60552,12 @@
       </c>
       <c r="L699" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#8|6000110#3000|6000124#1980</t>
+          <t>16#2475|20#8|6000110#3000|6000124#1980</t>
         </is>
       </c>
       <c r="M699" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#8|6000110#3000</t>
+          <t>16#2475|20#8|6000110#3000</t>
         </is>
       </c>
       <c r="Q699" s="0" t="n">
@@ -60631,12 +60636,12 @@
       </c>
       <c r="L700" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60412#2|6000124#3280</t>
+          <t>16#4264|81148#100|60412#10|60412#2|6000124#3280</t>
         </is>
       </c>
       <c r="M700" s="0" t="inlineStr">
         <is>
-          <t>16#3674|81148#100|60412#10|60412#2</t>
+          <t>16#4264|81148#100|60412#10|60412#2</t>
         </is>
       </c>
       <c r="Q700" s="0" t="n">
@@ -60982,12 +60987,12 @@
       </c>
       <c r="L704" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#4|60410#8|14#5000000|6000124#980</t>
+          <t>16#1176|60412#4|60410#8|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M704" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#4|60410#8|14#5000000</t>
+          <t>16#1176|60412#4|60410#8|14#5000000</t>
         </is>
       </c>
       <c r="Q704" s="0" t="n">
@@ -61071,12 +61076,12 @@
       </c>
       <c r="L705" s="0" t="inlineStr">
         <is>
-          <t>16#3674|3#15000000|14#8000000|60411#5|6000124#3280</t>
+          <t>16#4264|3#15000000|14#8000000|60411#5|6000124#3280</t>
         </is>
       </c>
       <c r="M705" s="0" t="inlineStr">
         <is>
-          <t>16#3674|3#15000000|14#8000000|60411#5</t>
+          <t>16#4264|3#15000000|14#8000000|60411#5</t>
         </is>
       </c>
       <c r="Q705" s="0" t="n">
@@ -61160,12 +61165,12 @@
       </c>
       <c r="L706" s="0" t="inlineStr">
         <is>
-          <t>16#7452|3#20000000|14#10000000|60412#4|6000124#6480</t>
+          <t>16#8748|3#20000000|14#10000000|60412#4|6000124#6480</t>
         </is>
       </c>
       <c r="M706" s="0" t="inlineStr">
         <is>
-          <t>16#7452|3#20000000|14#10000000|60412#4</t>
+          <t>16#8748|3#20000000|14#10000000|60412#4</t>
         </is>
       </c>
       <c r="Q706" s="0" t="n">
@@ -61516,12 +61521,12 @@
       </c>
       <c r="L710" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#4|60418#8|14#5000000|6000124#980</t>
+          <t>16#1176|60412#4|60418#8|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M710" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60412#4|60418#8|14#5000000</t>
+          <t>16#1176|60412#4|60418#8|14#5000000</t>
         </is>
       </c>
       <c r="Q710" s="0" t="n">
@@ -61605,12 +61610,12 @@
       </c>
       <c r="L711" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60412#6|60418#12|14#8000000|6000124#1280</t>
+          <t>16#1555|60412#6|60418#12|14#8000000|6000124#1280</t>
         </is>
       </c>
       <c r="M711" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60412#6|60418#12|14#8000000</t>
+          <t>16#1555|60412#6|60418#12|14#8000000</t>
         </is>
       </c>
       <c r="Q711" s="0" t="n">
@@ -61694,12 +61699,12 @@
       </c>
       <c r="L712" s="0" t="inlineStr">
         <is>
-          <t>16#7452|3#20000000|6000110#2000|99001#1|6000124#6480</t>
+          <t>16#8748|3#20000000|6000110#2000|99001#1|6000124#6480</t>
         </is>
       </c>
       <c r="M712" s="0" t="inlineStr">
         <is>
-          <t>16#7452|3#20000000|6000110#2000|99001#1</t>
+          <t>16#8748|3#20000000|6000110#2000|99001#1</t>
         </is>
       </c>
       <c r="Q712" s="0" t="n">
@@ -61961,12 +61966,12 @@
       </c>
       <c r="L715" s="0" t="inlineStr">
         <is>
-          <t>16#1127|72003#30|4#1500|3#3000000|6000124#980</t>
+          <t>16#1176|72003#30|4#1500|3#3000000|6000124#980</t>
         </is>
       </c>
       <c r="M715" s="0" t="inlineStr">
         <is>
-          <t>16#1127|72003#30|4#1500|3#3000000</t>
+          <t>16#1176|72003#30|4#1500|3#3000000</t>
         </is>
       </c>
       <c r="Q715" s="0" t="n">
@@ -62050,12 +62055,12 @@
       </c>
       <c r="L716" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72003#40|4#2000|3#5000000|6000124#1280</t>
+          <t>16#1555|72003#40|4#2000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M716" s="0" t="inlineStr">
         <is>
-          <t>16#1472|72003#40|4#2000|3#5000000</t>
+          <t>16#1555|72003#40|4#2000|3#5000000</t>
         </is>
       </c>
       <c r="Q716" s="0" t="n">
@@ -62139,12 +62144,12 @@
       </c>
       <c r="L717" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72003#60|4#3000|3#8000000|6000124#1980</t>
+          <t>16#2475|72003#60|4#3000|3#8000000|6000124#1980</t>
         </is>
       </c>
       <c r="M717" s="0" t="inlineStr">
         <is>
-          <t>16#2218|72003#60|4#3000|3#8000000</t>
+          <t>16#2475|72003#60|4#3000|3#8000000</t>
         </is>
       </c>
       <c r="Q717" s="0" t="n">
@@ -62228,12 +62233,12 @@
       </c>
       <c r="L718" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72003#100|4#4000|3#15000000|6000124#3280</t>
+          <t>16#4264|72003#100|4#4000|3#15000000|6000124#3280</t>
         </is>
       </c>
       <c r="M718" s="0" t="inlineStr">
         <is>
-          <t>16#3674|72003#100|4#4000|3#15000000</t>
+          <t>16#4264|72003#100|4#4000|3#15000000</t>
         </is>
       </c>
       <c r="Q718" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -18826,7 +18826,10 @@
         </is>
       </c>
       <c r="R228" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S228" t="n">
+        <v>1</v>
       </c>
       <c r="T228" s="0" t="n">
         <v>1</v>
@@ -18846,13 +18849,16 @@
         <v>1</v>
       </c>
       <c r="Y228" s="0" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z228" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AA228" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>30</v>
       </c>
       <c r="AF228" s="0" t="inlineStr">
         <is>
@@ -18924,7 +18930,10 @@
         </is>
       </c>
       <c r="R229" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S229" t="n">
+        <v>1</v>
       </c>
       <c r="T229" s="0" t="n">
         <v>1</v>
@@ -18937,6 +18946,12 @@
       </c>
       <c r="X229" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>30</v>
       </c>
       <c r="AF229" s="0" t="inlineStr">
         <is>
@@ -19008,7 +19023,10 @@
         </is>
       </c>
       <c r="R230" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S230" t="n">
+        <v>1</v>
       </c>
       <c r="T230" s="0" t="n">
         <v>1</v>
@@ -19018,6 +19036,12 @@
       </c>
       <c r="X230" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>30</v>
       </c>
       <c r="AF230" s="0" t="inlineStr">
         <is>
@@ -49200,12 +49224,12 @@
       </c>
       <c r="L571" s="0" t="inlineStr">
         <is>
-          <t>16#816|4#1200|6000110#1500|72001#120|6000124#680|19#11</t>
+          <t>16#816|4#1200|6000110#1500|72001#120|6000124#680|19#12</t>
         </is>
       </c>
       <c r="M571" s="0" t="inlineStr">
         <is>
-          <t>16#816|4#1200|6000110#1500|72001#120|19#11</t>
+          <t>16#816|4#1200|6000110#1500|72001#120|19#12</t>
         </is>
       </c>
       <c r="Q571" s="0" t="n">
@@ -49289,12 +49313,12 @@
       </c>
       <c r="L572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280|19#23</t>
+          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280|19#26</t>
         </is>
       </c>
       <c r="M572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|19#23</t>
+          <t>16#1619|72005#40|72004#150|72001#300|19#26</t>
         </is>
       </c>
       <c r="Q572" s="0" t="n">
@@ -49378,12 +49402,12 @@
       </c>
       <c r="L573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280|19#23</t>
+          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280|19#26</t>
         </is>
       </c>
       <c r="M573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|19#23</t>
+          <t>16#1619|60403#2|60402#10|72001#300|19#26</t>
         </is>
       </c>
       <c r="Q573" s="0" t="n">
@@ -49467,12 +49491,12 @@
       </c>
       <c r="L574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980|19#37</t>
+          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980|19#42</t>
         </is>
       </c>
       <c r="M574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|19#37</t>
+          <t>16#2624|72005#60|72004#275|72001#450|19#42</t>
         </is>
       </c>
       <c r="Q574" s="0" t="n">
@@ -49556,12 +49580,12 @@
       </c>
       <c r="L575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980|19#37</t>
+          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980|19#42</t>
         </is>
       </c>
       <c r="M575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|19#37</t>
+          <t>16#2624|60403#4|60402#15|72001#450|19#42</t>
         </is>
       </c>
       <c r="Q575" s="0" t="n">
@@ -49645,12 +49669,12 @@
       </c>
       <c r="L576" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|72005#80|72004#400|6000124#3280|19#66</t>
+          <t>16#4592|60417#1|72005#80|72004#400|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M576" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|72005#80|72004#400|19#66</t>
+          <t>16#4592|60417#1|72005#80|72004#400|19#75</t>
         </is>
       </c>
       <c r="Q576" s="0" t="n">
@@ -49734,12 +49758,12 @@
       </c>
       <c r="L577" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|60403#6|60402#20|6000124#3280|19#66</t>
+          <t>16#4592|60417#1|60403#6|60402#20|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M577" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|60403#6|60402#20|19#66</t>
+          <t>16#4592|60417#1|60403#6|60402#20|19#75</t>
         </is>
       </c>
       <c r="Q577" s="0" t="n">
@@ -49823,12 +49847,12 @@
       </c>
       <c r="L578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480|19#145</t>
+          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480|19#168</t>
         </is>
       </c>
       <c r="M578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|19#145</t>
+          <t>16#9558|60403#18|60402#18|4#10000|19#168</t>
         </is>
       </c>
       <c r="Q578" s="0" t="n">
@@ -49912,12 +49936,12 @@
       </c>
       <c r="L579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480|19#145</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480|19#168</t>
         </is>
       </c>
       <c r="M579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|19#145</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000|19#168</t>
         </is>
       </c>
       <c r="Q579" s="0" t="n">
@@ -50001,12 +50025,12 @@
       </c>
       <c r="L580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480|19#144</t>
+          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480|19#171</t>
         </is>
       </c>
       <c r="M580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|19#144</t>
+          <t>16#9720|60403#18|60402#18|4#10000|19#171</t>
         </is>
       </c>
       <c r="Q580" s="0" t="n">
@@ -50090,12 +50114,12 @@
       </c>
       <c r="L581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480|19#144</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480|19#175</t>
         </is>
       </c>
       <c r="M581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|19#144</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000|19#175</t>
         </is>
       </c>
       <c r="Q581" s="0" t="n">
@@ -50179,12 +50203,12 @@
       </c>
       <c r="L582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480|19#143</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480|19#178</t>
         </is>
       </c>
       <c r="M582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|19#143</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000|19#178</t>
         </is>
       </c>
       <c r="Q582" s="0" t="n">
@@ -54896,12 +54920,12 @@
       </c>
       <c r="L635" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|6000110#1500|72001#200|6000124#980|19#17</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M635" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|6000110#1500|72001#200|19#17</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200|19#18</t>
         </is>
       </c>
       <c r="Q635" s="0" t="n">
@@ -54985,12 +55009,12 @@
       </c>
       <c r="L636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280|19#23</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280|19#25</t>
         </is>
       </c>
       <c r="M636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|19#23</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250|19#25</t>
         </is>
       </c>
       <c r="Q636" s="0" t="n">
@@ -56320,12 +56344,12 @@
       </c>
       <c r="L651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280|19#23</t>
+          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280|19#24</t>
         </is>
       </c>
       <c r="M651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|19#23</t>
+          <t>16#1555|99005#1|3#4000000|4#2000|19#24</t>
         </is>
       </c>
       <c r="Q651" s="0" t="n">
@@ -56409,12 +56433,12 @@
       </c>
       <c r="L652" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99005#1|3#10000000|4#5000|6000124#3280|19#67</t>
+          <t>16#4264|99005#1|3#10000000|4#5000|6000124#3280|19#69</t>
         </is>
       </c>
       <c r="M652" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99005#1|3#10000000|4#5000|19#67</t>
+          <t>16#4264|99005#1|3#10000000|4#5000|19#69</t>
         </is>
       </c>
       <c r="Q652" s="0" t="n">
@@ -56498,12 +56522,12 @@
       </c>
       <c r="L653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480|19#149</t>
+          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480|19#153</t>
         </is>
       </c>
       <c r="M653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|19#149</t>
+          <t>16#8748|99005#1|3#15000000|4#10000|19#153</t>
         </is>
       </c>
       <c r="Q653" s="0" t="n">
@@ -56676,12 +56700,12 @@
       </c>
       <c r="L655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280|19#23</t>
+          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280|19#24</t>
         </is>
       </c>
       <c r="M655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|19#23</t>
+          <t>16#1555|99006#1|3#4000000|4#2000|19#24</t>
         </is>
       </c>
       <c r="Q655" s="0" t="n">
@@ -56765,12 +56789,12 @@
       </c>
       <c r="L656" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99006#1|3#10000000|4#5000|6000124#3280|19#67</t>
+          <t>16#4264|99006#1|3#10000000|4#5000|6000124#3280|19#69</t>
         </is>
       </c>
       <c r="M656" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99006#1|3#10000000|4#5000|19#67</t>
+          <t>16#4264|99006#1|3#10000000|4#5000|19#69</t>
         </is>
       </c>
       <c r="Q656" s="0" t="n">
@@ -56854,12 +56878,12 @@
       </c>
       <c r="L657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480|19#149</t>
+          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480|19#153</t>
         </is>
       </c>
       <c r="M657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|19#149</t>
+          <t>16#8748|99006#1|3#15000000|4#10000|19#153</t>
         </is>
       </c>
       <c r="Q657" s="0" t="n">
@@ -57032,12 +57056,12 @@
       </c>
       <c r="L659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280|19#23</t>
+          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280|19#24</t>
         </is>
       </c>
       <c r="M659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|19#23</t>
+          <t>16#1555|99007#1|3#4000000|4#2000|19#24</t>
         </is>
       </c>
       <c r="Q659" s="0" t="n">
@@ -57121,12 +57145,12 @@
       </c>
       <c r="L660" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99007#1|3#10000000|4#5000|6000124#3280|19#67</t>
+          <t>16#4264|99007#1|3#10000000|4#5000|6000124#3280|19#69</t>
         </is>
       </c>
       <c r="M660" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99007#1|3#10000000|4#5000|19#67</t>
+          <t>16#4264|99007#1|3#10000000|4#5000|19#69</t>
         </is>
       </c>
       <c r="Q660" s="0" t="n">
@@ -57210,12 +57234,12 @@
       </c>
       <c r="L661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480|19#149</t>
+          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480|19#153</t>
         </is>
       </c>
       <c r="M661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|19#149</t>
+          <t>16#8748|99007#1|3#15000000|4#10000|19#153</t>
         </is>
       </c>
       <c r="Q661" s="0" t="n">
@@ -57299,12 +57323,12 @@
       </c>
       <c r="L662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280|19#23</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280|19#25</t>
         </is>
       </c>
       <c r="M662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|19#23</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000|19#25</t>
         </is>
       </c>
       <c r="Q662" s="0" t="n">
@@ -57388,12 +57412,12 @@
       </c>
       <c r="L663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980|19#38</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980|19#40</t>
         </is>
       </c>
       <c r="M663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|19#38</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200|19#40</t>
         </is>
       </c>
       <c r="Q663" s="0" t="n">
@@ -57477,12 +57501,12 @@
       </c>
       <c r="L664" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|6000110#3000|72001#250|6000124#3280|19#67</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250|6000124#3280|19#71</t>
         </is>
       </c>
       <c r="M664" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|6000110#3000|72001#250|19#67</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250|19#71</t>
         </is>
       </c>
       <c r="Q664" s="0" t="n">
@@ -57566,12 +57590,12 @@
       </c>
       <c r="L665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280|19#23</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280|19#25</t>
         </is>
       </c>
       <c r="M665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|19#23</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000|19#25</t>
         </is>
       </c>
       <c r="Q665" s="0" t="n">
@@ -57655,12 +57679,12 @@
       </c>
       <c r="L666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980|19#38</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980|19#40</t>
         </is>
       </c>
       <c r="M666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|19#38</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000|19#40</t>
         </is>
       </c>
       <c r="Q666" s="0" t="n">
@@ -57744,12 +57768,12 @@
       </c>
       <c r="L667" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|99002#1|6000110#5000|6000124#3280|19#67</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000|6000124#3280|19#71</t>
         </is>
       </c>
       <c r="M667" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|99002#1|6000110#5000|19#67</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000|19#71</t>
         </is>
       </c>
       <c r="Q667" s="0" t="n">
@@ -57833,12 +57857,12 @@
       </c>
       <c r="L668" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|60411#8|60412#2|6000124#980|19#17</t>
+          <t>16#1176|4#2000|60411#8|60412#2|6000124#980|19#19</t>
         </is>
       </c>
       <c r="M668" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|60411#8|60412#2|19#17</t>
+          <t>16#1176|4#2000|60411#8|60412#2|19#19</t>
         </is>
       </c>
       <c r="Q668" s="0" t="n">
@@ -57922,12 +57946,12 @@
       </c>
       <c r="L669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280|19#23</t>
+          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280|19#26</t>
         </is>
       </c>
       <c r="M669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|19#23</t>
+          <t>16#1555|4#2500|60411#10|60412#3|19#26</t>
         </is>
       </c>
       <c r="Q669" s="0" t="n">
@@ -58011,12 +58035,12 @@
       </c>
       <c r="L670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980|19#38</t>
+          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980|19#41</t>
         </is>
       </c>
       <c r="M670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|19#38</t>
+          <t>16#2475|4#3000|60411#12|6000088#1|19#41</t>
         </is>
       </c>
       <c r="Q670" s="0" t="n">
@@ -58100,12 +58124,12 @@
       </c>
       <c r="L671" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#4000|60411#15|6000088#2|6000124#3280|19#67</t>
+          <t>16#4264|4#4000|60411#15|6000088#2|6000124#3280|19#73</t>
         </is>
       </c>
       <c r="M671" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#4000|60411#15|6000088#2|19#67</t>
+          <t>16#4264|4#4000|60411#15|6000088#2|19#73</t>
         </is>
       </c>
       <c r="Q671" s="0" t="n">
@@ -58189,12 +58213,12 @@
       </c>
       <c r="L672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880|19#108</t>
+          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880|19#117</t>
         </is>
       </c>
       <c r="M672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|19#108</t>
+          <t>16#6466|4#4500|60411#20|6000089#1|19#117</t>
         </is>
       </c>
       <c r="Q672" s="0" t="n">
@@ -58278,12 +58302,12 @@
       </c>
       <c r="L673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480|19#149</t>
+          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480|19#160</t>
         </is>
       </c>
       <c r="M673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|19#149</t>
+          <t>16#8748|4#5000|60412#3|6000090#1|19#160</t>
         </is>
       </c>
       <c r="Q673" s="0" t="n">
@@ -58367,12 +58391,12 @@
       </c>
       <c r="L674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280|19#23</t>
+          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280|19#27</t>
         </is>
       </c>
       <c r="M674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|19#23</t>
+          <t>16#1555|72001#200|60411#10|60412#3|19#27</t>
         </is>
       </c>
       <c r="Q674" s="0" t="n">
@@ -58456,12 +58480,12 @@
       </c>
       <c r="L675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980|19#38</t>
+          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980|19#42</t>
         </is>
       </c>
       <c r="M675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|19#38</t>
+          <t>16#2475|72001#300|60411#15|60412#4|19#42</t>
         </is>
       </c>
       <c r="Q675" s="0" t="n">
@@ -58545,12 +58569,12 @@
       </c>
       <c r="L676" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#500|60411#25|60412#6|6000124#3280|19#67</t>
+          <t>16#4264|72001#500|60411#25|60412#6|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M676" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#500|60411#25|60412#6|19#67</t>
+          <t>16#4264|72001#500|60411#25|60412#6|19#75</t>
         </is>
       </c>
       <c r="Q676" s="0" t="n">
@@ -58634,12 +58658,12 @@
       </c>
       <c r="L677" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#450|60411#15|60412#4|6000124#3280|19#67</t>
+          <t>16#4264|72001#450|60411#15|60412#4|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M677" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#450|60411#15|60412#4|19#67</t>
+          <t>16#4264|72001#450|60411#15|60412#4|19#75</t>
         </is>
       </c>
       <c r="Q677" s="0" t="n">
@@ -58723,12 +58747,12 @@
       </c>
       <c r="L678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880|19#108</t>
+          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880|19#119</t>
         </is>
       </c>
       <c r="M678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|19#108</t>
+          <t>16#6466|72001#500|60411#20|60412#5|19#119</t>
         </is>
       </c>
       <c r="Q678" s="0" t="n">
@@ -58812,12 +58836,12 @@
       </c>
       <c r="L679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480|19#149</t>
+          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480|19#164</t>
         </is>
       </c>
       <c r="M679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|19#149</t>
+          <t>16#8748|72001#550|60411#25|60412#5|19#164</t>
         </is>
       </c>
       <c r="Q679" s="0" t="n">
@@ -58901,12 +58925,12 @@
       </c>
       <c r="L680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280|19#23</t>
+          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280|19#28</t>
         </is>
       </c>
       <c r="M680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|19#23</t>
+          <t>16#1555|60417#1|60411#8|60412#2|19#28</t>
         </is>
       </c>
       <c r="Q680" s="0" t="n">
@@ -58990,12 +59014,12 @@
       </c>
       <c r="L681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980|19#38</t>
+          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980|19#44</t>
         </is>
       </c>
       <c r="M681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|19#38</t>
+          <t>16#2475|60417#1|60411#15|60412#4|19#44</t>
         </is>
       </c>
       <c r="Q681" s="0" t="n">
@@ -59079,12 +59103,12 @@
       </c>
       <c r="L682" s="0" t="inlineStr">
         <is>
-          <t>16#4264|60417#1|60411#25|60412#6|6000124#3280|19#67</t>
+          <t>16#4264|60417#1|60411#25|60412#6|6000124#3280|19#77</t>
         </is>
       </c>
       <c r="M682" s="0" t="inlineStr">
         <is>
-          <t>16#4264|60417#1|60411#25|60412#6|19#67</t>
+          <t>16#4264|60417#1|60411#25|60412#6|19#77</t>
         </is>
       </c>
       <c r="Q682" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -18828,7 +18828,7 @@
       <c r="R228" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="S228" t="n">
+      <c r="S228" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T228" s="0" t="n">
@@ -18857,7 +18857,7 @@
       <c r="AA228" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="AB228" t="n">
+      <c r="AB228" s="0" t="n">
         <v>30</v>
       </c>
       <c r="AF228" s="0" t="inlineStr">
@@ -18932,7 +18932,7 @@
       <c r="R229" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="S229" t="n">
+      <c r="S229" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T229" s="0" t="n">
@@ -18947,10 +18947,10 @@
       <c r="X229" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Y229" t="n">
+      <c r="Y229" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="AB229" t="n">
+      <c r="AB229" s="0" t="n">
         <v>30</v>
       </c>
       <c r="AF229" s="0" t="inlineStr">
@@ -19025,7 +19025,7 @@
       <c r="R230" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="S230" t="n">
+      <c r="S230" s="0" t="n">
         <v>1</v>
       </c>
       <c r="T230" s="0" t="n">
@@ -19037,10 +19037,10 @@
       <c r="X230" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Y230" t="n">
+      <c r="Y230" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="AB230" t="n">
+      <c r="AB230" s="0" t="n">
         <v>30</v>
       </c>
       <c r="AF230" s="0" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="M267" s="0" t="inlineStr">
         <is>
-          <t>16#38640</t>
+          <t>16#46460</t>
         </is>
       </c>
       <c r="N267" s="0" t="n">
@@ -23275,12 +23275,12 @@
       </c>
       <c r="L280" s="0" t="inlineStr">
         <is>
-          <t>16#600|81150#3|19#5|61#1|3#1200000|6000124#300</t>
+          <t>16#600|81150#3|19#7|61#1|3#1200000|6000124#300</t>
         </is>
       </c>
       <c r="M280" s="0" t="inlineStr">
         <is>
-          <t>16#300|81150#3|19#5|61#1|3#1200000</t>
+          <t>16#300|81150#3|19#7|61#1|3#1200000</t>
         </is>
       </c>
       <c r="Q280" s="0" t="n">
@@ -23367,12 +23367,12 @@
       </c>
       <c r="L281" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#11|4#600|80#6|3#1700000|6000124#600</t>
+          <t>16#1320|81150#6|61#1|19#15|4#600|80#6|3#1700000|6000124#600</t>
         </is>
       </c>
       <c r="M281" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#11|4#600|80#6|3#1700000</t>
+          <t>16#1320|81150#6|61#1|19#15|4#600|80#6|3#1700000</t>
         </is>
       </c>
       <c r="Q281" s="0" t="n">
@@ -23715,12 +23715,12 @@
       </c>
       <c r="L285" s="0" t="inlineStr">
         <is>
-          <t>16#600|81150#3|19#5|61#1|6000110#800|6000124#300</t>
+          <t>16#600|81150#3|19#7|61#1|6000110#800|6000124#300</t>
         </is>
       </c>
       <c r="M285" s="0" t="inlineStr">
         <is>
-          <t>16#300|81150#3|19#5|61#1|6000110#800</t>
+          <t>16#300|81150#3|19#7|61#1|6000110#800</t>
         </is>
       </c>
       <c r="Q285" s="0" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="L286" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#11|17009#70|72001#20|80#6|6000110#1600|6000124#600</t>
+          <t>16#1320|81150#6|61#1|19#15|17009#70|72001#20|80#6|6000110#1600|6000124#600</t>
         </is>
       </c>
       <c r="M286" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#11|17009#70|72001#20|80#6|6000110#1600</t>
+          <t>16#1320|81150#6|61#1|19#15|17009#70|72001#20|80#6|6000110#1600</t>
         </is>
       </c>
       <c r="Q286" s="0" t="n">
@@ -24061,12 +24061,12 @@
       </c>
       <c r="L289" s="0" t="inlineStr">
         <is>
-          <t>16#360|81113#1|60430#1|19#5|6000124#300</t>
+          <t>16#360|81113#1|60430#1|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M289" s="0" t="inlineStr">
         <is>
-          <t>16#360|81113#1|60430#1|19#5</t>
+          <t>16#360|81113#1|60430#1|19#6</t>
         </is>
       </c>
       <c r="Q289" s="0" t="n">
@@ -24150,12 +24150,12 @@
       </c>
       <c r="L290" s="0" t="inlineStr">
         <is>
-          <t>16#816|81113#2|60431#1|19#11|6000124#680</t>
+          <t>16#816|81113#2|60431#1|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M290" s="0" t="inlineStr">
         <is>
-          <t>16#816|81113#2|60431#1|19#11</t>
+          <t>16#816|81113#2|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q290" s="0" t="n">
@@ -24239,12 +24239,12 @@
       </c>
       <c r="L291" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|60431#1|19#17|6000124#980</t>
+          <t>16#1127|60403#1|60431#1|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M291" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|60431#1|19#17</t>
+          <t>16#1127|60403#1|60431#1|19#22</t>
         </is>
       </c>
       <c r="Q291" s="0" t="n">
@@ -24506,12 +24506,12 @@
       </c>
       <c r="L294" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000089#1|6000110#4000|19#70|6000124#3280</t>
+          <t>16#3674|6000089#1|6000110#4000|19#88|6000124#3280</t>
         </is>
       </c>
       <c r="M294" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000089#1|6000110#4000|19#70</t>
+          <t>16#3674|6000089#1|6000110#4000|19#88</t>
         </is>
       </c>
       <c r="Q294" s="0" t="n">
@@ -24593,12 +24593,12 @@
       </c>
       <c r="L295" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#20|60431#8|14#50000000|6000124#3280|19#70</t>
+          <t>16#3674|6000085#20|60431#8|14#50000000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M295" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#20|60431#8|14#50000000|19#70</t>
+          <t>16#3674|6000085#20|60431#8|14#50000000|19#88</t>
         </is>
       </c>
       <c r="Q295" s="0" t="n">
@@ -24682,12 +24682,12 @@
       </c>
       <c r="L296" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000110#15000|60431#8|19#70|6000124#3280</t>
+          <t>16#3674|6000110#15000|60431#8|19#88|6000124#3280</t>
         </is>
       </c>
       <c r="M296" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000110#15000|60431#8|19#70</t>
+          <t>16#3674|6000110#15000|60431#8|19#88</t>
         </is>
       </c>
       <c r="Q296" s="0" t="n">
@@ -25630,12 +25630,12 @@
       </c>
       <c r="L307" s="0" t="inlineStr">
         <is>
-          <t>16#360|81148#20|19#5|60#5|6000124#300</t>
+          <t>16#360|81148#20|19#6|60#5|6000124#300</t>
         </is>
       </c>
       <c r="M307" s="0" t="inlineStr">
         <is>
-          <t>16#360|81148#20|19#5|60#5</t>
+          <t>16#360|81148#20|19#6|60#5</t>
         </is>
       </c>
       <c r="Q307" s="0" t="n">
@@ -25719,12 +25719,12 @@
       </c>
       <c r="L308" s="0" t="inlineStr">
         <is>
-          <t>16#816|81148#50|19#11|60431#1|6000124#680</t>
+          <t>16#816|81148#50|19#14|60431#1|6000124#680</t>
         </is>
       </c>
       <c r="M308" s="0" t="inlineStr">
         <is>
-          <t>16#816|81148#50|19#11|60431#1</t>
+          <t>16#816|81148#50|19#14|60431#1</t>
         </is>
       </c>
       <c r="Q308" s="0" t="n">
@@ -25808,12 +25808,12 @@
       </c>
       <c r="L309" s="0" t="inlineStr">
         <is>
-          <t>16#1472|81148#50|20#24|6000110#2000|6000124#1280</t>
+          <t>16#1472|81148#50|20#30|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M309" s="0" t="inlineStr">
         <is>
-          <t>16#1472|81148#50|20#24|6000110#2000</t>
+          <t>16#1472|81148#50|20#30|6000110#2000</t>
         </is>
       </c>
       <c r="Q309" s="0" t="n">
@@ -25986,12 +25986,12 @@
       </c>
       <c r="L311" s="0" t="inlineStr">
         <is>
-          <t>16#3226|81148#100|20#6|19#52|6000124#2880</t>
+          <t>16#3226|81148#100|20#6|19#67|6000124#2880</t>
         </is>
       </c>
       <c r="M311" s="0" t="inlineStr">
         <is>
-          <t>16#3226|81148#100|20#6|19#52</t>
+          <t>16#3226|81148#100|20#6|19#67</t>
         </is>
       </c>
       <c r="Q311" s="0" t="n">
@@ -26075,12 +26075,12 @@
       </c>
       <c r="L312" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60428#1|20#8|19#62|6000124#3280</t>
+          <t>16#3674|60428#1|20#8|19#80|6000124#3280</t>
         </is>
       </c>
       <c r="M312" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60428#1|20#8|19#62</t>
+          <t>16#3674|60428#1|20#8|19#80</t>
         </is>
       </c>
       <c r="Q312" s="0" t="n">
@@ -26162,12 +26162,12 @@
       </c>
       <c r="L313" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60459#1|20#12|19#143|6000124#6480</t>
+          <t>16#7452|60459#1|20#12|19#183|6000124#6480</t>
         </is>
       </c>
       <c r="M313" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60459#1|20#12|19#143</t>
+          <t>16#7452|60459#1|20#12|19#183</t>
         </is>
       </c>
       <c r="Q313" s="0" t="n">
@@ -26249,12 +26249,12 @@
       </c>
       <c r="L314" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60423#1|20#12|19#143|6000124#6480</t>
+          <t>16#7452|60423#1|20#12|19#183|6000124#6480</t>
         </is>
       </c>
       <c r="M314" s="0" t="inlineStr">
         <is>
-          <t>16#7452|60423#1|20#12|19#143</t>
+          <t>16#7452|60423#1|20#12|19#183</t>
         </is>
       </c>
       <c r="Q314" s="0" t="n">
@@ -26636,12 +26636,12 @@
       </c>
       <c r="L318" s="0" t="inlineStr">
         <is>
-          <t>88#1|16#816|19#11|4#1000|6000124#680</t>
+          <t>88#1|16#816|19#14|4#1000|6000124#680</t>
         </is>
       </c>
       <c r="M318" s="0" t="inlineStr">
         <is>
-          <t>88#1|16#816|19#11|4#1000</t>
+          <t>88#1|16#816|19#14|4#1000</t>
         </is>
       </c>
       <c r="Q318" s="0" t="inlineStr">
@@ -26742,12 +26742,12 @@
       </c>
       <c r="L319" s="0" t="inlineStr">
         <is>
-          <t>82001#1|16#360|20#4|4#800|6000124#300</t>
+          <t>82001#1|16#360|20#5|4#800|6000124#300</t>
         </is>
       </c>
       <c r="M319" s="0" t="inlineStr">
         <is>
-          <t>82001#1|16#360|20#4|4#800</t>
+          <t>82001#1|16#360|20#5|4#800</t>
         </is>
       </c>
       <c r="Q319" s="0" t="inlineStr">
@@ -26848,12 +26848,12 @@
       </c>
       <c r="L320" s="0" t="inlineStr">
         <is>
-          <t>16#360|100#1|10423#2|10428#2|6000124#300|19#4</t>
+          <t>16#360|100#1|10423#2|10428#2|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M320" s="0" t="inlineStr">
         <is>
-          <t>16#360|100#1|10423#2|10428#2|19#4</t>
+          <t>16#360|100#1|10423#2|10428#2|19#5</t>
         </is>
       </c>
       <c r="Q320" s="0" t="inlineStr">
@@ -27050,12 +27050,12 @@
       </c>
       <c r="L322" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20007#1|20#155|6000110#5000|6000124#6480</t>
+          <t>16#7452|20007#1|20#195|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M322" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20007#1|20#155|6000110#5000</t>
+          <t>16#7452|20007#1|20#195|6000110#5000</t>
         </is>
       </c>
       <c r="Q322" s="0" t="inlineStr">
@@ -27144,12 +27144,12 @@
       </c>
       <c r="L323" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20009#1|17014#300|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|20009#1|17014#300|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M323" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20009#1|17014#300|6000110#5000|19#155</t>
+          <t>16#7452|20009#1|17014#300|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q323" s="0" t="inlineStr">
@@ -27235,12 +27235,12 @@
       </c>
       <c r="L324" s="0" t="inlineStr">
         <is>
-          <t>200011#1|20010#1|19#20|200010#1000|6000124#600</t>
+          <t>200011#1|20010#1|19#24|200010#1000|6000124#600</t>
         </is>
       </c>
       <c r="M324" s="0" t="inlineStr">
         <is>
-          <t>200011#1|20010#1|19#20|200010#1000</t>
+          <t>200011#1|20010#1|19#24|200010#1000</t>
         </is>
       </c>
       <c r="Q324" s="0" t="inlineStr">
@@ -28769,12 +28769,12 @@
       </c>
       <c r="L342" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#2000|70034#2|72001#100|6000124#680</t>
+          <t>16#816|19#25|4#2000|70034#2|72001#100|6000124#680</t>
         </is>
       </c>
       <c r="M342" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#2000|70034#2|72001#100</t>
+          <t>16#816|19#25|4#2000|70034#2|72001#100</t>
         </is>
       </c>
       <c r="Q342" s="0" t="n">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="L343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#30|81114#2|6000088#1|14#5000000|6000124#980</t>
+          <t>16#1127|19#37|81114#2|6000088#1|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#30|81114#2|6000088#1|14#5000000</t>
+          <t>16#1127|19#37|81114#2|6000088#1|14#5000000</t>
         </is>
       </c>
       <c r="Q343" s="0" t="n">
@@ -28931,12 +28931,12 @@
       </c>
       <c r="L344" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60433#1|20#5|19#65|61#5|6000124#3280</t>
+          <t>16#3674|60433#1|20#5|19#83|61#5|6000124#3280</t>
         </is>
       </c>
       <c r="M344" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60433#1|20#5|19#65|61#5</t>
+          <t>16#3674|60433#1|20#5|19#83|61#5</t>
         </is>
       </c>
       <c r="Q344" s="0" t="n">
@@ -29012,12 +29012,12 @@
       </c>
       <c r="L345" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#2000|18101#10|61#2|6000124#680</t>
+          <t>16#816|19#25|4#2000|18101#10|61#2|6000124#680</t>
         </is>
       </c>
       <c r="M345" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#2000|18101#10|61#2</t>
+          <t>16#816|19#25|4#2000|18101#10|61#2</t>
         </is>
       </c>
       <c r="Q345" s="0" t="n">
@@ -29093,12 +29093,12 @@
       </c>
       <c r="L346" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|6000124#1280|19#24</t>
+          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M346" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|19#24</t>
+          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|19#30</t>
         </is>
       </c>
       <c r="Q346" s="0" t="n">
@@ -29174,12 +29174,12 @@
       </c>
       <c r="L347" s="0" t="inlineStr">
         <is>
-          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|6000124#2880|19#58</t>
+          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|6000124#2880|19#73</t>
         </is>
       </c>
       <c r="M347" s="0" t="inlineStr">
         <is>
-          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|19#58</t>
+          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|19#73</t>
         </is>
       </c>
       <c r="Q347" s="0" t="n">
@@ -29255,12 +29255,12 @@
       </c>
       <c r="L348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|17012#30|17011#120|17009#300|6000124#1280</t>
+          <t>16#1472|19#38|17012#30|17011#120|17009#300|6000124#1280</t>
         </is>
       </c>
       <c r="M348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|17012#30|17011#120|17009#300</t>
+          <t>16#1472|19#38|17012#30|17011#120|17009#300</t>
         </is>
       </c>
       <c r="Q348" s="0" t="n">
@@ -29336,12 +29336,12 @@
       </c>
       <c r="L349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#20|4#2000|6000110#2000|6000124#980</t>
+          <t>16#1127|20#8|19#27|4#2000|6000110#2000|6000124#980</t>
         </is>
       </c>
       <c r="M349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#20|4#2000|6000110#2000</t>
+          <t>16#1127|20#8|19#27|4#2000|6000110#2000</t>
         </is>
       </c>
       <c r="Q349" s="0" t="n">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="L350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|6000097#30|6000098#120|6000092#120|6000124#1280</t>
+          <t>16#1472|19#38|6000097#30|6000098#120|6000092#120|6000124#1280</t>
         </is>
       </c>
       <c r="M350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#30|6000097#30|6000098#120|6000092#120</t>
+          <t>16#1472|19#38|6000097#30|6000098#120|6000092#120</t>
         </is>
       </c>
       <c r="Q350" s="0" t="n">
@@ -29498,12 +29498,12 @@
       </c>
       <c r="L351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#20|60403#1|60402#1|6000124#980</t>
+          <t>16#1127|20#8|19#27|60403#1|60402#1|6000124#980</t>
         </is>
       </c>
       <c r="M351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#20|60403#1|60402#1</t>
+          <t>16#1127|20#8|19#27|60403#1|60402#1</t>
         </is>
       </c>
       <c r="Q351" s="0" t="n">
@@ -29579,12 +29579,12 @@
       </c>
       <c r="L352" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|6000124#1980|19#39</t>
+          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M352" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|19#39</t>
+          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|19#49</t>
         </is>
       </c>
       <c r="Q352" s="0" t="n">
@@ -29660,12 +29660,12 @@
       </c>
       <c r="L353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#30|60403#1|60402#2|6000124#1280</t>
+          <t>16#1472|20#10|19#40|60403#1|60402#2|6000124#1280</t>
         </is>
       </c>
       <c r="M353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#30|60403#1|60402#2</t>
+          <t>16#1472|20#10|19#40|60403#1|60402#2</t>
         </is>
       </c>
       <c r="Q353" s="0" t="n">
@@ -29741,12 +29741,12 @@
       </c>
       <c r="L354" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#39|10423#5|10428#5|10424#30|6000124#1980</t>
+          <t>16#2218|20#49|10423#5|10428#5|10424#30|6000124#1980</t>
         </is>
       </c>
       <c r="M354" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#39|10423#5|10428#5|10424#30</t>
+          <t>16#2218|20#49|10423#5|10428#5|10424#30</t>
         </is>
       </c>
       <c r="Q354" s="0" t="n">
@@ -29990,12 +29990,12 @@
       </c>
       <c r="L357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#5|60103#1|6000124#300</t>
+          <t>16#600|19#7|60103#1|6000124#300</t>
         </is>
       </c>
       <c r="M357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#5|60103#1</t>
+          <t>16#600|19#7|60103#1</t>
         </is>
       </c>
       <c r="Q357" s="0" t="n">
@@ -30074,12 +30074,12 @@
       </c>
       <c r="L358" s="0" t="inlineStr">
         <is>
-          <t>16#1360|81148#50|19#10|6000124#680</t>
+          <t>16#1360|81148#50|19#13|6000124#680</t>
         </is>
       </c>
       <c r="M358" s="0" t="inlineStr">
         <is>
-          <t>16#1360|81148#50|19#10</t>
+          <t>16#1360|81148#50|19#13</t>
         </is>
       </c>
       <c r="Q358" s="0" t="n">
@@ -30158,12 +30158,12 @@
       </c>
       <c r="L359" s="0" t="inlineStr">
         <is>
-          <t>16#1960|14#20000000|14#10000000|14#10000000|6000124#980|19#13</t>
+          <t>16#1960|14#20000000|14#10000000|14#10000000|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M359" s="0" t="inlineStr">
         <is>
-          <t>16#1960|14#20000000|14#10000000|14#10000000|19#13</t>
+          <t>16#1960|14#20000000|14#10000000|14#10000000|19#18</t>
         </is>
       </c>
       <c r="Q359" s="0" t="n">
@@ -30242,12 +30242,12 @@
       </c>
       <c r="L360" s="0" t="inlineStr">
         <is>
-          <t>16#2560|81148#100|19#19|60155#1|6000124#1280</t>
+          <t>16#2560|81148#100|19#25|60155#1|6000124#1280</t>
         </is>
       </c>
       <c r="M360" s="0" t="inlineStr">
         <is>
-          <t>16#2560|81148#100|19#19|60155#1</t>
+          <t>16#2560|81148#100|19#25|60155#1</t>
         </is>
       </c>
       <c r="Q360" s="0" t="n">
@@ -30326,12 +30326,12 @@
       </c>
       <c r="L361" s="0" t="inlineStr">
         <is>
-          <t>16#6560|60432#1|19#57|6000088#1|6000124#3280</t>
+          <t>16#6560|60432#1|19#75|6000088#1|6000124#3280</t>
         </is>
       </c>
       <c r="M361" s="0" t="inlineStr">
         <is>
-          <t>16#6560|60432#1|19#57|6000088#1</t>
+          <t>16#6560|60432#1|19#75|6000088#1</t>
         </is>
       </c>
       <c r="Q361" s="0" t="n">
@@ -30410,12 +30410,12 @@
       </c>
       <c r="L362" s="0" t="inlineStr">
         <is>
-          <t>16#12960|6000072#50|20#130|60156#1|6000124#6480</t>
+          <t>16#12960|6000072#50|20#170|60156#1|6000124#6480</t>
         </is>
       </c>
       <c r="M362" s="0" t="inlineStr">
         <is>
-          <t>16#12960|6000072#50|20#130|60156#1</t>
+          <t>16#12960|6000072#50|20#170|60156#1</t>
         </is>
       </c>
       <c r="Q362" s="0" t="n">
@@ -30785,12 +30785,12 @@
       </c>
       <c r="L366" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60402#4|19#17|14#3000000|6000124#980</t>
+          <t>16#1127|60402#4|19#22|14#3000000|6000124#980</t>
         </is>
       </c>
       <c r="M366" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60402#4|19#17|14#3000000</t>
+          <t>16#1127|60402#4|19#22|14#3000000</t>
         </is>
       </c>
       <c r="Q366" s="0" t="n">
@@ -30882,12 +30882,12 @@
       </c>
       <c r="L367" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60403#5|19#39|14#10000000|6000124#1980</t>
+          <t>16#2218|60403#5|19#49|14#10000000|6000124#1980</t>
         </is>
       </c>
       <c r="M367" s="0" t="inlineStr">
         <is>
-          <t>16#2218|60403#5|19#39|14#10000000</t>
+          <t>16#2218|60403#5|19#49|14#10000000</t>
         </is>
       </c>
       <c r="Q367" s="0" t="n">
@@ -31076,12 +31076,12 @@
       </c>
       <c r="L369" s="0" t="inlineStr">
         <is>
-          <t>16#360|18101#10|4#500|14#1000000|6000124#300|19#4</t>
+          <t>16#360|18101#10|4#500|14#1000000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M369" s="0" t="inlineStr">
         <is>
-          <t>16#360|18101#10|4#500|14#1000000|19#4</t>
+          <t>16#360|18101#10|4#500|14#1000000|19#5</t>
         </is>
       </c>
       <c r="Q369" s="0" t="n">
@@ -31171,12 +31171,12 @@
       </c>
       <c r="L370" s="0" t="inlineStr">
         <is>
-          <t>16#2218|18102#10|20#39|6001020#50|6000124#1980</t>
+          <t>16#2218|18102#10|20#49|6001020#50|6000124#1980</t>
         </is>
       </c>
       <c r="M370" s="0" t="inlineStr">
         <is>
-          <t>16#2218|18102#10|20#39|6001020#50</t>
+          <t>16#2218|18102#10|20#49|6001020#50</t>
         </is>
       </c>
       <c r="Q370" s="0" t="n">
@@ -31268,12 +31268,12 @@
       </c>
       <c r="L371" s="0" t="inlineStr">
         <is>
-          <t>16#816|17012#30|17011#60|17009#200|6000124#680|19#11</t>
+          <t>16#816|17012#30|17011#60|17009#200|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M371" s="0" t="inlineStr">
         <is>
-          <t>16#816|17012#30|17011#60|17009#200|19#11</t>
+          <t>16#816|17012#30|17011#60|17009#200|19#14</t>
         </is>
       </c>
       <c r="Q371" s="0" t="n">
@@ -31365,12 +31365,12 @@
       </c>
       <c r="L372" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17012#150|17011#300|17009#1000|6000124#3280|19#70</t>
+          <t>16#3674|17012#150|17011#300|17009#1000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M372" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17012#150|17011#300|17009#1000|19#70</t>
+          <t>16#3674|17012#150|17011#300|17009#1000|19#88</t>
         </is>
       </c>
       <c r="Q372" s="0" t="n">
@@ -31462,12 +31462,12 @@
       </c>
       <c r="L373" s="0" t="inlineStr">
         <is>
-          <t>16#2218|6000097#20|6000098#60|6000092#250|6000124#1980|19#39</t>
+          <t>16#2218|6000097#20|6000098#60|6000092#250|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M373" s="0" t="inlineStr">
         <is>
-          <t>16#2218|6000097#20|6000098#60|6000092#250|19#39</t>
+          <t>16#2218|6000097#20|6000098#60|6000092#250|19#49</t>
         </is>
       </c>
       <c r="Q373" s="0" t="n">
@@ -31557,12 +31557,12 @@
       </c>
       <c r="L374" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#30|10441#150|6000124#1980|19#39</t>
+          <t>16#2218|99000#8|10442#30|10441#150|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M374" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#30|10441#150|19#39</t>
+          <t>16#2218|99000#8|10442#30|10441#150|19#49</t>
         </is>
       </c>
       <c r="Q374" s="0" t="n">
@@ -31652,12 +31652,12 @@
       </c>
       <c r="L375" s="0" t="inlineStr">
         <is>
-          <t>16#816|10423#1|10422#2|10425#100|6000124#680|19#11</t>
+          <t>16#816|10423#1|10422#2|10425#100|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M375" s="0" t="inlineStr">
         <is>
-          <t>16#816|10423#1|10422#2|10425#100|19#11</t>
+          <t>16#816|10423#1|10422#2|10425#100|19#14</t>
         </is>
       </c>
       <c r="Q375" s="0" t="n">
@@ -31747,12 +31747,12 @@
       </c>
       <c r="L376" s="0" t="inlineStr">
         <is>
-          <t>16#3674|10423#6|10424#15|10425#600|6000124#3280|19#70</t>
+          <t>16#3674|10423#6|10424#15|10425#600|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M376" s="0" t="inlineStr">
         <is>
-          <t>16#3674|10423#6|10424#15|10425#600|19#70</t>
+          <t>16#3674|10423#6|10424#15|10425#600|19#88</t>
         </is>
       </c>
       <c r="Q376" s="0" t="n">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="L391" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5|6000124#300</t>
+          <t>16#360|1004#5|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M391" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5</t>
+          <t>16#360|1004#5|19#6</t>
         </is>
       </c>
       <c r="Q391" s="0" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="L392" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11|6000124#680</t>
+          <t>16#816|1004#11|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M392" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11</t>
+          <t>16#816|1004#11|19#14</t>
         </is>
       </c>
       <c r="Q392" s="0" t="n">
@@ -33331,12 +33331,12 @@
       </c>
       <c r="L393" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24|6000124#1280</t>
+          <t>16#1472|1004#24|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M393" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24</t>
+          <t>16#1472|1004#24|20#30</t>
         </is>
       </c>
       <c r="Q393" s="0" t="n">
@@ -33423,12 +33423,12 @@
       </c>
       <c r="L394" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M394" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q394" s="0" t="n">
@@ -33515,12 +33515,12 @@
       </c>
       <c r="L395" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5|6000124#300</t>
+          <t>16#360|50002#10|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M395" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5</t>
+          <t>16#360|50002#10|19#6</t>
         </is>
       </c>
       <c r="Q395" s="0" t="n">
@@ -33607,12 +33607,12 @@
       </c>
       <c r="L396" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11|6000124#680</t>
+          <t>16#816|50002#25|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M396" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11</t>
+          <t>16#816|50002#25|19#14</t>
         </is>
       </c>
       <c r="Q396" s="0" t="n">
@@ -33699,12 +33699,12 @@
       </c>
       <c r="L397" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24|6000124#1280</t>
+          <t>16#1472|50002#50|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M397" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24</t>
+          <t>16#1472|50002#50|20#30</t>
         </is>
       </c>
       <c r="Q397" s="0" t="n">
@@ -33791,12 +33791,12 @@
       </c>
       <c r="L398" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M398" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q398" s="0" t="n">
@@ -33883,12 +33883,12 @@
       </c>
       <c r="L399" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|81114#1|6000124#980</t>
+          <t>16#1127|87#20|20#2|81114#1|6000124#980</t>
         </is>
       </c>
       <c r="M399" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|81114#1</t>
+          <t>16#1127|87#20|20#2|81114#1</t>
         </is>
       </c>
       <c r="Q399" s="0" t="n">
@@ -33972,12 +33972,12 @@
       </c>
       <c r="L400" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|60415#1|6000124#1280</t>
+          <t>16#1472|87#27|20#3|60415#1|6000124#1280</t>
         </is>
       </c>
       <c r="M400" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|60415#1</t>
+          <t>16#1472|87#27|20#3|60415#1</t>
         </is>
       </c>
       <c r="Q400" s="0" t="n">
@@ -34061,12 +34061,12 @@
       </c>
       <c r="L401" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001022#50|60416#1|6000124#1980</t>
+          <t>16#2218|87#49|6001022#50|60416#1|6000124#1980</t>
         </is>
       </c>
       <c r="M401" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001022#50|60416#1</t>
+          <t>16#2218|87#49|6001022#50|60416#1</t>
         </is>
       </c>
       <c r="Q401" s="0" t="n">
@@ -34150,12 +34150,12 @@
       </c>
       <c r="L402" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000021#50|60408#1|6000124#3280</t>
+          <t>16#3674|87#88|6000021#50|60408#1|6000124#3280</t>
         </is>
       </c>
       <c r="M402" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000021#50|60408#1</t>
+          <t>16#3674|87#88|6000021#50|60408#1</t>
         </is>
       </c>
       <c r="Q402" s="0" t="n">
@@ -34239,12 +34239,12 @@
       </c>
       <c r="L403" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|6000110#1500|6000124#980</t>
+          <t>16#1127|87#20|20#2|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M403" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|6000110#1500</t>
+          <t>16#1127|87#20|20#2|6000110#1500</t>
         </is>
       </c>
       <c r="Q403" s="0" t="n">
@@ -34328,12 +34328,12 @@
       </c>
       <c r="L404" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#35|20#4|6000088#1|6000124#1980</t>
+          <t>16#2218|87#45|20#4|6000088#1|6000124#1980</t>
         </is>
       </c>
       <c r="M404" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#35|20#4|6000088#1</t>
+          <t>16#2218|87#45|20#4|6000088#1</t>
         </is>
       </c>
       <c r="Q404" s="0" t="n">
@@ -34417,12 +34417,12 @@
       </c>
       <c r="L405" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6001026#50|6000110#7500|6000124#3280</t>
+          <t>16#3674|87#88|6001026#50|6000110#7500|6000124#3280</t>
         </is>
       </c>
       <c r="M405" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6001026#50|6000110#7500</t>
+          <t>16#3674|87#88|6001026#50|6000110#7500</t>
         </is>
       </c>
       <c r="Q405" s="0" t="n">
@@ -34506,12 +34506,12 @@
       </c>
       <c r="L406" s="0" t="inlineStr">
         <is>
-          <t>16#5612|87#112|6000055#50|6000089#1|6000124#4880</t>
+          <t>16#5612|87#141|6000055#50|6000089#1|6000124#4880</t>
         </is>
       </c>
       <c r="M406" s="0" t="inlineStr">
         <is>
-          <t>16#5612|87#112|6000055#50|6000089#1</t>
+          <t>16#5612|87#141|6000055#50|6000089#1</t>
         </is>
       </c>
       <c r="Q406" s="0" t="n">
@@ -34595,12 +34595,12 @@
       </c>
       <c r="L407" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|17009#100|6000124#980</t>
+          <t>16#1127|87#20|20#2|17009#100|6000124#980</t>
         </is>
       </c>
       <c r="M407" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|17009#100</t>
+          <t>16#1127|87#20|20#2|17009#100</t>
         </is>
       </c>
       <c r="Q407" s="0" t="n">
@@ -34684,12 +34684,12 @@
       </c>
       <c r="L408" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|17011#80|6000124#1280</t>
+          <t>16#1472|87#27|20#3|17011#80|6000124#1280</t>
         </is>
       </c>
       <c r="M408" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|17011#80</t>
+          <t>16#1472|87#27|20#3|17011#80</t>
         </is>
       </c>
       <c r="Q408" s="0" t="n">
@@ -34773,12 +34773,12 @@
       </c>
       <c r="L409" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001023#50|17012#30|6000124#1980</t>
+          <t>16#2218|87#49|6001023#50|17012#30|6000124#1980</t>
         </is>
       </c>
       <c r="M409" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001023#50|17012#30</t>
+          <t>16#2218|87#49|6001023#50|17012#30</t>
         </is>
       </c>
       <c r="Q409" s="0" t="n">
@@ -34862,12 +34862,12 @@
       </c>
       <c r="L410" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000036#50|6000089#1|6000124#3280</t>
+          <t>16#3674|87#88|6000036#50|6000089#1|6000124#3280</t>
         </is>
       </c>
       <c r="M410" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000036#50|6000089#1</t>
+          <t>16#3674|87#88|6000036#50|6000089#1</t>
         </is>
       </c>
       <c r="Q410" s="0" t="n">
@@ -34951,12 +34951,12 @@
       </c>
       <c r="L411" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5|6000124#300</t>
+          <t>16#360|1004#5|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M411" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5</t>
+          <t>16#360|1004#5|19#6</t>
         </is>
       </c>
       <c r="Q411" s="0" t="n">
@@ -35043,12 +35043,12 @@
       </c>
       <c r="L412" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11|6000124#680</t>
+          <t>16#816|1004#11|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M412" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11</t>
+          <t>16#816|1004#11|19#14</t>
         </is>
       </c>
       <c r="Q412" s="0" t="n">
@@ -35135,12 +35135,12 @@
       </c>
       <c r="L413" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24|6000124#1280</t>
+          <t>16#1472|1004#24|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M413" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24</t>
+          <t>16#1472|1004#24|20#30</t>
         </is>
       </c>
       <c r="Q413" s="0" t="n">
@@ -35227,12 +35227,12 @@
       </c>
       <c r="L414" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M414" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q414" s="0" t="n">
@@ -35319,12 +35319,12 @@
       </c>
       <c r="L415" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5|6000124#300</t>
+          <t>16#360|50002#10|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M415" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5</t>
+          <t>16#360|50002#10|19#6</t>
         </is>
       </c>
       <c r="Q415" s="0" t="n">
@@ -35411,12 +35411,12 @@
       </c>
       <c r="L416" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11|6000124#680</t>
+          <t>16#816|50002#25|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M416" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11</t>
+          <t>16#816|50002#25|19#14</t>
         </is>
       </c>
       <c r="Q416" s="0" t="n">
@@ -35503,12 +35503,12 @@
       </c>
       <c r="L417" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24|6000124#1280</t>
+          <t>16#1472|50002#50|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M417" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24</t>
+          <t>16#1472|50002#50|20#30</t>
         </is>
       </c>
       <c r="Q417" s="0" t="n">
@@ -35595,12 +35595,12 @@
       </c>
       <c r="L418" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M418" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q418" s="0" t="n">
@@ -35687,12 +35687,12 @@
       </c>
       <c r="L419" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|81114#1|6000124#980</t>
+          <t>16#1127|87#20|20#2|81114#1|6000124#980</t>
         </is>
       </c>
       <c r="M419" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|81114#1</t>
+          <t>16#1127|87#20|20#2|81114#1</t>
         </is>
       </c>
       <c r="Q419" s="0" t="n">
@@ -35776,12 +35776,12 @@
       </c>
       <c r="L420" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|60415#1|6000124#1280</t>
+          <t>16#1472|87#27|20#3|60415#1|6000124#1280</t>
         </is>
       </c>
       <c r="M420" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#21|20#3|60415#1</t>
+          <t>16#1472|87#27|20#3|60415#1</t>
         </is>
       </c>
       <c r="Q420" s="0" t="n">
@@ -35865,12 +35865,12 @@
       </c>
       <c r="L421" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001022#50|60416#1|6000124#1980</t>
+          <t>16#2218|87#49|6001022#50|60416#1|6000124#1980</t>
         </is>
       </c>
       <c r="M421" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#39|6001022#50|60416#1</t>
+          <t>16#2218|87#49|6001022#50|60416#1</t>
         </is>
       </c>
       <c r="Q421" s="0" t="n">
@@ -35954,12 +35954,12 @@
       </c>
       <c r="L422" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000025#50|60408#1|6000124#3280</t>
+          <t>16#3674|87#88|6000025#50|60408#1|6000124#3280</t>
         </is>
       </c>
       <c r="M422" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6000025#50|60408#1</t>
+          <t>16#3674|87#88|6000025#50|60408#1</t>
         </is>
       </c>
       <c r="Q422" s="0" t="n">
@@ -36043,12 +36043,12 @@
       </c>
       <c r="L423" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|6000110#1500|6000124#980</t>
+          <t>16#1127|87#20|20#2|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M423" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#15|20#2|6000110#1500</t>
+          <t>16#1127|87#20|20#2|6000110#1500</t>
         </is>
       </c>
       <c r="Q423" s="0" t="n">
@@ -36132,12 +36132,12 @@
       </c>
       <c r="L424" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#35|20#4|6000088#1|6000124#1980</t>
+          <t>16#2218|87#45|20#4|6000088#1|6000124#1980</t>
         </is>
       </c>
       <c r="M424" s="0" t="inlineStr">
         <is>
-          <t>16#2218|87#35|20#4|6000088#1</t>
+          <t>16#2218|87#45|20#4|6000088#1</t>
         </is>
       </c>
       <c r="Q424" s="0" t="n">
@@ -36221,12 +36221,12 @@
       </c>
       <c r="L425" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6001026#50|6000110#7500|6000124#3280</t>
+          <t>16#3674|87#88|6001026#50|6000110#7500|6000124#3280</t>
         </is>
       </c>
       <c r="M425" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|6001026#50|6000110#7500</t>
+          <t>16#3674|87#88|6001026#50|6000110#7500</t>
         </is>
       </c>
       <c r="Q425" s="0" t="n">
@@ -36310,12 +36310,12 @@
       </c>
       <c r="L426" s="0" t="inlineStr">
         <is>
-          <t>16#5612|87#112|6000073#50|6000089#1|6000124#4880</t>
+          <t>16#5612|87#141|6000073#50|6000089#1|6000124#4880</t>
         </is>
       </c>
       <c r="M426" s="0" t="inlineStr">
         <is>
-          <t>16#5612|87#112|6000073#50|6000089#1</t>
+          <t>16#5612|87#141|6000073#50|6000089#1</t>
         </is>
       </c>
       <c r="Q426" s="0" t="n">
@@ -36399,12 +36399,12 @@
       </c>
       <c r="L427" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5|6000124#300</t>
+          <t>16#360|1004#5|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M427" s="0" t="inlineStr">
         <is>
-          <t>16#360|1004#5|19#5</t>
+          <t>16#360|1004#5|19#6</t>
         </is>
       </c>
       <c r="Q427" s="0" t="n">
@@ -36491,12 +36491,12 @@
       </c>
       <c r="L428" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11|6000124#680</t>
+          <t>16#816|1004#11|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M428" s="0" t="inlineStr">
         <is>
-          <t>16#816|1004#11|19#11</t>
+          <t>16#816|1004#11|19#14</t>
         </is>
       </c>
       <c r="Q428" s="0" t="n">
@@ -36583,12 +36583,12 @@
       </c>
       <c r="L429" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24|6000124#1280</t>
+          <t>16#1472|1004#24|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M429" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1004#24|20#24</t>
+          <t>16#1472|1004#24|20#30</t>
         </is>
       </c>
       <c r="Q429" s="0" t="n">
@@ -36675,12 +36675,12 @@
       </c>
       <c r="L430" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M430" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1004#36|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|1004#36|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q430" s="0" t="n">
@@ -36767,12 +36767,12 @@
       </c>
       <c r="L431" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5|6000124#300</t>
+          <t>16#360|50002#10|19#6|6000124#300</t>
         </is>
       </c>
       <c r="M431" s="0" t="inlineStr">
         <is>
-          <t>16#360|50002#10|19#5</t>
+          <t>16#360|50002#10|19#6</t>
         </is>
       </c>
       <c r="Q431" s="0" t="n">
@@ -36859,12 +36859,12 @@
       </c>
       <c r="L432" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11|6000124#680</t>
+          <t>16#816|50002#25|19#14|6000124#680</t>
         </is>
       </c>
       <c r="M432" s="0" t="inlineStr">
         <is>
-          <t>16#816|50002#25|19#11</t>
+          <t>16#816|50002#25|19#14</t>
         </is>
       </c>
       <c r="Q432" s="0" t="n">
@@ -36951,12 +36951,12 @@
       </c>
       <c r="L433" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24|6000124#1280</t>
+          <t>16#1472|50002#50|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M433" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50002#50|20#24</t>
+          <t>16#1472|50002#50|20#30</t>
         </is>
       </c>
       <c r="Q433" s="0" t="n">
@@ -37043,12 +37043,12 @@
       </c>
       <c r="L434" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M434" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#100|60403#3|6000110#2500|19#70</t>
+          <t>16#3674|50002#100|60403#3|6000110#2500|19#88</t>
         </is>
       </c>
       <c r="Q434" s="0" t="n">
@@ -37135,12 +37135,12 @@
       </c>
       <c r="L435" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#1|6000124#680</t>
+          <t>16#816|50007#13|20#1|60430#1|6000124#680</t>
         </is>
       </c>
       <c r="M435" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#1</t>
+          <t>16#816|50007#13|20#1|60430#1</t>
         </is>
       </c>
       <c r="Q435" s="0" t="n">
@@ -37224,12 +37224,12 @@
       </c>
       <c r="L436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#12|19#10|60430#3|6000124#980</t>
+          <t>16#1127|50007#18|19#10|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#12|19#10|60430#3</t>
+          <t>16#1127|50007#18|19#10|60430#3</t>
         </is>
       </c>
       <c r="Q436" s="0" t="n">
@@ -37313,12 +37313,12 @@
       </c>
       <c r="L437" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#34|20#5|60431#2|6000124#1980</t>
+          <t>16#2218|50007#44|20#5|60431#2|6000124#1980</t>
         </is>
       </c>
       <c r="M437" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#34|20#5|60431#2</t>
+          <t>16#2218|50007#44|20#5|60431#2</t>
         </is>
       </c>
       <c r="Q437" s="0" t="n">
@@ -37402,12 +37402,12 @@
       </c>
       <c r="L438" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#62|20#8|60415#2|6000124#3280</t>
+          <t>16#3674|50007#80|20#8|60415#2|6000124#3280</t>
         </is>
       </c>
       <c r="M438" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#62|20#8|60415#2</t>
+          <t>16#3674|50007#80|20#8|60415#2</t>
         </is>
       </c>
       <c r="Q438" s="0" t="n">
@@ -37491,12 +37491,12 @@
       </c>
       <c r="L439" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50007#155|60431#5|72001#1000|6000124#6480</t>
+          <t>16#7452|50007#195|60431#5|72001#1000|6000124#6480</t>
         </is>
       </c>
       <c r="M439" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50007#155|60431#5|72001#1000</t>
+          <t>16#7452|50007#195|60431#5|72001#1000</t>
         </is>
       </c>
       <c r="Q439" s="0" t="n">
@@ -37580,12 +37580,12 @@
       </c>
       <c r="L440" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#5|19#65|6000124#3280</t>
+          <t>16#3674|67#800|20#5|19#83|6000124#3280</t>
         </is>
       </c>
       <c r="M440" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#5|19#65</t>
+          <t>16#3674|67#800|20#5|19#83</t>
         </is>
       </c>
       <c r="Q440" s="0" t="n">
@@ -37669,12 +37669,12 @@
       </c>
       <c r="L441" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#10|19#145|6000124#6480</t>
+          <t>16#7452|67#1500|20#10|19#185|6000124#6480</t>
         </is>
       </c>
       <c r="M441" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#10|19#145</t>
+          <t>16#7452|67#1500|20#10|19#185</t>
         </is>
       </c>
       <c r="Q441" s="0" t="n">
@@ -37758,12 +37758,12 @@
       </c>
       <c r="L442" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#11|60403#1|6000110#1000|6000124#680</t>
+          <t>16#816|50007#14|60403#1|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M442" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#11|60403#1|6000110#1000</t>
+          <t>16#816|50007#14|60403#1|6000110#1000</t>
         </is>
       </c>
       <c r="Q442" s="0" t="n">
@@ -37847,12 +37847,12 @@
       </c>
       <c r="L443" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|6000110#1500|6000124#980</t>
+          <t>16#1127|50007#22|60402#2|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M443" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|6000110#1500</t>
+          <t>16#1127|50007#22|60402#2|6000110#1500</t>
         </is>
       </c>
       <c r="Q443" s="0" t="n">
@@ -37936,12 +37936,12 @@
       </c>
       <c r="L444" s="0" t="inlineStr">
         <is>
-          <t>16#1980|50007#21|60403#3|6000110#2000|6000124#1980</t>
+          <t>16#1980|50007#27|60403#3|6000110#2000|6000124#1980</t>
         </is>
       </c>
       <c r="M444" s="0" t="inlineStr">
         <is>
-          <t>16#1980|50007#21|60403#3|6000110#2000</t>
+          <t>16#1980|50007#27|60403#3|6000110#2000</t>
         </is>
       </c>
       <c r="Q444" s="0" t="n">
@@ -38025,12 +38025,12 @@
       </c>
       <c r="L445" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20|6000124#3280</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20|6000124#3280</t>
         </is>
       </c>
       <c r="M445" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20</t>
         </is>
       </c>
       <c r="Q445" s="0" t="n">
@@ -38114,12 +38114,12 @@
       </c>
       <c r="L446" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50007#155|60433#1|72001#1000|6000124#6480</t>
+          <t>16#7452|50007#195|60433#1|72001#1000|6000124#6480</t>
         </is>
       </c>
       <c r="M446" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50007#155|60433#1|72001#1000</t>
+          <t>16#7452|50007#195|60433#1|72001#1000</t>
         </is>
       </c>
       <c r="Q446" s="0" t="n">
@@ -38203,12 +38203,12 @@
       </c>
       <c r="L447" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1002#20|20#24|6000110#2000|6000124#1280</t>
+          <t>16#1472|1002#20|20#30|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M447" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1002#20|20#24|6000110#2000</t>
+          <t>16#1472|1002#20|20#30|6000110#2000</t>
         </is>
       </c>
       <c r="Q447" s="0" t="n">
@@ -38292,12 +38292,12 @@
       </c>
       <c r="L448" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|60415#1|6000110#3000|6000124#1980|19#39</t>
+          <t>16#2218|1002#30|60415#1|6000110#3000|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M448" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|60415#1|6000110#3000|19#39</t>
+          <t>16#2218|1002#30|60415#1|6000110#3000|19#49</t>
         </is>
       </c>
       <c r="Q448" s="0" t="n">
@@ -38381,12 +38381,12 @@
       </c>
       <c r="L449" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000|6000124#3280</t>
+          <t>16#3674|1002#40|20#88|6000110#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M449" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000</t>
+          <t>16#3674|1002#40|20#88|6000110#5000</t>
         </is>
       </c>
       <c r="Q449" s="0" t="n">
@@ -38470,12 +38470,12 @@
       </c>
       <c r="L450" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000|6000124#680</t>
+          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M450" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000</t>
+          <t>16#816|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q450" s="0" t="n">
@@ -38559,12 +38559,12 @@
       </c>
       <c r="L451" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500|6000124#980</t>
+          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M451" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500</t>
+          <t>16#1127|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q451" s="0" t="n">
@@ -38648,12 +38648,12 @@
       </c>
       <c r="L452" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M452" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000</t>
+          <t>16#1472|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q452" s="0" t="n">
@@ -38737,12 +38737,12 @@
       </c>
       <c r="L453" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1|6000124#3280</t>
+          <t>16#3674|87#88|60403#3|60415#1|6000124#3280</t>
         </is>
       </c>
       <c r="M453" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1</t>
+          <t>16#3674|87#88|60403#3|60415#1</t>
         </is>
       </c>
       <c r="Q453" s="0" t="n">
@@ -38826,12 +38826,12 @@
       </c>
       <c r="L454" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6|6000124#6480</t>
+          <t>16#7452|87#195|60403#6|60402#6|6000124#6480</t>
         </is>
       </c>
       <c r="M454" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6</t>
+          <t>16#7452|87#195|60403#6|60402#6</t>
         </is>
       </c>
       <c r="Q454" s="0" t="n">
@@ -38915,12 +38915,12 @@
       </c>
       <c r="L455" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#70|17011#50|6000124#3280</t>
+          <t>16#3674|50002#50|20#88|17011#50|6000124#3280</t>
         </is>
       </c>
       <c r="M455" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#70|17011#50</t>
+          <t>16#3674|50002#50|20#88|17011#50</t>
         </is>
       </c>
       <c r="Q455" s="0" t="n">
@@ -39004,12 +39004,12 @@
       </c>
       <c r="L456" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#155|17012#50|6000124#6480</t>
+          <t>16#7452|50002#80|20#195|17012#50|6000124#6480</t>
         </is>
       </c>
       <c r="M456" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#155|17012#50</t>
+          <t>16#7452|50002#80|20#195|17012#50</t>
         </is>
       </c>
       <c r="Q456" s="0" t="n">
@@ -39093,12 +39093,12 @@
       </c>
       <c r="L457" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000|6000124#680</t>
+          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M457" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000</t>
+          <t>16#816|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q457" s="0" t="n">
@@ -39182,12 +39182,12 @@
       </c>
       <c r="L458" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500|6000124#980</t>
+          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M458" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500</t>
+          <t>16#1127|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q458" s="0" t="n">
@@ -39271,12 +39271,12 @@
       </c>
       <c r="L459" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M459" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000</t>
+          <t>16#1472|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q459" s="0" t="n">
@@ -39360,12 +39360,12 @@
       </c>
       <c r="L460" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1|6000124#3280</t>
+          <t>16#3674|87#88|60403#3|60415#1|6000124#3280</t>
         </is>
       </c>
       <c r="M460" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1</t>
+          <t>16#3674|87#88|60403#3|60415#1</t>
         </is>
       </c>
       <c r="Q460" s="0" t="n">
@@ -39449,12 +39449,12 @@
       </c>
       <c r="L461" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6|6000124#6480</t>
+          <t>16#7452|87#195|60403#6|60402#6|6000124#6480</t>
         </is>
       </c>
       <c r="M461" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6</t>
+          <t>16#7452|87#195|60403#6|60402#6</t>
         </is>
       </c>
       <c r="Q461" s="0" t="n">
@@ -39538,12 +39538,12 @@
       </c>
       <c r="L462" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|20#39|6000110#3000|6000124#1980</t>
+          <t>16#2218|1002#30|20#49|6000110#3000|6000124#1980</t>
         </is>
       </c>
       <c r="M462" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|20#39|6000110#3000</t>
+          <t>16#2218|1002#30|20#49|6000110#3000</t>
         </is>
       </c>
       <c r="Q462" s="0" t="n">
@@ -39627,12 +39627,12 @@
       </c>
       <c r="L463" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000|6000124#3280</t>
+          <t>16#3674|1002#40|20#88|6000110#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M463" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000</t>
+          <t>16#3674|1002#40|20#88|6000110#5000</t>
         </is>
       </c>
       <c r="Q463" s="0" t="n">
@@ -39716,12 +39716,12 @@
       </c>
       <c r="L464" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M464" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1</t>
+          <t>16#360|50007#5|19#7|60430#1</t>
         </is>
       </c>
       <c r="Q464" s="0" t="n">
@@ -39805,12 +39805,12 @@
       </c>
       <c r="L465" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2|6000124#680</t>
+          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M465" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2</t>
+          <t>16#816|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q465" s="0" t="n">
@@ -39894,12 +39894,12 @@
       </c>
       <c r="L466" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3|6000124#980</t>
+          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M466" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3</t>
+          <t>16#1127|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q466" s="0" t="n">
@@ -39983,12 +39983,12 @@
       </c>
       <c r="L467" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2|6000124#1980</t>
+          <t>16#2218|50007#49|60403#3|60431#2|6000124#1980</t>
         </is>
       </c>
       <c r="M467" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2</t>
+          <t>16#2218|50007#49|60403#3|60431#2</t>
         </is>
       </c>
       <c r="Q467" s="0" t="n">
@@ -40072,12 +40072,12 @@
       </c>
       <c r="L468" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20|6000124#3280</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20|6000124#3280</t>
         </is>
       </c>
       <c r="M468" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20</t>
         </is>
       </c>
       <c r="Q468" s="0" t="n">
@@ -40161,12 +40161,12 @@
       </c>
       <c r="L469" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|17012#40|6000124#3280</t>
+          <t>16#3674|1002#40|20#88|17012#40|6000124#3280</t>
         </is>
       </c>
       <c r="M469" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|17012#40</t>
+          <t>16#3674|1002#40|20#88|17012#40</t>
         </is>
       </c>
       <c r="Q469" s="0" t="n">
@@ -40250,12 +40250,12 @@
       </c>
       <c r="L470" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000|6000124#680</t>
+          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M470" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000</t>
+          <t>16#816|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q470" s="0" t="n">
@@ -40339,12 +40339,12 @@
       </c>
       <c r="L471" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500|6000124#980</t>
+          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M471" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500</t>
+          <t>16#1127|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q471" s="0" t="n">
@@ -40428,12 +40428,12 @@
       </c>
       <c r="L472" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M472" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000</t>
+          <t>16#1472|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q472" s="0" t="n">
@@ -40517,12 +40517,12 @@
       </c>
       <c r="L473" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1|6000124#3280</t>
+          <t>16#3674|87#88|60403#3|60415#1|6000124#3280</t>
         </is>
       </c>
       <c r="M473" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1</t>
+          <t>16#3674|87#88|60403#3|60415#1</t>
         </is>
       </c>
       <c r="Q473" s="0" t="n">
@@ -40606,12 +40606,12 @@
       </c>
       <c r="L474" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6|6000124#6480</t>
+          <t>16#7452|87#195|60403#6|60402#6|6000124#6480</t>
         </is>
       </c>
       <c r="M474" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6</t>
+          <t>16#7452|87#195|60403#6|60402#6</t>
         </is>
       </c>
       <c r="Q474" s="0" t="n">
@@ -40695,12 +40695,12 @@
       </c>
       <c r="L475" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#70|60412#3|6000124#3280</t>
+          <t>16#3674|50002#50|20#88|60412#3|6000124#3280</t>
         </is>
       </c>
       <c r="M475" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#70|60412#3</t>
+          <t>16#3674|50002#50|20#88|60412#3</t>
         </is>
       </c>
       <c r="Q475" s="0" t="n">
@@ -40784,12 +40784,12 @@
       </c>
       <c r="L476" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#155|60412#8|6000124#6480</t>
+          <t>16#7452|50002#80|20#195|60412#8|6000124#6480</t>
         </is>
       </c>
       <c r="M476" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#155|60412#8</t>
+          <t>16#7452|50002#80|20#195|60412#8</t>
         </is>
       </c>
       <c r="Q476" s="0" t="n">
@@ -40873,12 +40873,12 @@
       </c>
       <c r="L477" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M477" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1</t>
+          <t>16#360|50007#5|19#7|60430#1</t>
         </is>
       </c>
       <c r="Q477" s="0" t="n">
@@ -40962,12 +40962,12 @@
       </c>
       <c r="L478" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2|6000124#680</t>
+          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M478" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2</t>
+          <t>16#816|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q478" s="0" t="n">
@@ -41051,12 +41051,12 @@
       </c>
       <c r="L479" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3|6000124#980</t>
+          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M479" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3</t>
+          <t>16#1127|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q479" s="0" t="n">
@@ -41140,12 +41140,12 @@
       </c>
       <c r="L480" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2|6000124#1980</t>
+          <t>16#2218|50007#49|60403#3|60431#2|6000124#1980</t>
         </is>
       </c>
       <c r="M480" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2</t>
+          <t>16#2218|50007#49|60403#3|60431#2</t>
         </is>
       </c>
       <c r="Q480" s="0" t="n">
@@ -41229,12 +41229,12 @@
       </c>
       <c r="L481" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20|6000124#3280</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20|6000124#3280</t>
         </is>
       </c>
       <c r="M481" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20</t>
         </is>
       </c>
       <c r="Q481" s="0" t="n">
@@ -41318,12 +41318,12 @@
       </c>
       <c r="L482" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#5|19#65|6000124#3280</t>
+          <t>16#3674|67#800|20#5|19#83|6000124#3280</t>
         </is>
       </c>
       <c r="M482" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#5|19#65</t>
+          <t>16#3674|67#800|20#5|19#83</t>
         </is>
       </c>
       <c r="Q482" s="0" t="n">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="L483" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#10|19#145|6000124#6480</t>
+          <t>16#7452|67#1500|20#10|19#185|6000124#6480</t>
         </is>
       </c>
       <c r="M483" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#10|19#145</t>
+          <t>16#7452|67#1500|20#10|19#185</t>
         </is>
       </c>
       <c r="Q483" s="0" t="n">
@@ -41496,12 +41496,12 @@
       </c>
       <c r="L484" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000|6000124#680</t>
+          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M484" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000</t>
+          <t>16#816|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q484" s="0" t="n">
@@ -41585,12 +41585,12 @@
       </c>
       <c r="L485" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500|6000124#980</t>
+          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M485" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500</t>
+          <t>16#1127|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q485" s="0" t="n">
@@ -41674,12 +41674,12 @@
       </c>
       <c r="L486" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M486" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000</t>
+          <t>16#1472|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q486" s="0" t="n">
@@ -41763,12 +41763,12 @@
       </c>
       <c r="L487" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1|6000124#3280</t>
+          <t>16#3674|87#88|60403#3|60415#1|6000124#3280</t>
         </is>
       </c>
       <c r="M487" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1</t>
+          <t>16#3674|87#88|60403#3|60415#1</t>
         </is>
       </c>
       <c r="Q487" s="0" t="n">
@@ -41852,12 +41852,12 @@
       </c>
       <c r="L488" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6|6000124#6480</t>
+          <t>16#7452|87#195|60403#6|60402#6|6000124#6480</t>
         </is>
       </c>
       <c r="M488" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6</t>
+          <t>16#7452|87#195|60403#6|60402#6</t>
         </is>
       </c>
       <c r="Q488" s="0" t="n">
@@ -41941,12 +41941,12 @@
       </c>
       <c r="L489" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|20#39|6000110#3000|6000124#1980</t>
+          <t>16#2218|1002#30|20#49|6000110#3000|6000124#1980</t>
         </is>
       </c>
       <c r="M489" s="0" t="inlineStr">
         <is>
-          <t>16#2218|1002#30|20#39|6000110#3000</t>
+          <t>16#2218|1002#30|20#49|6000110#3000</t>
         </is>
       </c>
       <c r="Q489" s="0" t="n">
@@ -42030,12 +42030,12 @@
       </c>
       <c r="L490" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000|6000124#3280</t>
+          <t>16#3674|1002#40|20#88|6000110#5000|6000124#3280</t>
         </is>
       </c>
       <c r="M490" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|6000110#5000</t>
+          <t>16#3674|1002#40|20#88|6000110#5000</t>
         </is>
       </c>
       <c r="Q490" s="0" t="n">
@@ -42119,12 +42119,12 @@
       </c>
       <c r="L491" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M491" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1</t>
+          <t>16#360|50007#5|19#7|60430#1</t>
         </is>
       </c>
       <c r="Q491" s="0" t="n">
@@ -42208,12 +42208,12 @@
       </c>
       <c r="L492" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2|6000124#680</t>
+          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M492" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2</t>
+          <t>16#816|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q492" s="0" t="n">
@@ -42297,12 +42297,12 @@
       </c>
       <c r="L493" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3|6000124#980</t>
+          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M493" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3</t>
+          <t>16#1127|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q493" s="0" t="n">
@@ -42386,12 +42386,12 @@
       </c>
       <c r="L494" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2|6000124#1980</t>
+          <t>16#2218|50007#49|60403#3|60431#2|6000124#1980</t>
         </is>
       </c>
       <c r="M494" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2</t>
+          <t>16#2218|50007#49|60403#3|60431#2</t>
         </is>
       </c>
       <c r="Q494" s="0" t="n">
@@ -42475,12 +42475,12 @@
       </c>
       <c r="L495" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20|6000124#3280</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20|6000124#3280</t>
         </is>
       </c>
       <c r="M495" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20</t>
         </is>
       </c>
       <c r="Q495" s="0" t="n">
@@ -42564,12 +42564,12 @@
       </c>
       <c r="L496" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|17012#40|6000124#3280</t>
+          <t>16#3674|1002#40|20#88|17012#40|6000124#3280</t>
         </is>
       </c>
       <c r="M496" s="0" t="inlineStr">
         <is>
-          <t>16#3674|1002#40|20#70|17012#40</t>
+          <t>16#3674|1002#40|20#88|17012#40</t>
         </is>
       </c>
       <c r="Q496" s="0" t="n">
@@ -42653,12 +42653,12 @@
       </c>
       <c r="L497" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000|6000124#680</t>
+          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M497" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#7|6000110#1000</t>
+          <t>16#816|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q497" s="0" t="n">
@@ -42742,12 +42742,12 @@
       </c>
       <c r="L498" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500|6000124#980</t>
+          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M498" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#11|6000110#1500</t>
+          <t>16#1127|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q498" s="0" t="n">
@@ -42831,12 +42831,12 @@
       </c>
       <c r="L499" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M499" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#24|60403#2|6000110#2000</t>
+          <t>16#1472|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q499" s="0" t="n">
@@ -42920,12 +42920,12 @@
       </c>
       <c r="L500" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1|6000124#3280</t>
+          <t>16#3674|87#88|60403#3|60415#1|6000124#3280</t>
         </is>
       </c>
       <c r="M500" s="0" t="inlineStr">
         <is>
-          <t>16#3674|87#70|60403#3|60415#1</t>
+          <t>16#3674|87#88|60403#3|60415#1</t>
         </is>
       </c>
       <c r="Q500" s="0" t="n">
@@ -43009,12 +43009,12 @@
       </c>
       <c r="L501" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6|6000124#6480</t>
+          <t>16#7452|87#195|60403#6|60402#6|6000124#6480</t>
         </is>
       </c>
       <c r="M501" s="0" t="inlineStr">
         <is>
-          <t>16#7452|87#155|60403#6|60402#6</t>
+          <t>16#7452|87#195|60403#6|60402#6</t>
         </is>
       </c>
       <c r="Q501" s="0" t="n">
@@ -43098,12 +43098,12 @@
       </c>
       <c r="L502" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#5|19#65|6000124#3280</t>
+          <t>16#3674|50002#50|20#5|19#83|6000124#3280</t>
         </is>
       </c>
       <c r="M502" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50002#50|20#5|19#65</t>
+          <t>16#3674|50002#50|20#5|19#83</t>
         </is>
       </c>
       <c r="Q502" s="0" t="n">
@@ -43187,12 +43187,12 @@
       </c>
       <c r="L503" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#10|19#145|6000124#6480</t>
+          <t>16#7452|50002#80|20#10|19#185|6000124#6480</t>
         </is>
       </c>
       <c r="M503" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50002#80|20#10|19#145</t>
+          <t>16#7452|50002#80|20#10|19#185</t>
         </is>
       </c>
       <c r="Q503" s="0" t="n">
@@ -43276,12 +43276,12 @@
       </c>
       <c r="L504" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M504" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#5|60430#1</t>
+          <t>16#360|50007#5|19#7|60430#1</t>
         </is>
       </c>
       <c r="Q504" s="0" t="n">
@@ -43365,12 +43365,12 @@
       </c>
       <c r="L505" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2|6000124#680</t>
+          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M505" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#10|20#1|60430#2</t>
+          <t>16#816|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q505" s="0" t="n">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="L506" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3|6000124#980</t>
+          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M506" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|60402#2|60430#3</t>
+          <t>16#1127|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q506" s="0" t="n">
@@ -43543,12 +43543,12 @@
       </c>
       <c r="L507" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2|6000124#1980</t>
+          <t>16#2218|50007#49|60403#3|60431#2|6000124#1980</t>
         </is>
       </c>
       <c r="M507" s="0" t="inlineStr">
         <is>
-          <t>16#2218|50007#39|60403#3|60431#2</t>
+          <t>16#2218|50007#49|60403#3|60431#2</t>
         </is>
       </c>
       <c r="Q507" s="0" t="n">
@@ -43632,12 +43632,12 @@
       </c>
       <c r="L508" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20|6000124#3280</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20|6000124#3280</t>
         </is>
       </c>
       <c r="M508" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50007#70|6000089#1|6000085#20</t>
+          <t>16#3674|50007#88|6000089#1|6000085#20</t>
         </is>
       </c>
       <c r="Q508" s="0" t="n">
@@ -43721,12 +43721,12 @@
       </c>
       <c r="L509" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#70|60412#3|6000124#3280</t>
+          <t>16#3674|67#800|20#88|60412#3|6000124#3280</t>
         </is>
       </c>
       <c r="M509" s="0" t="inlineStr">
         <is>
-          <t>16#3674|67#800|20#70|60412#3</t>
+          <t>16#3674|67#800|20#88|60412#3</t>
         </is>
       </c>
       <c r="Q509" s="0" t="n">
@@ -43810,12 +43810,12 @@
       </c>
       <c r="L510" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#155|60412#8|6000124#6480</t>
+          <t>16#7452|67#1500|20#195|60412#8|6000124#6480</t>
         </is>
       </c>
       <c r="M510" s="0" t="inlineStr">
         <is>
-          <t>16#7452|67#1500|20#155|60412#8</t>
+          <t>16#7452|67#1500|20#195|60412#8</t>
         </is>
       </c>
       <c r="Q510" s="0" t="n">
@@ -43988,12 +43988,12 @@
       </c>
       <c r="L512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#10|14#1000000|6000124#500</t>
+          <t>16#1000|81113#2|19#13|14#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#10|14#1000000</t>
+          <t>16#1000|81113#2|19#13|14#1000000</t>
         </is>
       </c>
       <c r="Q512" s="0" t="n">
@@ -44077,12 +44077,12 @@
       </c>
       <c r="L513" s="0" t="inlineStr">
         <is>
-          <t>16#6560|6001032#50|20#57|14#1000000|6000124#3280</t>
+          <t>16#6560|6001032#50|20#75|14#1000000|6000124#3280</t>
         </is>
       </c>
       <c r="M513" s="0" t="inlineStr">
         <is>
-          <t>16#6560|6001032#50|20#57|14#1000000</t>
+          <t>16#6560|6001032#50|20#75|14#1000000</t>
         </is>
       </c>
       <c r="Q513" s="0" t="n">
@@ -44255,12 +44255,12 @@
       </c>
       <c r="L515" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#5</t>
+          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M515" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|19#5</t>
+          <t>16#1000|60435#1|6000110#1000|14#1000000|19#7</t>
         </is>
       </c>
       <c r="Q515" s="0" t="n">
@@ -44344,12 +44344,12 @@
       </c>
       <c r="L516" s="0" t="inlineStr">
         <is>
-          <t>16#3960|60436#2|6000110#5000|14#5000000|6000124#1980|19#31</t>
+          <t>16#3960|60436#2|6000110#5000|14#5000000|6000124#1980|19#41</t>
         </is>
       </c>
       <c r="M516" s="0" t="inlineStr">
         <is>
-          <t>16#3960|60436#2|6000110#5000|14#5000000|19#31</t>
+          <t>16#3960|60436#2|6000110#5000|14#5000000|19#41</t>
         </is>
       </c>
       <c r="Q516" s="0" t="n">
@@ -44611,12 +44611,12 @@
       </c>
       <c r="L519" s="0" t="inlineStr">
         <is>
-          <t>16#1000|99005#1|60431#1|14#2000000|6000124#500|19#5</t>
+          <t>16#1000|99005#1|60431#1|14#2000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M519" s="0" t="inlineStr">
         <is>
-          <t>16#1000|99005#1|60431#1|14#2000000|19#5</t>
+          <t>16#1000|99005#1|60431#1|14#2000000|19#7</t>
         </is>
       </c>
       <c r="Q519" s="0" t="n">
@@ -44789,12 +44789,12 @@
       </c>
       <c r="L521" s="0" t="inlineStr">
         <is>
-          <t>16#600|81002#1|19#10|14#1000000|6000124#300</t>
+          <t>16#600|81002#1|19#13|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M521" s="0" t="inlineStr">
         <is>
-          <t>16#600|81002#1|19#10|14#1000000</t>
+          <t>16#600|81002#1|19#13|14#1000000</t>
         </is>
       </c>
       <c r="Q521" s="0" t="n">
@@ -44878,12 +44878,12 @@
       </c>
       <c r="L522" s="0" t="inlineStr">
         <is>
-          <t>16#1360|60458#2|4#2000|3#1000000|6000124#680|19#9</t>
+          <t>16#1360|60458#2|4#2000|3#1000000|6000124#680|19#12</t>
         </is>
       </c>
       <c r="M522" s="0" t="inlineStr">
         <is>
-          <t>16#1360|60458#2|4#2000|3#1000000|19#9</t>
+          <t>16#1360|60458#2|4#2000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q522" s="0" t="n">
@@ -45056,12 +45056,12 @@
       </c>
       <c r="L524" s="0" t="inlineStr">
         <is>
-          <t>16#600|81113#2|19#10|14#1000000|6000124#300</t>
+          <t>16#600|81113#2|19#13|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M524" s="0" t="inlineStr">
         <is>
-          <t>16#600|81113#2|19#10|14#1000000</t>
+          <t>16#600|81113#2|19#13|14#1000000</t>
         </is>
       </c>
       <c r="Q524" s="0" t="n">
@@ -45145,12 +45145,12 @@
       </c>
       <c r="L525" s="0" t="inlineStr">
         <is>
-          <t>16#2560|60417#1|60458#4|4#3000|6000124#1280|19#19</t>
+          <t>16#2560|60417#1|60458#4|4#3000|6000124#1280|19#25</t>
         </is>
       </c>
       <c r="M525" s="0" t="inlineStr">
         <is>
-          <t>16#2560|60417#1|60458#4|4#3000|19#19</t>
+          <t>16#2560|60417#1|60458#4|4#3000|19#25</t>
         </is>
       </c>
       <c r="Q525" s="0" t="n">
@@ -45323,12 +45323,12 @@
       </c>
       <c r="L527" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#5</t>
+          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M527" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|19#5</t>
+          <t>16#1000|60415#1|61#2|60431#1|19#7</t>
         </is>
       </c>
       <c r="Q527" s="0" t="n">
@@ -45412,12 +45412,12 @@
       </c>
       <c r="L528" s="0" t="inlineStr">
         <is>
-          <t>16#6560|6000089#1|6000110#15000|14#1000000|6000124#3280|19#57</t>
+          <t>16#6560|6000089#1|6000110#15000|14#1000000|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M528" s="0" t="inlineStr">
         <is>
-          <t>16#6560|6000089#1|6000110#15000|14#1000000|19#57</t>
+          <t>16#6560|6000089#1|6000110#15000|14#1000000|19#75</t>
         </is>
       </c>
       <c r="Q528" s="0" t="n">
@@ -45590,12 +45590,12 @@
       </c>
       <c r="L530" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#5</t>
+          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M530" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|19#5</t>
+          <t>16#1000|60435#1|6000110#1000|14#1000000|19#7</t>
         </is>
       </c>
       <c r="Q530" s="0" t="n">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="L531" s="0" t="inlineStr">
         <is>
-          <t>16#2560|60436#2|6000110#3000|3#1000000|6000124#1280|19#19</t>
+          <t>16#2560|60436#2|6000110#3000|3#1000000|6000124#1280|19#25</t>
         </is>
       </c>
       <c r="M531" s="0" t="inlineStr">
         <is>
-          <t>16#2560|60436#2|6000110#3000|3#1000000|19#19</t>
+          <t>16#2560|60436#2|6000110#3000|3#1000000|19#25</t>
         </is>
       </c>
       <c r="Q531" s="0" t="n">
@@ -45852,12 +45852,12 @@
       </c>
       <c r="L533" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#5</t>
+          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M533" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|19#5</t>
+          <t>16#1000|60415#1|61#2|60431#1|19#7</t>
         </is>
       </c>
       <c r="Q533" s="0" t="n">
@@ -45936,12 +45936,12 @@
       </c>
       <c r="L534" s="0" t="inlineStr">
         <is>
-          <t>16#6560|60459#1|4#10000|14#10000000|6000124#3280|19#57</t>
+          <t>16#6560|60459#1|4#10000|14#10000000|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M534" s="0" t="inlineStr">
         <is>
-          <t>16#6560|60459#1|4#10000|14#10000000|19#57</t>
+          <t>16#6560|60459#1|4#10000|14#10000000|19#75</t>
         </is>
       </c>
       <c r="Q534" s="0" t="n">
@@ -46198,12 +46198,12 @@
       </c>
       <c r="L537" s="0" t="inlineStr">
         <is>
-          <t>16#600|50007#5|19#5|14#1000000|6000124#300</t>
+          <t>16#600|50007#5|19#8|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M537" s="0" t="inlineStr">
         <is>
-          <t>16#600|50007#5|19#5|14#1000000</t>
+          <t>16#600|50007#5|19#8|14#1000000</t>
         </is>
       </c>
       <c r="Q537" s="0" t="n">
@@ -46465,12 +46465,12 @@
       </c>
       <c r="L540" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M540" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q540" s="0" t="n">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="L543" s="0" t="inlineStr">
         <is>
-          <t>16#360|67#200|20#4|6000124#300</t>
+          <t>16#360|67#200|20#5|6000124#300</t>
         </is>
       </c>
       <c r="M543" s="0" t="inlineStr">
         <is>
-          <t>16#360|67#200|20#4</t>
+          <t>16#360|67#200|20#5</t>
         </is>
       </c>
       <c r="Q543" s="0" t="n">
@@ -46999,12 +46999,12 @@
       </c>
       <c r="L546" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000|6000124#300</t>
+          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M546" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000</t>
+          <t>16#600|87#5|19#8|14#1000000</t>
         </is>
       </c>
       <c r="Q546" s="0" t="n">
@@ -47266,12 +47266,12 @@
       </c>
       <c r="L549" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#5|14#1000000|6000124#300</t>
+          <t>16#600|50005#5|50007#7|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M549" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#5|14#1000000</t>
+          <t>16#600|50005#5|50007#7|14#1000000</t>
         </is>
       </c>
       <c r="Q549" s="0" t="n">
@@ -47533,12 +47533,12 @@
       </c>
       <c r="L552" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000|6000124#300</t>
+          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M552" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000</t>
+          <t>16#600|87#5|19#8|14#1000000</t>
         </is>
       </c>
       <c r="Q552" s="0" t="n">
@@ -47800,12 +47800,12 @@
       </c>
       <c r="L555" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M555" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q555" s="0" t="n">
@@ -48067,12 +48067,12 @@
       </c>
       <c r="L558" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000|6000124#300</t>
+          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M558" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000</t>
+          <t>16#600|87#5|19#8|14#1000000</t>
         </is>
       </c>
       <c r="Q558" s="0" t="n">
@@ -48334,12 +48334,12 @@
       </c>
       <c r="L561" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#5|14#1000000|6000124#300</t>
+          <t>16#600|50005#5|50007#7|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M561" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#5|14#1000000</t>
+          <t>16#600|50005#5|50007#7|14#1000000</t>
         </is>
       </c>
       <c r="Q561" s="0" t="n">
@@ -48601,12 +48601,12 @@
       </c>
       <c r="L564" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000|6000124#300</t>
+          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M564" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#5|14#1000000</t>
+          <t>16#600|87#5|19#8|14#1000000</t>
         </is>
       </c>
       <c r="Q564" s="0" t="n">
@@ -48868,12 +48868,12 @@
       </c>
       <c r="L567" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M567" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#3</t>
+          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q567" s="0" t="n">
@@ -48957,12 +48957,12 @@
       </c>
       <c r="L568" s="0" t="inlineStr">
         <is>
-          <t>16#360|4#1000|14#2000000|3#1000000|6000124#300|19#4</t>
+          <t>16#360|4#1000|14#2000000|3#1000000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M568" s="0" t="inlineStr">
         <is>
-          <t>16#360|4#1000|14#2000000|3#1000000|19#4</t>
+          <t>16#360|4#1000|14#2000000|3#1000000|19#5</t>
         </is>
       </c>
       <c r="Q568" s="0" t="n">
@@ -49046,12 +49046,12 @@
       </c>
       <c r="L569" s="0" t="inlineStr">
         <is>
-          <t>16#360|99005#1|14#1000000|3#500000|6000124#300|19#4</t>
+          <t>16#360|99005#1|14#1000000|3#500000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M569" s="0" t="inlineStr">
         <is>
-          <t>16#360|99005#1|14#1000000|3#500000|19#4</t>
+          <t>16#360|99005#1|14#1000000|3#500000|19#5</t>
         </is>
       </c>
       <c r="Q569" s="0" t="n">
@@ -49135,12 +49135,12 @@
       </c>
       <c r="L570" s="0" t="inlineStr">
         <is>
-          <t>16#720|99008#1|14#2000000|3#1000000|6000124#600|19#9</t>
+          <t>16#720|99008#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M570" s="0" t="inlineStr">
         <is>
-          <t>16#720|99008#1|14#2000000|3#1000000|19#9</t>
+          <t>16#720|99008#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q570" s="0" t="n">
@@ -49224,12 +49224,12 @@
       </c>
       <c r="L571" s="0" t="inlineStr">
         <is>
-          <t>16#816|4#1200|6000110#1500|72001#120|6000124#680|19#12</t>
+          <t>16#816|4#1200|6000110#1500|72001#120|6000124#680|19#15</t>
         </is>
       </c>
       <c r="M571" s="0" t="inlineStr">
         <is>
-          <t>16#816|4#1200|6000110#1500|72001#120|19#12</t>
+          <t>16#816|4#1200|6000110#1500|72001#120|19#15</t>
         </is>
       </c>
       <c r="Q571" s="0" t="n">
@@ -49313,12 +49313,12 @@
       </c>
       <c r="L572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280|19#26</t>
+          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|19#26</t>
+          <t>16#1619|72005#40|72004#150|72001#300|19#33</t>
         </is>
       </c>
       <c r="Q572" s="0" t="n">
@@ -49402,12 +49402,12 @@
       </c>
       <c r="L573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280|19#26</t>
+          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|19#26</t>
+          <t>16#1619|60403#2|60402#10|72001#300|19#33</t>
         </is>
       </c>
       <c r="Q573" s="0" t="n">
@@ -49491,12 +49491,12 @@
       </c>
       <c r="L574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980|19#42</t>
+          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|19#42</t>
+          <t>16#2624|72005#60|72004#275|72001#450|19#53</t>
         </is>
       </c>
       <c r="Q574" s="0" t="n">
@@ -49580,12 +49580,12 @@
       </c>
       <c r="L575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980|19#42</t>
+          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|19#42</t>
+          <t>16#2624|60403#4|60402#15|72001#450|19#53</t>
         </is>
       </c>
       <c r="Q575" s="0" t="n">
@@ -49669,12 +49669,12 @@
       </c>
       <c r="L576" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|72005#80|72004#400|6000124#3280|19#75</t>
+          <t>16#4592|60417#1|72005#80|72004#400|6000124#3280|19#95</t>
         </is>
       </c>
       <c r="M576" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|72005#80|72004#400|19#75</t>
+          <t>16#4592|60417#1|72005#80|72004#400|19#95</t>
         </is>
       </c>
       <c r="Q576" s="0" t="n">
@@ -49758,12 +49758,12 @@
       </c>
       <c r="L577" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|60403#6|60402#20|6000124#3280|19#75</t>
+          <t>16#4592|60417#1|60403#6|60402#20|6000124#3280|19#95</t>
         </is>
       </c>
       <c r="M577" s="0" t="inlineStr">
         <is>
-          <t>16#4592|60417#1|60403#6|60402#20|19#75</t>
+          <t>16#4592|60417#1|60403#6|60402#20|19#95</t>
         </is>
       </c>
       <c r="Q577" s="0" t="n">
@@ -49847,12 +49847,12 @@
       </c>
       <c r="L578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480|19#168</t>
+          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480|19#212</t>
         </is>
       </c>
       <c r="M578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|19#168</t>
+          <t>16#9558|60403#18|60402#18|4#10000|19#212</t>
         </is>
       </c>
       <c r="Q578" s="0" t="n">
@@ -49936,12 +49936,12 @@
       </c>
       <c r="L579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480|19#168</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480|19#212</t>
         </is>
       </c>
       <c r="M579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|19#168</t>
+          <t>16#9558|60403#18|60402#18|6000110#10000|19#212</t>
         </is>
       </c>
       <c r="Q579" s="0" t="n">
@@ -50025,12 +50025,12 @@
       </c>
       <c r="L580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480|19#171</t>
+          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480|19#216</t>
         </is>
       </c>
       <c r="M580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|19#171</t>
+          <t>16#9720|60403#18|60402#18|4#10000|19#216</t>
         </is>
       </c>
       <c r="Q580" s="0" t="n">
@@ -50114,12 +50114,12 @@
       </c>
       <c r="L581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480|19#175</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480|19#221</t>
         </is>
       </c>
       <c r="M581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|19#175</t>
+          <t>16#9882|60403#18|60402#18|6000110#20000|19#221</t>
         </is>
       </c>
       <c r="Q581" s="0" t="n">
@@ -50203,12 +50203,12 @@
       </c>
       <c r="L582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480|19#178</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480|19#225</t>
         </is>
       </c>
       <c r="M582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|19#178</t>
+          <t>16#10044|60403#18|60402#18|6000110#30000|19#225</t>
         </is>
       </c>
       <c r="Q582" s="0" t="n">
@@ -50292,12 +50292,12 @@
       </c>
       <c r="L583" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#15|72004#60|19#13|6000124#980</t>
+          <t>16#1960|72005#15|72004#60|19#18|6000124#980</t>
         </is>
       </c>
       <c r="M583" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#15|72004#60|19#13</t>
+          <t>16#1960|72005#15|72004#60|19#18</t>
         </is>
       </c>
       <c r="Q583" s="0" t="n">
@@ -50381,12 +50381,12 @@
       </c>
       <c r="L584" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#30|72004#120|19#20|6000124#980</t>
+          <t>16#1960|72005#30|72004#120|19#26|6000124#980</t>
         </is>
       </c>
       <c r="M584" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#30|72004#120|19#20</t>
+          <t>16#1960|72005#30|72004#120|19#26</t>
         </is>
       </c>
       <c r="Q584" s="0" t="n">
@@ -50470,12 +50470,12 @@
       </c>
       <c r="L585" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72001#1000|72003#5|19#20|6000124#980</t>
+          <t>16#1960|72001#1000|72003#5|19#26|6000124#980</t>
         </is>
       </c>
       <c r="M585" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72001#1000|72003#5|19#20</t>
+          <t>16#1960|72001#1000|72003#5|19#26</t>
         </is>
       </c>
       <c r="Q585" s="0" t="n">
@@ -50559,12 +50559,12 @@
       </c>
       <c r="L586" s="0" t="inlineStr">
         <is>
-          <t>16#2475|17012#100|17011#300|19#38|6000124#1980</t>
+          <t>16#2475|17012#100|17011#300|19#48|6000124#1980</t>
         </is>
       </c>
       <c r="M586" s="0" t="inlineStr">
         <is>
-          <t>16#2475|17012#100|17011#300|19#38</t>
+          <t>16#2475|17012#100|17011#300|19#48</t>
         </is>
       </c>
       <c r="Q586" s="0" t="n">
@@ -50648,12 +50648,12 @@
       </c>
       <c r="L587" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000097#10|6000098#20|6000095#20|6000124#680|19#11</t>
+          <t>16#816|6000097#10|6000098#20|6000095#20|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M587" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000097#10|6000098#20|6000095#20|19#11</t>
+          <t>16#816|6000097#10|6000098#20|6000095#20|19#14</t>
         </is>
       </c>
       <c r="Q587" s="0" t="n">
@@ -50737,12 +50737,12 @@
       </c>
       <c r="L588" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000092#10000|6000094#10|14#10000000|6000124#980|19#13</t>
+          <t>16#1960|6000092#10000|6000094#10|14#10000000|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M588" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000092#10000|6000094#10|14#10000000|19#13</t>
+          <t>16#1960|6000092#10000|6000094#10|14#10000000|19#18</t>
         </is>
       </c>
       <c r="Q588" s="0" t="n">
@@ -50826,12 +50826,12 @@
       </c>
       <c r="L589" s="0" t="inlineStr">
         <is>
-          <t>16#8748|6000097#100|6000098#200|6000095#130|6000124#6480|19#149</t>
+          <t>16#8748|6000097#100|6000098#200|6000095#130|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M589" s="0" t="inlineStr">
         <is>
-          <t>16#8748|6000097#100|6000098#200|6000095#130|19#149</t>
+          <t>16#8748|6000097#100|6000098#200|6000095#130|19#189</t>
         </is>
       </c>
       <c r="Q589" s="0" t="n">
@@ -50915,12 +50915,12 @@
       </c>
       <c r="L590" s="0" t="inlineStr">
         <is>
-          <t>16#1360|6000097#10|6000098#20|6000095#20|6000124#680|19#9</t>
+          <t>16#1360|6000097#10|6000098#20|6000095#20|6000124#680|19#12</t>
         </is>
       </c>
       <c r="M590" s="0" t="inlineStr">
         <is>
-          <t>16#1360|6000097#10|6000098#20|6000095#20|19#9</t>
+          <t>16#1360|6000097#10|6000098#20|6000095#20|19#12</t>
         </is>
       </c>
       <c r="Q590" s="0" t="n">
@@ -51004,12 +51004,12 @@
       </c>
       <c r="L591" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#20|6000098#40|6000095#40|6000124#980|19#13</t>
+          <t>16#1960|6000097#20|6000098#40|6000095#40|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M591" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#20|6000098#40|6000095#40|19#13</t>
+          <t>16#1960|6000097#20|6000098#40|6000095#40|19#18</t>
         </is>
       </c>
       <c r="Q591" s="0" t="n">
@@ -51093,12 +51093,12 @@
       </c>
       <c r="L592" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#20|6000098#40|6000094#10|6000124#980|19#13</t>
+          <t>16#1960|6000097#20|6000098#40|6000094#10|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M592" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#20|6000098#40|6000094#10|19#13</t>
+          <t>16#1960|6000097#20|6000098#40|6000094#10|19#18</t>
         </is>
       </c>
       <c r="Q592" s="0" t="n">
@@ -51182,12 +51182,12 @@
       </c>
       <c r="L593" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#10|6000098#40|6000094#15|6000124#980|19#13</t>
+          <t>16#1960|6000097#10|6000098#40|6000094#15|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M593" s="0" t="inlineStr">
         <is>
-          <t>16#1960|6000097#10|6000098#40|6000094#15|19#13</t>
+          <t>16#1960|6000097#10|6000098#40|6000094#15|19#18</t>
         </is>
       </c>
       <c r="Q593" s="0" t="n">
@@ -51271,12 +51271,12 @@
       </c>
       <c r="L594" s="0" t="inlineStr">
         <is>
-          <t>16#360|10443#30|6000104#10|14#1000000|6000124#300|19#4</t>
+          <t>16#360|10443#30|6000104#10|14#1000000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M594" s="0" t="inlineStr">
         <is>
-          <t>16#360|10443#30|6000104#10|14#1000000|19#4</t>
+          <t>16#360|10443#30|6000104#10|14#1000000|19#5</t>
         </is>
       </c>
       <c r="Q594" s="0" t="n">
@@ -51360,12 +51360,12 @@
       </c>
       <c r="L595" s="0" t="inlineStr">
         <is>
-          <t>16#816|10443#100|6000104#20|14#2000000|6000124#680|19#11</t>
+          <t>16#816|10443#100|6000104#20|14#2000000|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M595" s="0" t="inlineStr">
         <is>
-          <t>16#816|10443#100|6000104#20|14#2000000|19#11</t>
+          <t>16#816|10443#100|6000104#20|14#2000000|19#14</t>
         </is>
       </c>
       <c r="Q595" s="0" t="n">
@@ -51449,12 +51449,12 @@
       </c>
       <c r="L596" s="0" t="inlineStr">
         <is>
-          <t>16#1555|10443#200|6000104#40|14#8000000|6000124#1280|19#23</t>
+          <t>16#1555|10443#200|6000104#40|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M596" s="0" t="inlineStr">
         <is>
-          <t>16#1555|10443#200|6000104#40|14#8000000|19#23</t>
+          <t>16#1555|10443#200|6000104#40|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q596" s="0" t="n">
@@ -51538,12 +51538,12 @@
       </c>
       <c r="L597" s="0" t="inlineStr">
         <is>
-          <t>16#4264|10443#500|6000104#100|14#50000000|6000124#3280|19#67</t>
+          <t>16#4264|10443#500|6000104#100|14#50000000|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M597" s="0" t="inlineStr">
         <is>
-          <t>16#4264|10443#500|6000104#100|14#50000000|19#67</t>
+          <t>16#4264|10443#500|6000104#100|14#50000000|19#85</t>
         </is>
       </c>
       <c r="Q597" s="0" t="n">
@@ -51627,12 +51627,12 @@
       </c>
       <c r="L598" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#20|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000|6000124#300</t>
+          <t>16#600|19#25|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000|6000124#300</t>
         </is>
       </c>
       <c r="M598" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#20|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000</t>
+          <t>16#600|19#25|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000</t>
         </is>
       </c>
       <c r="Q598" s="0" t="n">
@@ -51716,12 +51716,12 @@
       </c>
       <c r="L599" s="0" t="inlineStr">
         <is>
-          <t>16#1360|19#30|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000|6000124#680</t>
+          <t>16#1360|19#38|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000|6000124#680</t>
         </is>
       </c>
       <c r="M599" s="0" t="inlineStr">
         <is>
-          <t>16#1360|19#30|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000</t>
+          <t>16#1360|19#38|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000</t>
         </is>
       </c>
       <c r="Q599" s="0" t="n">
@@ -51805,12 +51805,12 @@
       </c>
       <c r="L600" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#40|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
+          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
         </is>
       </c>
       <c r="M600" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#40|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
+          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q600" s="0" t="n">
@@ -51894,12 +51894,12 @@
       </c>
       <c r="L601" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#40|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
+          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
         </is>
       </c>
       <c r="M601" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#40|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
+          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q601" s="0" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="L602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#50|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2560|19#63|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#50|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2560|19#63|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q602" s="0" t="n">
@@ -52072,12 +52072,12 @@
       </c>
       <c r="L603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#50|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2560|19#63|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#50|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2560|19#63|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q603" s="0" t="n">
@@ -52161,12 +52161,12 @@
       </c>
       <c r="L604" s="0" t="inlineStr">
         <is>
-          <t>16#6560|99000#8|10442#25|10441#150|6000110#5000|61#5|60#36|14#10000000|3#10000000|6000124#3280|19#57</t>
+          <t>16#6560|99000#8|10442#25|10441#150|6000110#5000|61#5|60#36|14#10000000|3#10000000|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M604" s="0" t="inlineStr">
         <is>
-          <t>16#6560|99000#8|10442#25|10441#150|6000110#5000|61#5|60#36|14#10000000|3#10000000|19#57</t>
+          <t>16#6560|99000#8|10442#25|10441#150|6000110#5000|61#5|60#36|14#10000000|3#10000000|19#75</t>
         </is>
       </c>
       <c r="Q604" s="0" t="n">
@@ -52250,12 +52250,12 @@
       </c>
       <c r="L605" s="0" t="inlineStr">
         <is>
-          <t>16#6560|81148#100|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280|19#57</t>
+          <t>16#6560|81148#100|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280|19#75</t>
         </is>
       </c>
       <c r="M605" s="0" t="inlineStr">
         <is>
-          <t>16#6560|81148#100|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|19#57</t>
+          <t>16#6560|81148#100|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|19#75</t>
         </is>
       </c>
       <c r="Q605" s="0" t="n">
@@ -52339,12 +52339,12 @@
       </c>
       <c r="L606" s="0" t="inlineStr">
         <is>
-          <t>16#6560|20#57|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280</t>
+          <t>16#6560|20#75|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280</t>
         </is>
       </c>
       <c r="M606" s="0" t="inlineStr">
         <is>
-          <t>16#6560|20#57|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000</t>
+          <t>16#6560|20#75|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000</t>
         </is>
       </c>
       <c r="Q606" s="0" t="n">
@@ -52428,12 +52428,12 @@
       </c>
       <c r="L607" s="0" t="inlineStr">
         <is>
-          <t>16#6560|20#57|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280</t>
+          <t>16#6560|20#75|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000|6000124#3280</t>
         </is>
       </c>
       <c r="M607" s="0" t="inlineStr">
         <is>
-          <t>16#6560|20#57|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000</t>
+          <t>16#6560|20#75|60412#10|60411#20|6000110#10000|61#5|60#36|14#10000000|3#10000000</t>
         </is>
       </c>
       <c r="Q607" s="0" t="n">
@@ -52517,12 +52517,12 @@
       </c>
       <c r="L608" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000|6000124#300</t>
+          <t>16#360|19#12|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000|6000124#300</t>
         </is>
       </c>
       <c r="M608" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000</t>
+          <t>16#360|19#12|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000</t>
         </is>
       </c>
       <c r="Q608" s="0" t="n">
@@ -52606,12 +52606,12 @@
       </c>
       <c r="L609" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000|6000124#680</t>
+          <t>16#816|19#25|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000|6000124#680</t>
         </is>
       </c>
       <c r="M609" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#20|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000</t>
+          <t>16#816|19#25|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000</t>
         </is>
       </c>
       <c r="Q609" s="0" t="n">
@@ -52695,12 +52695,12 @@
       </c>
       <c r="L610" s="0" t="inlineStr">
         <is>
-          <t>16#1176|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
+          <t>16#1176|19#37|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
         </is>
       </c>
       <c r="M610" s="0" t="inlineStr">
         <is>
-          <t>16#1176|19#30|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
+          <t>16#1176|19#37|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
         </is>
       </c>
       <c r="Q610" s="0" t="n">
@@ -52784,12 +52784,12 @@
       </c>
       <c r="L611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
+          <t>16#1555|20#2|19#50|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#40|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
+          <t>16#1555|20#2|19#50|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
         </is>
       </c>
       <c r="Q611" s="0" t="n">
@@ -52873,12 +52873,12 @@
       </c>
       <c r="L612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
+          <t>16#2475|20#5|19#64|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
         </is>
       </c>
       <c r="M612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#50|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
+          <t>16#2475|20#5|19#64|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
         </is>
       </c>
       <c r="Q612" s="0" t="n">
@@ -52962,12 +52962,12 @@
       </c>
       <c r="L613" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
+          <t>16#4264|20#10|19#103|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
         </is>
       </c>
       <c r="M613" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#80|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
+          <t>16#4264|20#10|19#103|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
         </is>
       </c>
       <c r="Q613" s="0" t="n">
@@ -53051,12 +53051,12 @@
       </c>
       <c r="L614" s="0" t="inlineStr">
         <is>
-          <t>16#720|6001020#50|20#1|19#10|80#10|60#24|23#6|14#5000000|3#1000000|6000124#600</t>
+          <t>16#720|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000|6000124#600</t>
         </is>
       </c>
       <c r="M614" s="0" t="inlineStr">
         <is>
-          <t>16#720|6001020#50|20#1|19#10|80#10|60#24|23#6|14#5000000|3#1000000</t>
+          <t>16#720|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q614" s="0" t="n">
@@ -53140,12 +53140,12 @@
       </c>
       <c r="L615" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|20#67|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000|6000124#3280</t>
+          <t>16#4264|81148#100|20#85|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000|6000124#3280</t>
         </is>
       </c>
       <c r="M615" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|20#67|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000</t>
+          <t>16#4264|81148#100|20#85|4#5000|6000110#5000|61#3|60#36|14#50000000|3#2000000</t>
         </is>
       </c>
       <c r="Q615" s="0" t="n">
@@ -53318,12 +53318,12 @@
       </c>
       <c r="L617" s="0" t="inlineStr">
         <is>
-          <t>16#360|60404#10|60430#5|14#1000000|6000124#300|19#4</t>
+          <t>16#360|60404#10|60430#5|14#1000000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M617" s="0" t="inlineStr">
         <is>
-          <t>16#360|60404#10|60430#5|14#1000000|19#4</t>
+          <t>16#360|60404#10|60430#5|14#1000000|19#5</t>
         </is>
       </c>
       <c r="Q617" s="0" t="n">
@@ -53407,12 +53407,12 @@
       </c>
       <c r="L618" s="0" t="inlineStr">
         <is>
-          <t>16#720|60404#20|60431#5|14#2000000|6000124#600|19#9</t>
+          <t>16#720|60404#20|60431#5|14#2000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M618" s="0" t="inlineStr">
         <is>
-          <t>16#720|60404#20|60431#5|14#2000000|19#9</t>
+          <t>16#720|60404#20|60431#5|14#2000000|19#12</t>
         </is>
       </c>
       <c r="Q618" s="0" t="n">
@@ -53496,12 +53496,12 @@
       </c>
       <c r="L619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#19|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
+          <t>16#1000|19#19|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q619" s="0" t="n">
@@ -53585,12 +53585,12 @@
       </c>
       <c r="L620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q620" s="0" t="n">
@@ -53674,12 +53674,12 @@
       </c>
       <c r="L621" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M621" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q621" s="0" t="n">
@@ -53763,12 +53763,12 @@
       </c>
       <c r="L622" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M622" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#15|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q622" s="0" t="n">
@@ -53852,12 +53852,12 @@
       </c>
       <c r="L623" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#7|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M623" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#7|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q623" s="0" t="n">
@@ -53941,12 +53941,12 @@
       </c>
       <c r="L624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#15|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#600|19#19|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#15|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#600|19#19|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q624" s="0" t="n">
@@ -54030,12 +54030,12 @@
       </c>
       <c r="L625" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#7|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M625" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#7|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q625" s="0" t="n">
@@ -54119,12 +54119,12 @@
       </c>
       <c r="L626" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M626" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q626" s="0" t="n">
@@ -54208,12 +54208,12 @@
       </c>
       <c r="L627" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M627" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q627" s="0" t="n">
@@ -54297,12 +54297,12 @@
       </c>
       <c r="L628" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M628" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q628" s="0" t="n">
@@ -54386,12 +54386,12 @@
       </c>
       <c r="L629" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M629" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q629" s="0" t="n">
@@ -54475,12 +54475,12 @@
       </c>
       <c r="L630" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M630" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q630" s="0" t="n">
@@ -54564,12 +54564,12 @@
       </c>
       <c r="L631" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M631" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q631" s="0" t="n">
@@ -54653,12 +54653,12 @@
       </c>
       <c r="L632" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M632" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q632" s="0" t="n">
@@ -54742,12 +54742,12 @@
       </c>
       <c r="L633" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M633" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q633" s="0" t="n">
@@ -54831,12 +54831,12 @@
       </c>
       <c r="L634" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M634" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#130|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q634" s="0" t="n">
@@ -54920,12 +54920,12 @@
       </c>
       <c r="L635" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|6000110#1500|72001#200|6000124#980|19#18</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200|6000124#980|19#23</t>
         </is>
       </c>
       <c r="M635" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|6000110#1500|72001#200|19#18</t>
+          <t>16#1176|4#2000|6000110#1500|72001#200|19#23</t>
         </is>
       </c>
       <c r="Q635" s="0" t="n">
@@ -55009,12 +55009,12 @@
       </c>
       <c r="L636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280|19#25</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|19#25</t>
+          <t>16#1555|4#2500|6000110#2000|72001#250|19#32</t>
         </is>
       </c>
       <c r="Q636" s="0" t="n">
@@ -55098,12 +55098,12 @@
       </c>
       <c r="L637" s="0" t="inlineStr">
         <is>
-          <t>16#1555|81004#1|4#5000|3#5000000|6000124#1280|19#23</t>
+          <t>16#1555|81004#1|4#5000|3#5000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M637" s="0" t="inlineStr">
         <is>
-          <t>16#1555|81004#1|4#5000|3#5000000|19#23</t>
+          <t>16#1555|81004#1|4#5000|3#5000000|19#29</t>
         </is>
       </c>
       <c r="Q637" s="0" t="n">
@@ -55187,12 +55187,12 @@
       </c>
       <c r="L638" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|20#3|19#35|6000124#1980</t>
+          <t>16#2475|60415#1|20#3|19#45|6000124#1980</t>
         </is>
       </c>
       <c r="M638" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|20#3|19#35</t>
+          <t>16#2475|60415#1|20#3|19#45</t>
         </is>
       </c>
       <c r="Q638" s="0" t="n">
@@ -55276,12 +55276,12 @@
       </c>
       <c r="L639" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980|19#38</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M639" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|19#38</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q639" s="0" t="n">
@@ -55365,12 +55365,12 @@
       </c>
       <c r="L640" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280|19#23</t>
+          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M640" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|19#23</t>
+          <t>16#1555|17012#30|17011#120|17009#60|19#29</t>
         </is>
       </c>
       <c r="Q640" s="0" t="n">
@@ -55454,12 +55454,12 @@
       </c>
       <c r="L641" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980|19#38</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M641" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|19#38</t>
+          <t>16#2475|60415#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q641" s="0" t="n">
@@ -55543,12 +55543,12 @@
       </c>
       <c r="L642" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980|19#38</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M642" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|19#38</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q642" s="0" t="n">
@@ -55632,12 +55632,12 @@
       </c>
       <c r="L643" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280|19#23</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M643" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|19#23</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|19#29</t>
         </is>
       </c>
       <c r="Q643" s="0" t="n">
@@ -55721,12 +55721,12 @@
       </c>
       <c r="L644" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#57|61#5|6000124#3280</t>
+          <t>16#4264|20#10|19#75|61#5|6000124#3280</t>
         </is>
       </c>
       <c r="M644" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#57|61#5</t>
+          <t>16#4264|20#10|19#75|61#5</t>
         </is>
       </c>
       <c r="Q644" s="0" t="n">
@@ -55810,12 +55810,12 @@
       </c>
       <c r="L645" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280|19#67</t>
+          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M645" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99002#1|10442#25|10441#150|19#67</t>
+          <t>16#4264|99002#1|10442#25|10441#150|19#85</t>
         </is>
       </c>
       <c r="Q645" s="0" t="n">
@@ -55899,12 +55899,12 @@
       </c>
       <c r="L646" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280|19#67</t>
+          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M646" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60411#20|19#67</t>
+          <t>16#4264|81148#100|60412#10|60411#20|19#85</t>
         </is>
       </c>
       <c r="Q646" s="0" t="n">
@@ -55988,12 +55988,12 @@
       </c>
       <c r="L647" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#67|6000110#5000|14#30000000|6000124#3280</t>
+          <t>16#4264|20#85|6000110#5000|14#30000000|6000124#3280</t>
         </is>
       </c>
       <c r="M647" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#67|6000110#5000|14#30000000</t>
+          <t>16#4264|20#85|6000110#5000|14#30000000</t>
         </is>
       </c>
       <c r="Q647" s="0" t="n">
@@ -56077,12 +56077,12 @@
       </c>
       <c r="L648" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#2|60411#10|14#5000000|6000124#980|19#17</t>
+          <t>16#1176|60412#2|60411#10|14#5000000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M648" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#2|60411#10|14#5000000|19#17</t>
+          <t>16#1176|60412#2|60411#10|14#5000000|19#22</t>
         </is>
       </c>
       <c r="Q648" s="0" t="n">
@@ -56166,12 +56166,12 @@
       </c>
       <c r="L649" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#3|60411#15|14#8000000|6000124#1280|19#23</t>
+          <t>16#1555|60412#3|60411#15|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M649" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#3|60411#15|14#8000000|19#23</t>
+          <t>16#1555|60412#3|60411#15|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q649" s="0" t="n">
@@ -56255,12 +56255,12 @@
       </c>
       <c r="L650" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60412#5|60411#20|14#15000000|6000124#1980|19#38</t>
+          <t>16#2475|60412#5|60411#20|14#15000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M650" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60412#5|60411#20|14#15000000|19#38</t>
+          <t>16#2475|60412#5|60411#20|14#15000000|19#48</t>
         </is>
       </c>
       <c r="Q650" s="0" t="n">
@@ -56344,12 +56344,12 @@
       </c>
       <c r="L651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280|19#24</t>
+          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|19#24</t>
+          <t>16#1555|99005#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q651" s="0" t="n">
@@ -56433,12 +56433,12 @@
       </c>
       <c r="L652" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99005#1|3#10000000|4#5000|6000124#3280|19#69</t>
+          <t>16#4264|99005#1|3#10000000|4#5000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M652" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99005#1|3#10000000|4#5000|19#69</t>
+          <t>16#4264|99005#1|3#10000000|4#5000|19#88</t>
         </is>
       </c>
       <c r="Q652" s="0" t="n">
@@ -56522,12 +56522,12 @@
       </c>
       <c r="L653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480|19#153</t>
+          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|19#153</t>
+          <t>16#8748|99005#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q653" s="0" t="n">
@@ -56611,12 +56611,12 @@
       </c>
       <c r="L654" s="0" t="inlineStr">
         <is>
-          <t>16#720|99006#1|14#2000000|3#1000000|6000124#600|19#9</t>
+          <t>16#720|99006#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M654" s="0" t="inlineStr">
         <is>
-          <t>16#720|99006#1|14#2000000|3#1000000|19#9</t>
+          <t>16#720|99006#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q654" s="0" t="n">
@@ -56700,12 +56700,12 @@
       </c>
       <c r="L655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280|19#24</t>
+          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|19#24</t>
+          <t>16#1555|99006#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q655" s="0" t="n">
@@ -56789,12 +56789,12 @@
       </c>
       <c r="L656" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99006#1|3#10000000|4#5000|6000124#3280|19#69</t>
+          <t>16#4264|99006#1|3#10000000|4#5000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M656" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99006#1|3#10000000|4#5000|19#69</t>
+          <t>16#4264|99006#1|3#10000000|4#5000|19#88</t>
         </is>
       </c>
       <c r="Q656" s="0" t="n">
@@ -56878,12 +56878,12 @@
       </c>
       <c r="L657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480|19#153</t>
+          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|19#153</t>
+          <t>16#8748|99006#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q657" s="0" t="n">
@@ -56967,12 +56967,12 @@
       </c>
       <c r="L658" s="0" t="inlineStr">
         <is>
-          <t>16#720|99007#1|14#2000000|3#1000000|6000124#600|19#9</t>
+          <t>16#720|99007#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M658" s="0" t="inlineStr">
         <is>
-          <t>16#720|99007#1|14#2000000|3#1000000|19#9</t>
+          <t>16#720|99007#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q658" s="0" t="n">
@@ -57056,12 +57056,12 @@
       </c>
       <c r="L659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280|19#24</t>
+          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|19#24</t>
+          <t>16#1555|99007#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q659" s="0" t="n">
@@ -57145,12 +57145,12 @@
       </c>
       <c r="L660" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99007#1|3#10000000|4#5000|6000124#3280|19#69</t>
+          <t>16#4264|99007#1|3#10000000|4#5000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M660" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99007#1|3#10000000|4#5000|19#69</t>
+          <t>16#4264|99007#1|3#10000000|4#5000|19#88</t>
         </is>
       </c>
       <c r="Q660" s="0" t="n">
@@ -57234,12 +57234,12 @@
       </c>
       <c r="L661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480|19#153</t>
+          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|19#153</t>
+          <t>16#8748|99007#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q661" s="0" t="n">
@@ -57323,12 +57323,12 @@
       </c>
       <c r="L662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280|19#25</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|19#25</t>
+          <t>16#1555|4#3000|6000088#1|6000110#3000|19#32</t>
         </is>
       </c>
       <c r="Q662" s="0" t="n">
@@ -57412,12 +57412,12 @@
       </c>
       <c r="L663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980|19#40</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980|19#51</t>
         </is>
       </c>
       <c r="M663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|19#40</t>
+          <t>16#2475|4#3000|6000110#2000|72001#200|19#51</t>
         </is>
       </c>
       <c r="Q663" s="0" t="n">
@@ -57501,12 +57501,12 @@
       </c>
       <c r="L664" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|6000110#3000|72001#250|6000124#3280|19#71</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250|6000124#3280|19#90</t>
         </is>
       </c>
       <c r="M664" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|6000110#3000|72001#250|19#71</t>
+          <t>16#4264|4#5000|6000110#3000|72001#250|19#90</t>
         </is>
       </c>
       <c r="Q664" s="0" t="n">
@@ -57590,12 +57590,12 @@
       </c>
       <c r="L665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280|19#25</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|19#25</t>
+          <t>16#1555|4#3000|99000#1|6000110#3000|19#32</t>
         </is>
       </c>
       <c r="Q665" s="0" t="n">
@@ -57679,12 +57679,12 @@
       </c>
       <c r="L666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980|19#40</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980|19#51</t>
         </is>
       </c>
       <c r="M666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|19#40</t>
+          <t>16#2475|4#4000|99001#1|6000110#4000|19#51</t>
         </is>
       </c>
       <c r="Q666" s="0" t="n">
@@ -57768,12 +57768,12 @@
       </c>
       <c r="L667" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|99002#1|6000110#5000|6000124#3280|19#71</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000|6000124#3280|19#90</t>
         </is>
       </c>
       <c r="M667" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#5000|99002#1|6000110#5000|19#71</t>
+          <t>16#4264|4#5000|99002#1|6000110#5000|19#90</t>
         </is>
       </c>
       <c r="Q667" s="0" t="n">
@@ -57857,12 +57857,12 @@
       </c>
       <c r="L668" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|60411#8|60412#2|6000124#980|19#19</t>
+          <t>16#1176|4#2000|60411#8|60412#2|6000124#980|19#24</t>
         </is>
       </c>
       <c r="M668" s="0" t="inlineStr">
         <is>
-          <t>16#1176|4#2000|60411#8|60412#2|19#19</t>
+          <t>16#1176|4#2000|60411#8|60412#2|19#24</t>
         </is>
       </c>
       <c r="Q668" s="0" t="n">
@@ -57946,12 +57946,12 @@
       </c>
       <c r="L669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280|19#26</t>
+          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|19#26</t>
+          <t>16#1555|4#2500|60411#10|60412#3|19#33</t>
         </is>
       </c>
       <c r="Q669" s="0" t="n">
@@ -58035,12 +58035,12 @@
       </c>
       <c r="L670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980|19#41</t>
+          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980|19#52</t>
         </is>
       </c>
       <c r="M670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|19#41</t>
+          <t>16#2475|4#3000|60411#12|6000088#1|19#52</t>
         </is>
       </c>
       <c r="Q670" s="0" t="n">
@@ -58124,12 +58124,12 @@
       </c>
       <c r="L671" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#4000|60411#15|6000088#2|6000124#3280|19#73</t>
+          <t>16#4264|4#4000|60411#15|6000088#2|6000124#3280|19#92</t>
         </is>
       </c>
       <c r="M671" s="0" t="inlineStr">
         <is>
-          <t>16#4264|4#4000|60411#15|6000088#2|19#73</t>
+          <t>16#4264|4#4000|60411#15|6000088#2|19#92</t>
         </is>
       </c>
       <c r="Q671" s="0" t="n">
@@ -58213,12 +58213,12 @@
       </c>
       <c r="L672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880|19#117</t>
+          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880|19#148</t>
         </is>
       </c>
       <c r="M672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|19#117</t>
+          <t>16#6466|4#4500|60411#20|6000089#1|19#148</t>
         </is>
       </c>
       <c r="Q672" s="0" t="n">
@@ -58302,12 +58302,12 @@
       </c>
       <c r="L673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480|19#160</t>
+          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480|19#202</t>
         </is>
       </c>
       <c r="M673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|19#160</t>
+          <t>16#8748|4#5000|60412#3|6000090#1|19#202</t>
         </is>
       </c>
       <c r="Q673" s="0" t="n">
@@ -58391,12 +58391,12 @@
       </c>
       <c r="L674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280|19#27</t>
+          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280|19#34</t>
         </is>
       </c>
       <c r="M674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|19#27</t>
+          <t>16#1555|72001#200|60411#10|60412#3|19#34</t>
         </is>
       </c>
       <c r="Q674" s="0" t="n">
@@ -58480,12 +58480,12 @@
       </c>
       <c r="L675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980|19#42</t>
+          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|19#42</t>
+          <t>16#2475|72001#300|60411#15|60412#4|19#53</t>
         </is>
       </c>
       <c r="Q675" s="0" t="n">
@@ -58569,12 +58569,12 @@
       </c>
       <c r="L676" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#500|60411#25|60412#6|6000124#3280|19#75</t>
+          <t>16#4264|72001#500|60411#25|60412#6|6000124#3280|19#95</t>
         </is>
       </c>
       <c r="M676" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#500|60411#25|60412#6|19#75</t>
+          <t>16#4264|72001#500|60411#25|60412#6|19#95</t>
         </is>
       </c>
       <c r="Q676" s="0" t="n">
@@ -58658,12 +58658,12 @@
       </c>
       <c r="L677" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#450|60411#15|60412#4|6000124#3280|19#75</t>
+          <t>16#4264|72001#450|60411#15|60412#4|6000124#3280|19#95</t>
         </is>
       </c>
       <c r="M677" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72001#450|60411#15|60412#4|19#75</t>
+          <t>16#4264|72001#450|60411#15|60412#4|19#95</t>
         </is>
       </c>
       <c r="Q677" s="0" t="n">
@@ -58747,12 +58747,12 @@
       </c>
       <c r="L678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880|19#119</t>
+          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880|19#150</t>
         </is>
       </c>
       <c r="M678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|19#119</t>
+          <t>16#6466|72001#500|60411#20|60412#5|19#150</t>
         </is>
       </c>
       <c r="Q678" s="0" t="n">
@@ -58836,12 +58836,12 @@
       </c>
       <c r="L679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480|19#164</t>
+          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480|19#207</t>
         </is>
       </c>
       <c r="M679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|19#164</t>
+          <t>16#8748|72001#550|60411#25|60412#5|19#207</t>
         </is>
       </c>
       <c r="Q679" s="0" t="n">
@@ -58925,12 +58925,12 @@
       </c>
       <c r="L680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280|19#28</t>
+          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280|19#35</t>
         </is>
       </c>
       <c r="M680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|19#28</t>
+          <t>16#1555|60417#1|60411#8|60412#2|19#35</t>
         </is>
       </c>
       <c r="Q680" s="0" t="n">
@@ -59014,12 +59014,12 @@
       </c>
       <c r="L681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980|19#44</t>
+          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980|19#56</t>
         </is>
       </c>
       <c r="M681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|19#44</t>
+          <t>16#2475|60417#1|60411#15|60412#4|19#56</t>
         </is>
       </c>
       <c r="Q681" s="0" t="n">
@@ -59103,12 +59103,12 @@
       </c>
       <c r="L682" s="0" t="inlineStr">
         <is>
-          <t>16#4264|60417#1|60411#25|60412#6|6000124#3280|19#77</t>
+          <t>16#4264|60417#1|60411#25|60412#6|6000124#3280|19#97</t>
         </is>
       </c>
       <c r="M682" s="0" t="inlineStr">
         <is>
-          <t>16#4264|60417#1|60411#25|60412#6|19#77</t>
+          <t>16#4264|60417#1|60411#25|60412#6|19#97</t>
         </is>
       </c>
       <c r="Q682" s="0" t="n">
@@ -59192,12 +59192,12 @@
       </c>
       <c r="L683" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280|19#23</t>
+          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M683" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|19#23</t>
+          <t>16#1555|17012#30|17011#120|17009#60|19#29</t>
         </is>
       </c>
       <c r="Q683" s="0" t="n">
@@ -59281,12 +59281,12 @@
       </c>
       <c r="L684" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|3#8000000|6000124#1980|19#38</t>
+          <t>16#2475|60415#1|6000089#1|3#8000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M684" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|3#8000000|19#38</t>
+          <t>16#2475|60415#1|6000089#1|3#8000000|19#48</t>
         </is>
       </c>
       <c r="Q684" s="0" t="n">
@@ -59370,12 +59370,12 @@
       </c>
       <c r="L685" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280|19#23</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M685" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|19#23</t>
+          <t>16#1555|6000097#15|6000098#60|6000092#120|19#29</t>
         </is>
       </c>
       <c r="Q685" s="0" t="n">
@@ -59459,12 +59459,12 @@
       </c>
       <c r="L686" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980|19#38</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M686" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|19#38</t>
+          <t>16#2475|60416#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q686" s="0" t="n">
@@ -59548,12 +59548,12 @@
       </c>
       <c r="L687" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280|19#67</t>
+          <t>16#4264|99002#1|10442#25|10441#150|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M687" s="0" t="inlineStr">
         <is>
-          <t>16#4264|99002#1|10442#25|10441#150|19#67</t>
+          <t>16#4264|99002#1|10442#25|10441#150|19#85</t>
         </is>
       </c>
       <c r="Q687" s="0" t="n">
@@ -59637,12 +59637,12 @@
       </c>
       <c r="L688" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280|19#67</t>
+          <t>16#4264|81148#100|60412#10|60411#20|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M688" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60411#20|19#67</t>
+          <t>16#4264|81148#100|60412#10|60411#20|19#85</t>
         </is>
       </c>
       <c r="Q688" s="0" t="n">
@@ -59726,12 +59726,12 @@
       </c>
       <c r="L689" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#67|6000110#3000|14#3000000|6000124#3280</t>
+          <t>16#4264|20#85|6000110#3000|14#3000000|6000124#3280</t>
         </is>
       </c>
       <c r="M689" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#67|6000110#3000|14#3000000</t>
+          <t>16#4264|20#85|6000110#3000|14#3000000</t>
         </is>
       </c>
       <c r="Q689" s="0" t="n">
@@ -59815,12 +59815,12 @@
       </c>
       <c r="L690" s="0" t="inlineStr">
         <is>
-          <t>16#8748|60406#1|10423#10|10425#600|6000124#6480|19#149</t>
+          <t>16#8748|60406#1|10423#10|10425#600|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M690" s="0" t="inlineStr">
         <is>
-          <t>16#8748|60406#1|10423#10|10425#600|19#149</t>
+          <t>16#8748|60406#1|10423#10|10425#600|19#189</t>
         </is>
       </c>
       <c r="Q690" s="0" t="n">
@@ -59904,12 +59904,12 @@
       </c>
       <c r="L691" s="0" t="inlineStr">
         <is>
-          <t>16#720|81114#1|3#1000000|6000124#600|19#9</t>
+          <t>16#720|81114#1|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M691" s="0" t="inlineStr">
         <is>
-          <t>16#720|81114#1|3#1000000|19#9</t>
+          <t>16#720|81114#1|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q691" s="0" t="n">
@@ -59988,12 +59988,12 @@
       </c>
       <c r="L692" s="0" t="inlineStr">
         <is>
-          <t>16#816|20#11|14#2200000|6000124#680</t>
+          <t>16#816|20#14|14#2200000|6000124#680</t>
         </is>
       </c>
       <c r="M692" s="0" t="inlineStr">
         <is>
-          <t>16#816|20#11|14#2200000</t>
+          <t>16#816|20#14|14#2200000</t>
         </is>
       </c>
       <c r="Q692" s="0" t="n">
@@ -60072,12 +60072,12 @@
       </c>
       <c r="L693" s="0" t="inlineStr">
         <is>
-          <t>16#1176|81148#50|3#1000000|14#2200000|6000124#980|19#17</t>
+          <t>16#1176|81148#50|3#1000000|14#2200000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M693" s="0" t="inlineStr">
         <is>
-          <t>16#1176|81148#50|3#1000000|14#2200000|19#17</t>
+          <t>16#1176|81148#50|3#1000000|14#2200000|19#22</t>
         </is>
       </c>
       <c r="Q693" s="0" t="n">
@@ -60156,12 +60156,12 @@
       </c>
       <c r="L694" s="0" t="inlineStr">
         <is>
-          <t>16#1176|20#17|14#4400000|6000124#980</t>
+          <t>16#1176|20#22|14#4400000|6000124#980</t>
         </is>
       </c>
       <c r="M694" s="0" t="inlineStr">
         <is>
-          <t>16#1176|20#17|14#4400000</t>
+          <t>16#1176|20#22|14#4400000</t>
         </is>
       </c>
       <c r="Q694" s="0" t="n">
@@ -60240,12 +60240,12 @@
       </c>
       <c r="L695" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60415#1|19#23|3#1000000|6000124#1280</t>
+          <t>16#1555|60415#1|19#29|3#1000000|6000124#1280</t>
         </is>
       </c>
       <c r="M695" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60415#1|19#23|3#1000000</t>
+          <t>16#1555|60415#1|19#29|3#1000000</t>
         </is>
       </c>
       <c r="Q695" s="0" t="n">
@@ -60324,12 +60324,12 @@
       </c>
       <c r="L696" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#23|6000110#2000|6000124#1280</t>
+          <t>16#1555|20#29|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M696" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#23|6000110#2000</t>
+          <t>16#1555|20#29|6000110#2000</t>
         </is>
       </c>
       <c r="Q696" s="0" t="n">
@@ -60408,12 +60408,12 @@
       </c>
       <c r="L697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#30|3#2000000|14#4000000|6000124#1280</t>
+          <t>16#1555|19#38|3#2000000|14#4000000|6000124#1280</t>
         </is>
       </c>
       <c r="M697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#30|3#2000000|14#4000000</t>
+          <t>16#1555|19#38|3#2000000|14#4000000</t>
         </is>
       </c>
       <c r="Q697" s="0" t="n">
@@ -60492,12 +60492,12 @@
       </c>
       <c r="L698" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|19#38|3#2000000|6000124#1980</t>
+          <t>16#2475|60416#1|19#48|3#2000000|6000124#1980</t>
         </is>
       </c>
       <c r="M698" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|19#38|3#2000000</t>
+          <t>16#2475|60416#1|19#48|3#2000000</t>
         </is>
       </c>
       <c r="Q698" s="0" t="n">
@@ -60576,12 +60576,12 @@
       </c>
       <c r="L699" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#38|6000110#3000|6000124#1980</t>
+          <t>16#2475|20#48|6000110#3000|6000124#1980</t>
         </is>
       </c>
       <c r="M699" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#38|6000110#3000</t>
+          <t>16#2475|20#48|6000110#3000</t>
         </is>
       </c>
       <c r="Q699" s="0" t="n">
@@ -60660,12 +60660,12 @@
       </c>
       <c r="L700" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60412#2|6000124#3280|19#67</t>
+          <t>16#4264|81148#100|60412#10|60412#2|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M700" s="0" t="inlineStr">
         <is>
-          <t>16#4264|81148#100|60412#10|60412#2|19#67</t>
+          <t>16#4264|81148#100|60412#10|60412#2|19#85</t>
         </is>
       </c>
       <c r="Q700" s="0" t="n">
@@ -60833,12 +60833,12 @@
       </c>
       <c r="L702" s="0" t="inlineStr">
         <is>
-          <t>16#360|60411#2|60410#3|14#1600000|6000124#300|19#4</t>
+          <t>16#360|60411#2|60410#3|14#1600000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M702" s="0" t="inlineStr">
         <is>
-          <t>16#360|60411#2|60410#3|14#1600000|19#4</t>
+          <t>16#360|60411#2|60410#3|14#1600000|19#5</t>
         </is>
       </c>
       <c r="Q702" s="0" t="n">
@@ -60922,12 +60922,12 @@
       </c>
       <c r="L703" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60410#5|14#3000000|6000124#600|19#9</t>
+          <t>16#720|60411#4|60410#5|14#3000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M703" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60410#5|14#3000000|19#9</t>
+          <t>16#720|60411#4|60410#5|14#3000000|19#12</t>
         </is>
       </c>
       <c r="Q703" s="0" t="n">
@@ -61011,12 +61011,12 @@
       </c>
       <c r="L704" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#4|60410#8|14#5000000|6000124#980|19#17</t>
+          <t>16#1176|60412#4|60410#8|14#5000000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M704" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#4|60410#8|14#5000000|19#17</t>
+          <t>16#1176|60412#4|60410#8|14#5000000|19#22</t>
         </is>
       </c>
       <c r="Q704" s="0" t="n">
@@ -61100,12 +61100,12 @@
       </c>
       <c r="L705" s="0" t="inlineStr">
         <is>
-          <t>16#4264|3#15000000|14#8000000|60411#5|6000124#3280|19#67</t>
+          <t>16#4264|3#15000000|14#8000000|60411#5|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M705" s="0" t="inlineStr">
         <is>
-          <t>16#4264|3#15000000|14#8000000|60411#5|19#67</t>
+          <t>16#4264|3#15000000|14#8000000|60411#5|19#85</t>
         </is>
       </c>
       <c r="Q705" s="0" t="n">
@@ -61189,12 +61189,12 @@
       </c>
       <c r="L706" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|14#10000000|60412#4|6000124#6480|19#149</t>
+          <t>16#8748|3#20000000|14#10000000|60412#4|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M706" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|14#10000000|60412#4|19#149</t>
+          <t>16#8748|3#20000000|14#10000000|60412#4|19#189</t>
         </is>
       </c>
       <c r="Q706" s="0" t="n">
@@ -61367,12 +61367,12 @@
       </c>
       <c r="L708" s="0" t="inlineStr">
         <is>
-          <t>16#360|60411#2|60418#3|14#1600000|6000124#300|19#4</t>
+          <t>16#360|60411#2|60418#3|14#1600000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M708" s="0" t="inlineStr">
         <is>
-          <t>16#360|60411#2|60418#3|14#1600000|19#4</t>
+          <t>16#360|60411#2|60418#3|14#1600000|19#5</t>
         </is>
       </c>
       <c r="Q708" s="0" t="n">
@@ -61456,12 +61456,12 @@
       </c>
       <c r="L709" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60418#5|14#3000000|6000124#600|19#9</t>
+          <t>16#720|60411#4|60418#5|14#3000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M709" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60418#5|14#3000000|19#9</t>
+          <t>16#720|60411#4|60418#5|14#3000000|19#12</t>
         </is>
       </c>
       <c r="Q709" s="0" t="n">
@@ -61545,12 +61545,12 @@
       </c>
       <c r="L710" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#4|60418#8|14#5000000|6000124#980|19#17</t>
+          <t>16#1176|60412#4|60418#8|14#5000000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M710" s="0" t="inlineStr">
         <is>
-          <t>16#1176|60412#4|60418#8|14#5000000|19#17</t>
+          <t>16#1176|60412#4|60418#8|14#5000000|19#22</t>
         </is>
       </c>
       <c r="Q710" s="0" t="n">
@@ -61634,12 +61634,12 @@
       </c>
       <c r="L711" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#6|60418#12|14#8000000|6000124#1280|19#23</t>
+          <t>16#1555|60412#6|60418#12|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M711" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#6|60418#12|14#8000000|19#23</t>
+          <t>16#1555|60412#6|60418#12|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q711" s="0" t="n">
@@ -61723,12 +61723,12 @@
       </c>
       <c r="L712" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|6000110#2000|99001#1|6000124#6480|19#149</t>
+          <t>16#8748|3#20000000|6000110#2000|99001#1|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M712" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|6000110#2000|99001#1|19#149</t>
+          <t>16#8748|3#20000000|6000110#2000|99001#1|19#189</t>
         </is>
       </c>
       <c r="Q712" s="0" t="n">
@@ -61812,12 +61812,12 @@
       </c>
       <c r="L713" s="0" t="inlineStr">
         <is>
-          <t>16#360|72003#10|4#500|3#800000|6000124#300|19#4</t>
+          <t>16#360|72003#10|4#500|3#800000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M713" s="0" t="inlineStr">
         <is>
-          <t>16#360|72003#10|4#500|3#800000|19#4</t>
+          <t>16#360|72003#10|4#500|3#800000|19#5</t>
         </is>
       </c>
       <c r="Q713" s="0" t="n">
@@ -61901,12 +61901,12 @@
       </c>
       <c r="L714" s="0" t="inlineStr">
         <is>
-          <t>16#720|72003#20|4#1000|3#1600000|6000124#600|19#9</t>
+          <t>16#720|72003#20|4#1000|3#1600000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M714" s="0" t="inlineStr">
         <is>
-          <t>16#720|72003#20|4#1000|3#1600000|19#9</t>
+          <t>16#720|72003#20|4#1000|3#1600000|19#12</t>
         </is>
       </c>
       <c r="Q714" s="0" t="n">
@@ -61990,12 +61990,12 @@
       </c>
       <c r="L715" s="0" t="inlineStr">
         <is>
-          <t>16#1176|72003#30|4#1500|3#3000000|6000124#980|19#17</t>
+          <t>16#1176|72003#30|4#1500|3#3000000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M715" s="0" t="inlineStr">
         <is>
-          <t>16#1176|72003#30|4#1500|3#3000000|19#17</t>
+          <t>16#1176|72003#30|4#1500|3#3000000|19#22</t>
         </is>
       </c>
       <c r="Q715" s="0" t="n">
@@ -62079,12 +62079,12 @@
       </c>
       <c r="L716" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72003#40|4#2000|3#5000000|6000124#1280|19#23</t>
+          <t>16#1555|72003#40|4#2000|3#5000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M716" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72003#40|4#2000|3#5000000|19#23</t>
+          <t>16#1555|72003#40|4#2000|3#5000000|19#29</t>
         </is>
       </c>
       <c r="Q716" s="0" t="n">
@@ -62168,12 +62168,12 @@
       </c>
       <c r="L717" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72003#60|4#3000|3#8000000|6000124#1980|19#38</t>
+          <t>16#2475|72003#60|4#3000|3#8000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M717" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72003#60|4#3000|3#8000000|19#38</t>
+          <t>16#2475|72003#60|4#3000|3#8000000|19#48</t>
         </is>
       </c>
       <c r="Q717" s="0" t="n">
@@ -62257,12 +62257,12 @@
       </c>
       <c r="L718" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72003#100|4#4000|3#15000000|6000124#3280|19#67</t>
+          <t>16#4264|72003#100|4#4000|3#15000000|6000124#3280|19#85</t>
         </is>
       </c>
       <c r="M718" s="0" t="inlineStr">
         <is>
-          <t>16#4264|72003#100|4#4000|3#15000000|19#67</t>
+          <t>16#4264|72003#100|4#4000|3#15000000|19#85</t>
         </is>
       </c>
       <c r="Q718" s="0" t="n">
@@ -62346,12 +62346,12 @@
       </c>
       <c r="L719" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000094#8|72003#8|3#800000|6000124#300|19#4</t>
+          <t>16#360|6000094#8|72003#8|3#800000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M719" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000094#8|72003#8|3#800000|19#4</t>
+          <t>16#360|6000094#8|72003#8|3#800000|19#5</t>
         </is>
       </c>
       <c r="Q719" s="0" t="n">
@@ -62435,12 +62435,12 @@
       </c>
       <c r="L720" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M720" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q720" s="0" t="n">
@@ -62524,12 +62524,12 @@
       </c>
       <c r="L721" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M721" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q721" s="0" t="n">
@@ -62613,12 +62613,12 @@
       </c>
       <c r="L722" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M722" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q722" s="0" t="n">
@@ -62702,12 +62702,12 @@
       </c>
       <c r="L723" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M723" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q723" s="0" t="n">
@@ -62791,12 +62791,12 @@
       </c>
       <c r="L724" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M724" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q724" s="0" t="n">
@@ -62875,12 +62875,12 @@
       </c>
       <c r="L725" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M725" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q725" s="0" t="n">
@@ -62959,12 +62959,12 @@
       </c>
       <c r="L726" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M726" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q726" s="0" t="n">
@@ -63043,12 +63043,12 @@
       </c>
       <c r="L727" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M727" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q727" s="0" t="n">
@@ -63127,12 +63127,12 @@
       </c>
       <c r="L728" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M728" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q728" s="0" t="n">
@@ -63211,12 +63211,12 @@
       </c>
       <c r="L729" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M729" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q729" s="0" t="n">
@@ -63295,12 +63295,12 @@
       </c>
       <c r="L730" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M730" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q730" s="0" t="n">
@@ -63384,12 +63384,12 @@
       </c>
       <c r="L731" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M731" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q731" s="0" t="n">
@@ -63473,12 +63473,12 @@
       </c>
       <c r="L732" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M732" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q732" s="0" t="n">
@@ -63562,12 +63562,12 @@
       </c>
       <c r="L733" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M733" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q733" s="0" t="n">
@@ -63651,12 +63651,12 @@
       </c>
       <c r="L734" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M734" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q734" s="0" t="n">
@@ -63735,12 +63735,12 @@
       </c>
       <c r="L735" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M735" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q735" s="0" t="n">
@@ -63824,12 +63824,12 @@
       </c>
       <c r="L736" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M736" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q736" s="0" t="n">
@@ -63913,12 +63913,12 @@
       </c>
       <c r="L737" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M737" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q737" s="0" t="n">
@@ -64002,12 +64002,12 @@
       </c>
       <c r="L738" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M738" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q738" s="0" t="n">
@@ -64091,12 +64091,12 @@
       </c>
       <c r="L739" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M739" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q739" s="0" t="n">
@@ -64175,12 +64175,12 @@
       </c>
       <c r="L740" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M740" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q740" s="0" t="n">
@@ -64264,12 +64264,12 @@
       </c>
       <c r="L741" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M741" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q741" s="0" t="n">
@@ -64353,12 +64353,12 @@
       </c>
       <c r="L742" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M742" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q742" s="0" t="n">
@@ -64442,12 +64442,12 @@
       </c>
       <c r="L743" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M743" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q743" s="0" t="n">
@@ -64531,12 +64531,12 @@
       </c>
       <c r="L744" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M744" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q744" s="0" t="n">
@@ -64615,12 +64615,12 @@
       </c>
       <c r="L745" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M745" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q745" s="0" t="n">
@@ -64699,12 +64699,12 @@
       </c>
       <c r="L746" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M746" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q746" s="0" t="n">
@@ -64783,12 +64783,12 @@
       </c>
       <c r="L747" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M747" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q747" s="0" t="n">
@@ -64867,12 +64867,12 @@
       </c>
       <c r="L748" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M748" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q748" s="0" t="n">
@@ -64951,12 +64951,12 @@
       </c>
       <c r="L749" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M749" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q749" s="0" t="n">
@@ -65035,12 +65035,12 @@
       </c>
       <c r="L750" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M750" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q750" s="0" t="n">
@@ -65124,12 +65124,12 @@
       </c>
       <c r="L751" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M751" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q751" s="0" t="n">
@@ -65213,12 +65213,12 @@
       </c>
       <c r="L752" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M752" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q752" s="0" t="n">
@@ -65302,12 +65302,12 @@
       </c>
       <c r="L753" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M753" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q753" s="0" t="n">
@@ -65391,12 +65391,12 @@
       </c>
       <c r="L754" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M754" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q754" s="0" t="n">
@@ -65475,12 +65475,12 @@
       </c>
       <c r="L755" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|6000124#300|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M755" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000115#100|6000110#1000|19#4</t>
+          <t>16#360|6000115#100|6000110#1000|19#5</t>
         </is>
       </c>
       <c r="Q755" s="0" t="n">
@@ -65559,12 +65559,12 @@
       </c>
       <c r="L756" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|6000124#680|19#11</t>
+          <t>16#816|6000115#200|6000094#4|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M756" s="0" t="inlineStr">
         <is>
-          <t>16#816|6000115#200|6000094#4|19#11</t>
+          <t>16#816|6000115#200|6000094#4|19#14</t>
         </is>
       </c>
       <c r="Q756" s="0" t="n">
@@ -65643,12 +65643,12 @@
       </c>
       <c r="L757" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17|6000124#980</t>
+          <t>16#1127|6000115#300|19#22|6000124#980</t>
         </is>
       </c>
       <c r="M757" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000115#300|19#17</t>
+          <t>16#1127|6000115#300|19#22</t>
         </is>
       </c>
       <c r="Q757" s="0" t="n">
@@ -65727,12 +65727,12 @@
       </c>
       <c r="L758" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M758" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60402#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60402#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q758" s="0" t="n">
@@ -65811,12 +65811,12 @@
       </c>
       <c r="L759" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M759" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6000115#400|60403#1|6000110#3000|19#24</t>
+          <t>16#1472|6000115#400|60403#1|6000110#3000|19#30</t>
         </is>
       </c>
       <c r="Q759" s="0" t="n">
@@ -65895,12 +65895,12 @@
       </c>
       <c r="L760" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M760" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q760" s="0" t="n">
@@ -65982,12 +65982,12 @@
       </c>
       <c r="L761" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M761" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q761" s="0" t="n">
@@ -66069,12 +66069,12 @@
       </c>
       <c r="L762" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M762" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q762" s="0" t="n">
@@ -66156,12 +66156,12 @@
       </c>
       <c r="L763" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M763" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q763" s="0" t="n">
@@ -66243,12 +66243,12 @@
       </c>
       <c r="L764" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M764" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q764" s="0" t="n">
@@ -66330,12 +66330,12 @@
       </c>
       <c r="L765" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M765" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q765" s="0" t="n">
@@ -66417,12 +66417,12 @@
       </c>
       <c r="L766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q766" s="0" t="n">
@@ -66504,12 +66504,12 @@
       </c>
       <c r="L767" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M767" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q767" s="0" t="n">
@@ -66591,12 +66591,12 @@
       </c>
       <c r="L768" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M768" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q768" s="0" t="n">
@@ -66678,12 +66678,12 @@
       </c>
       <c r="L769" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#50|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|6000085#50|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M769" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#50|20#70|6000110#2500</t>
+          <t>16#3674|6000085#50|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q769" s="0" t="n">
@@ -66765,12 +66765,12 @@
       </c>
       <c r="L770" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M770" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q770" s="0" t="n">
@@ -66852,12 +66852,12 @@
       </c>
       <c r="L771" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M771" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q771" s="0" t="n">
@@ -66939,12 +66939,12 @@
       </c>
       <c r="L772" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M772" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q772" s="0" t="n">
@@ -67026,12 +67026,12 @@
       </c>
       <c r="L773" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M773" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q773" s="0" t="n">
@@ -67113,12 +67113,12 @@
       </c>
       <c r="L774" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M774" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q774" s="0" t="n">
@@ -67200,12 +67200,12 @@
       </c>
       <c r="L775" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M775" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q775" s="0" t="n">
@@ -67287,12 +67287,12 @@
       </c>
       <c r="L776" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M776" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q776" s="0" t="n">
@@ -67374,12 +67374,12 @@
       </c>
       <c r="L777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q777" s="0" t="n">
@@ -67461,12 +67461,12 @@
       </c>
       <c r="L778" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M778" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q778" s="0" t="n">
@@ -67548,12 +67548,12 @@
       </c>
       <c r="L779" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M779" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q779" s="0" t="n">
@@ -67635,12 +67635,12 @@
       </c>
       <c r="L780" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#50|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|6000085#50|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M780" s="0" t="inlineStr">
         <is>
-          <t>16#3674|6000085#50|20#70|6000110#2500</t>
+          <t>16#3674|6000085#50|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q780" s="0" t="n">
@@ -67722,12 +67722,12 @@
       </c>
       <c r="L781" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M781" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q781" s="0" t="n">
@@ -67809,12 +67809,12 @@
       </c>
       <c r="L782" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M782" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q782" s="0" t="n">
@@ -67896,12 +67896,12 @@
       </c>
       <c r="L783" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M783" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q783" s="0" t="n">
@@ -67983,12 +67983,12 @@
       </c>
       <c r="L784" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M784" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q784" s="0" t="n">
@@ -68070,12 +68070,12 @@
       </c>
       <c r="L785" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M785" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q785" s="0" t="n">
@@ -68157,12 +68157,12 @@
       </c>
       <c r="L786" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M786" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q786" s="0" t="n">
@@ -68244,12 +68244,12 @@
       </c>
       <c r="L787" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M787" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q787" s="0" t="n">
@@ -68331,12 +68331,12 @@
       </c>
       <c r="L788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q788" s="0" t="n">
@@ -68418,12 +68418,12 @@
       </c>
       <c r="L789" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M789" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q789" s="0" t="n">
@@ -68505,12 +68505,12 @@
       </c>
       <c r="L790" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001025#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M790" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#24|6000110#1500</t>
+          <t>16#1472|6001025#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q790" s="0" t="n">
@@ -68592,12 +68592,12 @@
       </c>
       <c r="L791" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|17014#200|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M791" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500</t>
+          <t>16#3674|17014#200|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q791" s="0" t="n">
@@ -68679,12 +68679,12 @@
       </c>
       <c r="L792" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M792" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q792" s="0" t="n">
@@ -68766,12 +68766,12 @@
       </c>
       <c r="L793" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M793" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q793" s="0" t="n">
@@ -68853,12 +68853,12 @@
       </c>
       <c r="L794" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M794" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q794" s="0" t="n">
@@ -68940,12 +68940,12 @@
       </c>
       <c r="L795" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M795" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q795" s="0" t="n">
@@ -69027,12 +69027,12 @@
       </c>
       <c r="L796" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M796" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q796" s="0" t="n">
@@ -69114,12 +69114,12 @@
       </c>
       <c r="L797" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M797" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q797" s="0" t="n">
@@ -69201,12 +69201,12 @@
       </c>
       <c r="L798" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M798" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q798" s="0" t="n">
@@ -69288,12 +69288,12 @@
       </c>
       <c r="L799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q799" s="0" t="n">
@@ -69375,12 +69375,12 @@
       </c>
       <c r="L800" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M800" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q800" s="0" t="n">
@@ -69462,12 +69462,12 @@
       </c>
       <c r="L801" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M801" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q801" s="0" t="n">
@@ -69549,12 +69549,12 @@
       </c>
       <c r="L802" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|17014#200|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M802" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500</t>
+          <t>16#3674|17014#200|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q802" s="0" t="n">
@@ -69636,12 +69636,12 @@
       </c>
       <c r="L803" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M803" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q803" s="0" t="n">
@@ -69723,12 +69723,12 @@
       </c>
       <c r="L804" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M804" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q804" s="0" t="n">
@@ -69810,12 +69810,12 @@
       </c>
       <c r="L805" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M805" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q805" s="0" t="n">
@@ -69897,12 +69897,12 @@
       </c>
       <c r="L806" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M806" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q806" s="0" t="n">
@@ -69984,12 +69984,12 @@
       </c>
       <c r="L807" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M807" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q807" s="0" t="n">
@@ -70071,12 +70071,12 @@
       </c>
       <c r="L808" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M808" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q808" s="0" t="n">
@@ -70158,12 +70158,12 @@
       </c>
       <c r="L809" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M809" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q809" s="0" t="n">
@@ -70245,12 +70245,12 @@
       </c>
       <c r="L810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q810" s="0" t="n">
@@ -70332,12 +70332,12 @@
       </c>
       <c r="L811" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M811" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q811" s="0" t="n">
@@ -70419,12 +70419,12 @@
       </c>
       <c r="L812" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001025#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M812" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#24|6000110#1500</t>
+          <t>16#1472|6001025#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q812" s="0" t="n">
@@ -70506,12 +70506,12 @@
       </c>
       <c r="L813" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|17014#200|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M813" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500</t>
+          <t>16#3674|17014#200|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q813" s="0" t="n">
@@ -70593,12 +70593,12 @@
       </c>
       <c r="L814" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M814" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q814" s="0" t="n">
@@ -70680,12 +70680,12 @@
       </c>
       <c r="L815" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|6000124#680|19#11</t>
+          <t>16#816|50005#4|60431#1|6000124#680|19#14</t>
         </is>
       </c>
       <c r="M815" s="0" t="inlineStr">
         <is>
-          <t>16#816|50005#4|60431#1|19#11</t>
+          <t>16#816|50005#4|60431#1|19#14</t>
         </is>
       </c>
       <c r="Q815" s="0" t="n">
@@ -70767,12 +70767,12 @@
       </c>
       <c r="L816" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M816" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50005#6|60431#1|6000110#1000|19#17</t>
+          <t>16#1127|50005#6|60431#1|6000110#1000|19#22</t>
         </is>
       </c>
       <c r="Q816" s="0" t="n">
@@ -70854,12 +70854,12 @@
       </c>
       <c r="L817" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M817" s="0" t="inlineStr">
         <is>
-          <t>16#1472|50005#8|60431#1|6000110#1000|19#24</t>
+          <t>16#1472|50005#8|60431#1|6000110#1000|19#30</t>
         </is>
       </c>
       <c r="Q817" s="0" t="n">
@@ -70941,12 +70941,12 @@
       </c>
       <c r="L818" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M818" s="0" t="inlineStr">
         <is>
-          <t>16#3674|50005#20|60431#3|6000110#2000|19#70</t>
+          <t>16#3674|50005#20|60431#3|6000110#2000|19#88</t>
         </is>
       </c>
       <c r="Q818" s="0" t="n">
@@ -71028,12 +71028,12 @@
       </c>
       <c r="L819" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|6000124#6480|19#195</t>
         </is>
       </c>
       <c r="M819" s="0" t="inlineStr">
         <is>
-          <t>16#7452|50005#40|60431#6|6000110#5000|19#155</t>
+          <t>16#7452|50005#40|60431#6|6000110#5000|19#195</t>
         </is>
       </c>
       <c r="Q819" s="0" t="n">
@@ -71115,12 +71115,12 @@
       </c>
       <c r="L820" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M820" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#10|4#1000|6000110#1000</t>
+          <t>16#360|19#12|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q820" s="0" t="n">
@@ -71202,12 +71202,12 @@
       </c>
       <c r="L821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#15|4#1000|6000110#1000</t>
+          <t>16#816|19#19|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q821" s="0" t="n">
@@ -71289,12 +71289,12 @@
       </c>
       <c r="L822" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000|6000124#980</t>
+          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M822" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#12|19#5|6000110#1000</t>
+          <t>16#1127|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q822" s="0" t="n">
@@ -71376,12 +71376,12 @@
       </c>
       <c r="L823" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500|6000124#1280</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M823" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#24|6000110#1500</t>
+          <t>16#1472|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q823" s="0" t="n">
@@ -71463,12 +71463,12 @@
       </c>
       <c r="L824" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500|6000124#3280</t>
+          <t>16#3674|17014#200|20#88|6000110#2500|6000124#3280</t>
         </is>
       </c>
       <c r="M824" s="0" t="inlineStr">
         <is>
-          <t>16#3674|17014#200|20#70|6000110#2500</t>
+          <t>16#3674|17014#200|20#88|6000110#2500</t>
         </is>
       </c>
       <c r="Q824" s="0" t="n">
@@ -71550,12 +71550,12 @@
       </c>
       <c r="L825" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000|6000124#6480</t>
+          <t>16#7452|20#15|19#180|6000110#5000|6000124#6480</t>
         </is>
       </c>
       <c r="M825" s="0" t="inlineStr">
         <is>
-          <t>16#7452|20#15|19#140|6000110#5000</t>
+          <t>16#7452|20#15|19#180|6000110#5000</t>
         </is>
       </c>
       <c r="Q825" s="0" t="n">
@@ -71637,12 +71637,12 @@
       </c>
       <c r="L826" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#1000|6001020#50|6000124#980|19#17</t>
+          <t>16#1127|4#1000|6001020#50|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M826" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#1000|6001020#50|19#17</t>
+          <t>16#1127|4#1000|6001020#50|19#22</t>
         </is>
       </c>
       <c r="Q826" s="0" t="inlineStr">
@@ -71726,12 +71726,12 @@
       </c>
       <c r="L827" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#1000|6001020#50|6000124#980|19#17</t>
+          <t>16#1127|4#1000|6001020#50|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M827" s="0" t="inlineStr">
         <is>
-          <t>16#1127|4#1000|6001020#50|19#17</t>
+          <t>16#1127|4#1000|6001020#50|19#22</t>
         </is>
       </c>
       <c r="Q827" s="0" t="inlineStr">
@@ -71815,12 +71815,12 @@
       </c>
       <c r="L828" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|6000124#980|19#17</t>
+          <t>16#1127|60403#1|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M828" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|19#17</t>
+          <t>16#1127|60403#1|19#22</t>
         </is>
       </c>
       <c r="Q828" s="0" t="inlineStr">
@@ -71904,12 +71904,12 @@
       </c>
       <c r="L829" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|6000124#980|19#17</t>
+          <t>16#1127|60403#1|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M829" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|19#17</t>
+          <t>16#1127|60403#1|19#22</t>
         </is>
       </c>
       <c r="Q829" s="0" t="inlineStr">
@@ -71993,12 +71993,12 @@
       </c>
       <c r="L830" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|6000124#980|19#17</t>
+          <t>16#1127|60403#1|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M830" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|19#17</t>
+          <t>16#1127|60403#1|19#22</t>
         </is>
       </c>
       <c r="Q830" s="0" t="inlineStr">
@@ -72082,12 +72082,12 @@
       </c>
       <c r="L831" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|6000124#980|19#17</t>
+          <t>16#1127|60403#1|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M831" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|19#17</t>
+          <t>16#1127|60403#1|19#22</t>
         </is>
       </c>
       <c r="Q831" s="0" t="inlineStr">
@@ -72171,12 +72171,12 @@
       </c>
       <c r="L832" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|6000124#980|19#17</t>
+          <t>16#1127|60403#1|6000124#980|19#22</t>
         </is>
       </c>
       <c r="M832" s="0" t="inlineStr">
         <is>
-          <t>16#1127|60403#1|19#17</t>
+          <t>16#1127|60403#1|19#22</t>
         </is>
       </c>
       <c r="Q832" s="0" t="inlineStr">
@@ -72260,12 +72260,12 @@
       </c>
       <c r="L833" s="0" t="inlineStr">
         <is>
-          <t>16#2218|17013#200|6000124#1980|19#39</t>
+          <t>16#2218|17013#200|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M833" s="0" t="inlineStr">
         <is>
-          <t>16#2218|17013#200|19#39</t>
+          <t>16#2218|17013#200|19#49</t>
         </is>
       </c>
       <c r="Q833" s="0" t="inlineStr">
@@ -72349,12 +72349,12 @@
       </c>
       <c r="L834" s="0" t="inlineStr">
         <is>
-          <t>16#360|72003#1|6000124#300|19#4</t>
+          <t>16#360|72003#1|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M834" s="0" t="inlineStr">
         <is>
-          <t>16#360|72003#1|19#4</t>
+          <t>16#360|72003#1|19#5</t>
         </is>
       </c>
       <c r="Q834" s="0" t="inlineStr">
@@ -72438,12 +72438,12 @@
       </c>
       <c r="L835" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99000#4|6000104#10|6000124#3280|19#70</t>
+          <t>16#3674|99000#4|6000104#10|6000124#3280|19#88</t>
         </is>
       </c>
       <c r="M835" s="0" t="inlineStr">
         <is>
-          <t>16#3674|99000#4|6000104#10|19#70</t>
+          <t>16#3674|99000#4|6000104#10|19#88</t>
         </is>
       </c>
       <c r="Q835" s="0" t="inlineStr">
@@ -72527,12 +72527,12 @@
       </c>
       <c r="L836" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24|6000124#1280</t>
+          <t>16#1472|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M836" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24</t>
+          <t>16#1472|20#30</t>
         </is>
       </c>
       <c r="Q836" s="0" t="inlineStr">
@@ -72616,12 +72616,12 @@
       </c>
       <c r="L837" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24|6000124#1280</t>
+          <t>16#1472|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M837" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24</t>
+          <t>16#1472|20#30</t>
         </is>
       </c>
       <c r="Q837" s="0" t="inlineStr">
@@ -72705,12 +72705,12 @@
       </c>
       <c r="L838" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24|6000124#1280</t>
+          <t>16#1472|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M838" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24</t>
+          <t>16#1472|20#30</t>
         </is>
       </c>
       <c r="Q838" s="0" t="inlineStr">
@@ -72794,12 +72794,12 @@
       </c>
       <c r="L839" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24|6000124#1280</t>
+          <t>16#1472|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M839" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24</t>
+          <t>16#1472|20#30</t>
         </is>
       </c>
       <c r="Q839" s="0" t="inlineStr">
@@ -72883,12 +72883,12 @@
       </c>
       <c r="L840" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24|6000124#1280</t>
+          <t>16#1472|20#30|6000124#1280</t>
         </is>
       </c>
       <c r="M840" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#24</t>
+          <t>16#1472|20#30</t>
         </is>
       </c>
       <c r="Q840" s="0" t="inlineStr">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -21914,12 +21914,12 @@
       </c>
       <c r="L264" s="0" t="inlineStr">
         <is>
-          <t>16#980|19#10|65#1500|6000124#980</t>
+          <t>16#930|19#3|65#1500|6000124#980</t>
         </is>
       </c>
       <c r="M264" s="0" t="inlineStr">
         <is>
-          <t>16#980|19#10|65#1500</t>
+          <t>16#930|19#3|65#1500</t>
         </is>
       </c>
       <c r="Q264" s="0" t="n">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="L278" s="0" t="inlineStr">
         <is>
-          <t>16#240|81150#1|19#2|4#200|3#200000|6000124#120</t>
+          <t>16#170|81150#1|19#2|4#200|3#200000|6000124#120</t>
         </is>
       </c>
       <c r="M278" s="0" t="inlineStr">
         <is>
-          <t>16#120|81150#1|19#2|4#200|3#200000</t>
+          <t>16#50|81150#1|19#2|4#200|3#200000</t>
         </is>
       </c>
       <c r="Q278" s="0" t="n">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="L279" s="0" t="inlineStr">
         <is>
-          <t>16#360|81150#2|19#3|4#300|3#300000|6000124#180</t>
+          <t>16#360|81150#2|19#2|4#300|3#300000|6000124#180</t>
         </is>
       </c>
       <c r="M279" s="0" t="inlineStr">
         <is>
-          <t>16#180|81150#2|19#3|4#300|3#300000</t>
+          <t>16#180|81150#2|19#2|4#300|3#300000</t>
         </is>
       </c>
       <c r="Q279" s="0" t="n">
@@ -23275,12 +23275,12 @@
       </c>
       <c r="L280" s="0" t="inlineStr">
         <is>
-          <t>16#600|81150#3|19#7|61#1|3#1200000|6000124#300</t>
+          <t>16#600|81150#3|19#6|61#1|3#1200000|6000124#300</t>
         </is>
       </c>
       <c r="M280" s="0" t="inlineStr">
         <is>
-          <t>16#300|81150#3|19#7|61#1|3#1200000</t>
+          <t>16#300|81150#3|19#6|61#1|3#1200000</t>
         </is>
       </c>
       <c r="Q280" s="0" t="n">
@@ -23367,12 +23367,12 @@
       </c>
       <c r="L281" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#15|4#600|80#6|3#1700000|6000124#600</t>
+          <t>16#1320|81150#6|61#1|19#12|4#600|80#6|3#1700000|6000124#600</t>
         </is>
       </c>
       <c r="M281" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#15|4#600|80#6|3#1700000</t>
+          <t>16#1320|81150#6|61#1|19#12|4#600|80#6|3#1700000</t>
         </is>
       </c>
       <c r="Q281" s="0" t="n">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="L283" s="0" t="inlineStr">
         <is>
-          <t>16#240|81150#1|19#2|17009#30|6000110#300|6000124#120</t>
+          <t>16#170|81150#1|19#2|17009#30|6000110#300|6000124#120</t>
         </is>
       </c>
       <c r="M283" s="0" t="inlineStr">
         <is>
-          <t>16#120|81150#1|19#2|17009#30|6000110#300</t>
+          <t>16#50|81150#1|19#2|17009#30|6000110#300</t>
         </is>
       </c>
       <c r="Q283" s="0" t="n">
@@ -23628,12 +23628,12 @@
       </c>
       <c r="L284" s="0" t="inlineStr">
         <is>
-          <t>16#360|81150#2|19#3|17009#40|6000110#500|6000124#180</t>
+          <t>16#360|81150#2|19#2|17009#40|6000110#500|6000124#180</t>
         </is>
       </c>
       <c r="M284" s="0" t="inlineStr">
         <is>
-          <t>16#180|81150#2|19#3|17009#40|6000110#500</t>
+          <t>16#180|81150#2|19#2|17009#40|6000110#500</t>
         </is>
       </c>
       <c r="Q284" s="0" t="n">
@@ -23715,12 +23715,12 @@
       </c>
       <c r="L285" s="0" t="inlineStr">
         <is>
-          <t>16#600|81150#3|19#7|61#1|6000110#800|6000124#300</t>
+          <t>16#600|81150#3|19#6|61#1|6000110#800|6000124#300</t>
         </is>
       </c>
       <c r="M285" s="0" t="inlineStr">
         <is>
-          <t>16#300|81150#3|19#7|61#1|6000110#800</t>
+          <t>16#300|81150#3|19#6|61#1|6000110#800</t>
         </is>
       </c>
       <c r="Q285" s="0" t="n">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="L286" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#15|17009#70|72001#20|80#6|6000110#1600|6000124#600</t>
+          <t>16#1320|81150#6|61#1|19#12|17009#70|72001#20|80#6|6000110#1600|6000124#600</t>
         </is>
       </c>
       <c r="M286" s="0" t="inlineStr">
         <is>
-          <t>16#1320|81150#6|61#1|19#15|17009#70|72001#20|80#6|6000110#1600</t>
+          <t>16#1320|81150#6|61#1|19#12|17009#70|72001#20|80#6|6000110#1600</t>
         </is>
       </c>
       <c r="Q286" s="0" t="n">
@@ -25541,12 +25541,12 @@
       </c>
       <c r="L306" s="0" t="inlineStr">
         <is>
-          <t>16#156|81148#10|19#3|60#2|6000124#120</t>
+          <t>16#116|81148#10|19#2|60#2|6000124#120</t>
         </is>
       </c>
       <c r="M306" s="0" t="inlineStr">
         <is>
-          <t>16#156|81148#10|19#3|60#2</t>
+          <t>16#116|81148#10|19#2|60#2</t>
         </is>
       </c>
       <c r="Q306" s="0" t="n">
@@ -26428,12 +26428,12 @@
       </c>
       <c r="L316" s="0" t="inlineStr">
         <is>
-          <t>16#234|19#10|4#200|3#100000|6000124#180</t>
+          <t>16#234|19#3|4#200|3#100000|6000124#180</t>
         </is>
       </c>
       <c r="M316" s="0" t="inlineStr">
         <is>
-          <t>16#234|19#10|4#200|3#100000</t>
+          <t>16#234|19#3|4#200|3#100000</t>
         </is>
       </c>
       <c r="Q316" s="0" t="n">
@@ -27235,12 +27235,12 @@
       </c>
       <c r="L324" s="0" t="inlineStr">
         <is>
-          <t>200011#1|20010#1|19#24|200010#1000|6000124#600</t>
+          <t>200011#1|20010#1|19#18|200010#1000|6000124#600</t>
         </is>
       </c>
       <c r="M324" s="0" t="inlineStr">
         <is>
-          <t>200011#1|20010#1|19#24|200010#1000</t>
+          <t>200011#1|20010#1|19#18|200010#1000</t>
         </is>
       </c>
       <c r="Q324" s="0" t="inlineStr">
@@ -28769,12 +28769,12 @@
       </c>
       <c r="L342" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#2000|70034#2|72001#100|6000124#680</t>
+          <t>16#816|19#17|4#2000|70034#2|72001#100|6000124#680</t>
         </is>
       </c>
       <c r="M342" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#2000|70034#2|72001#100</t>
+          <t>16#816|19#17|4#2000|70034#2|72001#100</t>
         </is>
       </c>
       <c r="Q342" s="0" t="n">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="L343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#37|81114#2|6000088#1|14#5000000|6000124#980</t>
+          <t>16#1127|19#27|81114#2|6000088#1|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#37|81114#2|6000088#1|14#5000000</t>
+          <t>16#1127|19#27|81114#2|6000088#1|14#5000000</t>
         </is>
       </c>
       <c r="Q343" s="0" t="n">
@@ -29012,12 +29012,12 @@
       </c>
       <c r="L345" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#2000|18101#10|61#2|6000124#680</t>
+          <t>16#816|19#17|4#2000|18101#10|61#2|6000124#680</t>
         </is>
       </c>
       <c r="M345" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#2000|18101#10|61#2</t>
+          <t>16#816|19#17|4#2000|18101#10|61#2</t>
         </is>
       </c>
       <c r="Q345" s="0" t="n">
@@ -29255,12 +29255,12 @@
       </c>
       <c r="L348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#38|17012#30|17011#120|17009#300|6000124#1280</t>
+          <t>16#1472|19#37|17012#30|17011#120|17009#300|6000124#1280</t>
         </is>
       </c>
       <c r="M348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#38|17012#30|17011#120|17009#300</t>
+          <t>16#1472|19#37|17012#30|17011#120|17009#300</t>
         </is>
       </c>
       <c r="Q348" s="0" t="n">
@@ -29336,12 +29336,12 @@
       </c>
       <c r="L349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#27|4#2000|6000110#2000|6000124#980</t>
+          <t>16#1127|20#8|19#19|4#2000|6000110#2000|6000124#980</t>
         </is>
       </c>
       <c r="M349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#27|4#2000|6000110#2000</t>
+          <t>16#1127|20#8|19#19|4#2000|6000110#2000</t>
         </is>
       </c>
       <c r="Q349" s="0" t="n">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="L350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#38|6000097#30|6000098#120|6000092#120|6000124#1280</t>
+          <t>16#1472|19#37|6000097#30|6000098#120|6000092#120|6000124#1280</t>
         </is>
       </c>
       <c r="M350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#38|6000097#30|6000098#120|6000092#120</t>
+          <t>16#1472|19#37|6000097#30|6000098#120|6000092#120</t>
         </is>
       </c>
       <c r="Q350" s="0" t="n">
@@ -29498,12 +29498,12 @@
       </c>
       <c r="L351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#27|60403#1|60402#1|6000124#980</t>
+          <t>16#1127|20#8|19#19|60403#1|60402#1|6000124#980</t>
         </is>
       </c>
       <c r="M351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#27|60403#1|60402#1</t>
+          <t>16#1127|20#8|19#19|60403#1|60402#1</t>
         </is>
       </c>
       <c r="Q351" s="0" t="n">
@@ -29660,12 +29660,12 @@
       </c>
       <c r="L353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#40|60403#1|60402#2|6000124#1280</t>
+          <t>16#1472|20#10|19#27|60403#1|60402#2|6000124#1280</t>
         </is>
       </c>
       <c r="M353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#40|60403#1|60402#2</t>
+          <t>16#1472|20#10|19#27|60403#1|60402#2</t>
         </is>
       </c>
       <c r="Q353" s="0" t="n">
@@ -29906,12 +29906,12 @@
       </c>
       <c r="L356" s="0" t="inlineStr">
         <is>
-          <t>16#240|19#5|60100#1|6000124#120</t>
+          <t>16#240|19#2|60100#1|6000124#120</t>
         </is>
       </c>
       <c r="M356" s="0" t="inlineStr">
         <is>
-          <t>16#240|19#5|60100#1</t>
+          <t>16#240|19#2|60100#1</t>
         </is>
       </c>
       <c r="Q356" s="0" t="n">
@@ -29990,12 +29990,12 @@
       </c>
       <c r="L357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#7|60103#1|6000124#300</t>
+          <t>16#600|19#6|60103#1|6000124#300</t>
         </is>
       </c>
       <c r="M357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#7|60103#1</t>
+          <t>16#600|19#6|60103#1</t>
         </is>
       </c>
       <c r="Q357" s="0" t="n">
@@ -37224,12 +37224,12 @@
       </c>
       <c r="L436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#18|19#10|60430#3|6000124#980</t>
+          <t>16#1127|50007#17|19#10|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#18|19#10|60430#3</t>
+          <t>16#1127|50007#17|19#10|60430#3</t>
         </is>
       </c>
       <c r="Q436" s="0" t="n">
@@ -39716,12 +39716,12 @@
       </c>
       <c r="L464" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#2|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M464" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1</t>
+          <t>16#360|50007#5|19#2|60430#1</t>
         </is>
       </c>
       <c r="Q464" s="0" t="n">
@@ -40873,12 +40873,12 @@
       </c>
       <c r="L477" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#2|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M477" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1</t>
+          <t>16#360|50007#5|19#2|60430#1</t>
         </is>
       </c>
       <c r="Q477" s="0" t="n">
@@ -42119,12 +42119,12 @@
       </c>
       <c r="L491" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#2|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M491" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1</t>
+          <t>16#360|50007#5|19#2|60430#1</t>
         </is>
       </c>
       <c r="Q491" s="0" t="n">
@@ -43276,12 +43276,12 @@
       </c>
       <c r="L504" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1|6000124#300</t>
+          <t>16#360|50007#5|19#2|60430#1|6000124#300</t>
         </is>
       </c>
       <c r="M504" s="0" t="inlineStr">
         <is>
-          <t>16#360|50007#5|19#7|60430#1</t>
+          <t>16#360|50007#5|19#2|60430#1</t>
         </is>
       </c>
       <c r="Q504" s="0" t="n">
@@ -43988,12 +43988,12 @@
       </c>
       <c r="L512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#13|14#1000000|6000124#500</t>
+          <t>16#1000|81113#2|19#9|14#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#13|14#1000000</t>
+          <t>16#1000|81113#2|19#9|14#1000000</t>
         </is>
       </c>
       <c r="Q512" s="0" t="n">
@@ -44522,12 +44522,12 @@
       </c>
       <c r="L518" s="0" t="inlineStr">
         <is>
-          <t>16#360|81002#1|19#5|14#1000000|6000124#180</t>
+          <t>16#360|81002#1|19#2|14#1000000|6000124#180</t>
         </is>
       </c>
       <c r="M518" s="0" t="inlineStr">
         <is>
-          <t>16#360|81002#1|19#5|14#1000000</t>
+          <t>16#360|81002#1|19#2|14#1000000</t>
         </is>
       </c>
       <c r="Q518" s="0" t="n">
@@ -44789,12 +44789,12 @@
       </c>
       <c r="L521" s="0" t="inlineStr">
         <is>
-          <t>16#600|81002#1|19#13|14#1000000|6000124#300</t>
+          <t>16#430|81002#1|19#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M521" s="0" t="inlineStr">
         <is>
-          <t>16#600|81002#1|19#13|14#1000000</t>
+          <t>16#430|81002#1|19#6|14#1000000</t>
         </is>
       </c>
       <c r="Q521" s="0" t="n">
@@ -45056,12 +45056,12 @@
       </c>
       <c r="L524" s="0" t="inlineStr">
         <is>
-          <t>16#600|81113#2|19#13|14#1000000|6000124#300</t>
+          <t>16#430|81113#2|19#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M524" s="0" t="inlineStr">
         <is>
-          <t>16#600|81113#2|19#13|14#1000000</t>
+          <t>16#430|81113#2|19#6|14#1000000</t>
         </is>
       </c>
       <c r="Q524" s="0" t="n">
@@ -46020,12 +46020,12 @@
       </c>
       <c r="L535" s="0" t="inlineStr">
         <is>
-          <t>16#120|50007#1|19#1|14#200000|6000124#60</t>
+          <t>16#120|50007#1|14#200000|6000124#60</t>
         </is>
       </c>
       <c r="M535" s="0" t="inlineStr">
         <is>
-          <t>16#120|50007#1|19#1|14#200000</t>
+          <t>16#120|50007#1|14#200000</t>
         </is>
       </c>
       <c r="Q535" s="0" t="n">
@@ -46109,12 +46109,12 @@
       </c>
       <c r="L536" s="0" t="inlineStr">
         <is>
-          <t>16#240|50007#2|19#2|14#400000|6000124#120</t>
+          <t>16#170|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M536" s="0" t="inlineStr">
         <is>
-          <t>16#240|50007#2|19#2|14#400000</t>
+          <t>16#170|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q536" s="0" t="n">
@@ -46198,12 +46198,12 @@
       </c>
       <c r="L537" s="0" t="inlineStr">
         <is>
-          <t>16#600|50007#5|19#8|14#1000000|6000124#300</t>
+          <t>16#430|50007#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M537" s="0" t="inlineStr">
         <is>
-          <t>16#600|50007#5|19#8|14#1000000</t>
+          <t>16#430|50007#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q537" s="0" t="n">
@@ -46821,12 +46821,12 @@
       </c>
       <c r="L544" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000|6000124#60</t>
+          <t>16#120|87#1|14#200000|6000124#60</t>
         </is>
       </c>
       <c r="M544" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000</t>
+          <t>16#120|87#1|14#200000</t>
         </is>
       </c>
       <c r="Q544" s="0" t="n">
@@ -46910,12 +46910,12 @@
       </c>
       <c r="L545" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000|6000124#120</t>
+          <t>16#170|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M545" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000</t>
+          <t>16#170|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q545" s="0" t="n">
@@ -46999,12 +46999,12 @@
       </c>
       <c r="L546" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
+          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M546" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000</t>
+          <t>16#430|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q546" s="0" t="n">
@@ -47177,12 +47177,12 @@
       </c>
       <c r="L548" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50007#2|14#400000|6000124#120</t>
+          <t>16#170|50005#2|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M548" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50007#2|14#400000</t>
+          <t>16#170|50005#2|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q548" s="0" t="n">
@@ -47266,12 +47266,12 @@
       </c>
       <c r="L549" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#7|14#1000000|6000124#300</t>
+          <t>16#430|50005#5|50007#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M549" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#7|14#1000000</t>
+          <t>16#430|50005#5|50007#6|14#1000000</t>
         </is>
       </c>
       <c r="Q549" s="0" t="n">
@@ -47355,12 +47355,12 @@
       </c>
       <c r="L550" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000|6000124#60</t>
+          <t>16#120|87#1|14#200000|6000124#60</t>
         </is>
       </c>
       <c r="M550" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000</t>
+          <t>16#120|87#1|14#200000</t>
         </is>
       </c>
       <c r="Q550" s="0" t="n">
@@ -47444,12 +47444,12 @@
       </c>
       <c r="L551" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000|6000124#120</t>
+          <t>16#170|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M551" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000</t>
+          <t>16#170|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q551" s="0" t="n">
@@ -47533,12 +47533,12 @@
       </c>
       <c r="L552" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
+          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M552" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000</t>
+          <t>16#430|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q552" s="0" t="n">
@@ -47889,12 +47889,12 @@
       </c>
       <c r="L556" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000|6000124#60</t>
+          <t>16#120|87#1|14#200000|6000124#60</t>
         </is>
       </c>
       <c r="M556" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000</t>
+          <t>16#120|87#1|14#200000</t>
         </is>
       </c>
       <c r="Q556" s="0" t="n">
@@ -47978,12 +47978,12 @@
       </c>
       <c r="L557" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000|6000124#120</t>
+          <t>16#170|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M557" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000</t>
+          <t>16#170|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q557" s="0" t="n">
@@ -48067,12 +48067,12 @@
       </c>
       <c r="L558" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
+          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M558" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000</t>
+          <t>16#430|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q558" s="0" t="n">
@@ -48245,12 +48245,12 @@
       </c>
       <c r="L560" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50007#2|14#400000|6000124#120</t>
+          <t>16#170|50005#2|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M560" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50007#2|14#400000</t>
+          <t>16#170|50005#2|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q560" s="0" t="n">
@@ -48334,12 +48334,12 @@
       </c>
       <c r="L561" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#7|14#1000000|6000124#300</t>
+          <t>16#430|50005#5|50007#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M561" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50007#7|14#1000000</t>
+          <t>16#430|50005#5|50007#6|14#1000000</t>
         </is>
       </c>
       <c r="Q561" s="0" t="n">
@@ -48423,12 +48423,12 @@
       </c>
       <c r="L562" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000|6000124#60</t>
+          <t>16#120|87#1|14#200000|6000124#60</t>
         </is>
       </c>
       <c r="M562" s="0" t="inlineStr">
         <is>
-          <t>16#120|87#1|19#1|14#200000</t>
+          <t>16#120|87#1|14#200000</t>
         </is>
       </c>
       <c r="Q562" s="0" t="n">
@@ -48512,12 +48512,12 @@
       </c>
       <c r="L563" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000|6000124#120</t>
+          <t>16#170|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M563" s="0" t="inlineStr">
         <is>
-          <t>16#240|87#2|19#2|14#400000</t>
+          <t>16#170|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q563" s="0" t="n">
@@ -48601,12 +48601,12 @@
       </c>
       <c r="L564" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000|6000124#300</t>
+          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M564" s="0" t="inlineStr">
         <is>
-          <t>16#600|87#5|19#8|14#1000000</t>
+          <t>16#430|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q564" s="0" t="n">
@@ -50381,12 +50381,12 @@
       </c>
       <c r="L584" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#30|72004#120|19#26|6000124#980</t>
+          <t>16#1960|72005#30|72004#120|19#23|6000124#980</t>
         </is>
       </c>
       <c r="M584" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72005#30|72004#120|19#26</t>
+          <t>16#1960|72005#30|72004#120|19#23</t>
         </is>
       </c>
       <c r="Q584" s="0" t="n">
@@ -50470,12 +50470,12 @@
       </c>
       <c r="L585" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72001#1000|72003#5|19#26|6000124#980</t>
+          <t>16#1960|72001#1000|72003#5|19#23|6000124#980</t>
         </is>
       </c>
       <c r="M585" s="0" t="inlineStr">
         <is>
-          <t>16#1960|72001#1000|72003#5|19#26</t>
+          <t>16#1960|72001#1000|72003#5|19#23</t>
         </is>
       </c>
       <c r="Q585" s="0" t="n">
@@ -51627,12 +51627,12 @@
       </c>
       <c r="L598" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#25|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000|6000124#300</t>
+          <t>16#600|19#6|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000|6000124#300</t>
         </is>
       </c>
       <c r="M598" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#25|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000</t>
+          <t>16#600|19#6|4#1000|70034#1|80#6|60#10|23#3|14#100000|3#500000</t>
         </is>
       </c>
       <c r="Q598" s="0" t="n">
@@ -51716,12 +51716,12 @@
       </c>
       <c r="L599" s="0" t="inlineStr">
         <is>
-          <t>16#1360|19#38|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000|6000124#680</t>
+          <t>16#1360|19#15|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000|6000124#680</t>
         </is>
       </c>
       <c r="M599" s="0" t="inlineStr">
         <is>
-          <t>16#1360|19#38|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000</t>
+          <t>16#1360|19#15|4#2000|18101#10|61#2|60#12|23#5|14#500000|3#1000000</t>
         </is>
       </c>
       <c r="Q599" s="0" t="n">
@@ -51805,12 +51805,12 @@
       </c>
       <c r="L600" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
+          <t>16#1960|19#23|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
         </is>
       </c>
       <c r="M600" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
+          <t>16#1960|19#23|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q600" s="0" t="n">
@@ -51894,12 +51894,12 @@
       </c>
       <c r="L601" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
+          <t>16#1960|19#23|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000|6000124#980</t>
         </is>
       </c>
       <c r="M601" s="0" t="inlineStr">
         <is>
-          <t>16#1960|19#50|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
+          <t>16#1960|19#23|6000088#1|81114#2|61#1|60#12|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q601" s="0" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="L602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#63|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2560|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#63|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2560|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q602" s="0" t="n">
@@ -52072,12 +52072,12 @@
       </c>
       <c r="L603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#63|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2560|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#63|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2560|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q603" s="0" t="n">
@@ -52517,12 +52517,12 @@
       </c>
       <c r="L608" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000|6000124#300</t>
+          <t>16#360|19#7|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000|6000124#300</t>
         </is>
       </c>
       <c r="M608" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000</t>
+          <t>16#360|19#7|4#500|72001#50|80#5|60#12|23#3|14#500000|3#500000</t>
         </is>
       </c>
       <c r="Q608" s="0" t="n">
@@ -52606,12 +52606,12 @@
       </c>
       <c r="L609" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000|6000124#680</t>
+          <t>16#816|19#17|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000|6000124#680</t>
         </is>
       </c>
       <c r="M609" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#25|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000</t>
+          <t>16#816|19#17|4#1000|72001#100|80#10|60#24|23#6|14#1000000|3#1000000</t>
         </is>
       </c>
       <c r="Q609" s="0" t="n">
@@ -52695,12 +52695,12 @@
       </c>
       <c r="L610" s="0" t="inlineStr">
         <is>
-          <t>16#1176|19#37|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
+          <t>16#1176|19#27|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000|6000124#980</t>
         </is>
       </c>
       <c r="M610" s="0" t="inlineStr">
         <is>
-          <t>16#1176|19#37|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
+          <t>16#1176|19#27|4#1500|72001#150|80#15|60#30|23#10|14#2000000|3#2000000</t>
         </is>
       </c>
       <c r="Q610" s="0" t="n">
@@ -52784,12 +52784,12 @@
       </c>
       <c r="L611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#50|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
+          <t>16#1555|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#50|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
+          <t>16#1555|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
         </is>
       </c>
       <c r="Q611" s="0" t="n">
@@ -52873,12 +52873,12 @@
       </c>
       <c r="L612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#64|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
+          <t>16#2475|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
         </is>
       </c>
       <c r="M612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#64|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
+          <t>16#2475|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
         </is>
       </c>
       <c r="Q612" s="0" t="n">
@@ -52962,12 +52962,12 @@
       </c>
       <c r="L613" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#103|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
+          <t>16#4264|20#10|19#96|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000|6000124#3280</t>
         </is>
       </c>
       <c r="M613" s="0" t="inlineStr">
         <is>
-          <t>16#4264|20#10|19#103|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
+          <t>16#4264|20#10|19#96|4#5000|6000110#5000|61#3|60#36|14#20000000|3#2000000</t>
         </is>
       </c>
       <c r="Q613" s="0" t="n">
@@ -53496,12 +53496,12 @@
       </c>
       <c r="L619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
+          <t>16#1000|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q619" s="0" t="n">
@@ -53585,12 +53585,12 @@
       </c>
       <c r="L620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q620" s="0" t="n">
@@ -53674,12 +53674,12 @@
       </c>
       <c r="L621" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M621" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q621" s="0" t="n">
@@ -53763,12 +53763,12 @@
       </c>
       <c r="L622" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M622" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#19|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q622" s="0" t="n">
@@ -53941,12 +53941,12 @@
       </c>
       <c r="L624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#19|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#600|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#19|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#600|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q624" s="0" t="n">
@@ -60408,12 +60408,12 @@
       </c>
       <c r="L697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#38|3#2000000|14#4000000|6000124#1280</t>
+          <t>16#1555|19#36|3#2000000|14#4000000|6000124#1280</t>
         </is>
       </c>
       <c r="M697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#38|3#2000000|14#4000000</t>
+          <t>16#1555|19#36|3#2000000|14#4000000</t>
         </is>
       </c>
       <c r="Q697" s="0" t="n">
@@ -66330,12 +66330,12 @@
       </c>
       <c r="L765" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M765" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q765" s="0" t="n">
@@ -66417,12 +66417,12 @@
       </c>
       <c r="L766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q766" s="0" t="n">
@@ -67287,12 +67287,12 @@
       </c>
       <c r="L776" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M776" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q776" s="0" t="n">
@@ -67374,12 +67374,12 @@
       </c>
       <c r="L777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q777" s="0" t="n">
@@ -68244,12 +68244,12 @@
       </c>
       <c r="L787" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M787" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q787" s="0" t="n">
@@ -68331,12 +68331,12 @@
       </c>
       <c r="L788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q788" s="0" t="n">
@@ -69201,12 +69201,12 @@
       </c>
       <c r="L798" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M798" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q798" s="0" t="n">
@@ -69288,12 +69288,12 @@
       </c>
       <c r="L799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q799" s="0" t="n">
@@ -70158,12 +70158,12 @@
       </c>
       <c r="L809" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M809" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q809" s="0" t="n">
@@ -70245,12 +70245,12 @@
       </c>
       <c r="L810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q810" s="0" t="n">
@@ -71115,12 +71115,12 @@
       </c>
       <c r="L820" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000|6000124#300</t>
+          <t>16#360|19#7|4#1000|6000110#1000|6000124#300</t>
         </is>
       </c>
       <c r="M820" s="0" t="inlineStr">
         <is>
-          <t>16#360|19#12|4#1000|6000110#1000</t>
+          <t>16#360|19#7|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q820" s="0" t="n">
@@ -71202,12 +71202,12 @@
       </c>
       <c r="L821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000|6000124#680</t>
+          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#19|4#1000|6000110#1000</t>
+          <t>16#816|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q821" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -21914,12 +21914,12 @@
       </c>
       <c r="L264" s="0" t="inlineStr">
         <is>
-          <t>16#930|19#3|65#1500|6000124#980</t>
+          <t>16#820|19#3|65#1500|6000124#980</t>
         </is>
       </c>
       <c r="M264" s="0" t="inlineStr">
         <is>
-          <t>16#930|19#3|65#1500</t>
+          <t>16#820|19#3|65#1500</t>
         </is>
       </c>
       <c r="Q264" s="0" t="n">
@@ -22005,12 +22005,12 @@
       </c>
       <c r="L265" s="0" t="inlineStr">
         <is>
-          <t>16#6480|20#12|65#10000|6000124#6480</t>
+          <t>16#7150|20#12|65#10000|6000124#6480</t>
         </is>
       </c>
       <c r="M265" s="0" t="inlineStr">
         <is>
-          <t>16#6480|20#12|65#10000</t>
+          <t>16#7150|20#12|65#10000</t>
         </is>
       </c>
       <c r="Q265" s="0" t="n">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="AM273" s="0" t="inlineStr">
         <is>
-          <t>3#601|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AP273" s="0" t="n">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="AM274" s="0" t="inlineStr">
         <is>
-          <t>3#602|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AP274" s="0" t="n">
@@ -22896,7 +22896,7 @@
       </c>
       <c r="AM275" s="0" t="inlineStr">
         <is>
-          <t>3#603|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AP275" s="0" t="n">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="AM276" s="0" t="inlineStr">
         <is>
-          <t>3#604|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AP276" s="0" t="n">
@@ -23091,12 +23091,12 @@
       </c>
       <c r="L278" s="0" t="inlineStr">
         <is>
-          <t>16#170|81150#1|19#2|4#200|3#200000|6000124#120</t>
+          <t>16#240|81150#1|19#2|4#200|3#200000|6000124#120</t>
         </is>
       </c>
       <c r="M278" s="0" t="inlineStr">
         <is>
-          <t>16#50|81150#1|19#2|4#200|3#200000</t>
+          <t>16#120|81150#1|19#2|4#200|3#200000</t>
         </is>
       </c>
       <c r="Q278" s="0" t="n">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="L279" s="0" t="inlineStr">
         <is>
-          <t>16#360|81150#2|19#2|4#300|3#300000|6000124#180</t>
+          <t>16#580|81150#2|19#2|4#300|3#300000|6000124#180</t>
         </is>
       </c>
       <c r="M279" s="0" t="inlineStr">
         <is>
-          <t>16#180|81150#2|19#2|4#300|3#300000</t>
+          <t>16#400|81150#2|19#2|4#300|3#300000</t>
         </is>
       </c>
       <c r="Q279" s="0" t="n">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="L283" s="0" t="inlineStr">
         <is>
-          <t>16#170|81150#1|19#2|17009#30|6000110#300|6000124#120</t>
+          <t>16#240|81150#1|19#2|17009#30|6000110#300|6000124#120</t>
         </is>
       </c>
       <c r="M283" s="0" t="inlineStr">
         <is>
-          <t>16#50|81150#1|19#2|17009#30|6000110#300</t>
+          <t>16#120|81150#1|19#2|17009#30|6000110#300</t>
         </is>
       </c>
       <c r="Q283" s="0" t="n">
@@ -23628,12 +23628,12 @@
       </c>
       <c r="L284" s="0" t="inlineStr">
         <is>
-          <t>16#360|81150#2|19#2|17009#40|6000110#500|6000124#180</t>
+          <t>16#580|81150#2|19#2|17009#40|6000110#500|6000124#180</t>
         </is>
       </c>
       <c r="M284" s="0" t="inlineStr">
         <is>
-          <t>16#180|81150#2|19#2|17009#40|6000110#500</t>
+          <t>16#400|81150#2|19#2|17009#40|6000110#500</t>
         </is>
       </c>
       <c r="Q284" s="0" t="n">
@@ -26742,12 +26742,12 @@
       </c>
       <c r="L319" s="0" t="inlineStr">
         <is>
-          <t>82001#1|16#360|20#5|4#800|6000124#300</t>
+          <t>82001#1|16#390|20#5|4#800|6000124#300</t>
         </is>
       </c>
       <c r="M319" s="0" t="inlineStr">
         <is>
-          <t>82001#1|16#360|20#5|4#800</t>
+          <t>82001#1|16#390|20#5|4#800</t>
         </is>
       </c>
       <c r="Q319" s="0" t="inlineStr">
@@ -26848,12 +26848,12 @@
       </c>
       <c r="L320" s="0" t="inlineStr">
         <is>
-          <t>16#360|100#1|10423#2|10428#2|6000124#300|19#5</t>
+          <t>16#390|100#1|10423#2|10428#2|6000124#300|19#5</t>
         </is>
       </c>
       <c r="M320" s="0" t="inlineStr">
         <is>
-          <t>16#360|100#1|10423#2|10428#2|19#5</t>
+          <t>16#390|100#1|10423#2|10428#2|19#5</t>
         </is>
       </c>
       <c r="Q320" s="0" t="inlineStr">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="L343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#27|81114#2|6000088#1|14#5000000|6000124#980</t>
+          <t>16#1047|19#27|81114#2|6000088#1|14#5000000|6000124#980</t>
         </is>
       </c>
       <c r="M343" s="0" t="inlineStr">
         <is>
-          <t>16#1127|19#27|81114#2|6000088#1|14#5000000</t>
+          <t>16#1047|19#27|81114#2|6000088#1|14#5000000</t>
         </is>
       </c>
       <c r="Q343" s="0" t="n">
@@ -28931,12 +28931,12 @@
       </c>
       <c r="L344" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60433#1|20#5|19#83|61#5|6000124#3280</t>
+          <t>16#4024|60433#1|20#5|19#83|61#5|6000124#3280</t>
         </is>
       </c>
       <c r="M344" s="0" t="inlineStr">
         <is>
-          <t>16#3674|60433#1|20#5|19#83|61#5</t>
+          <t>16#4024|60433#1|20#5|19#83|61#5</t>
         </is>
       </c>
       <c r="Q344" s="0" t="n">
@@ -29093,12 +29093,12 @@
       </c>
       <c r="L346" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|6000124#1280|19#30</t>
+          <t>16#982|60417#1|6000085#20|18102#10|4#5000|6000124#1280|19#30</t>
         </is>
       </c>
       <c r="M346" s="0" t="inlineStr">
         <is>
-          <t>16#1472|60417#1|6000085#20|18102#10|4#5000|19#30</t>
+          <t>16#982|60417#1|6000085#20|18102#10|4#5000|19#30</t>
         </is>
       </c>
       <c r="Q346" s="0" t="n">
@@ -29174,12 +29174,12 @@
       </c>
       <c r="L347" s="0" t="inlineStr">
         <is>
-          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|6000124#2880|19#73</t>
+          <t>16#4476|6000089#1|6000111#30|6000112#100|6000110#8000|6000124#2880|19#73</t>
         </is>
       </c>
       <c r="M347" s="0" t="inlineStr">
         <is>
-          <t>16#3226|6000089#1|6000111#30|6000112#100|6000110#8000|19#73</t>
+          <t>16#4476|6000089#1|6000111#30|6000112#100|6000110#8000|19#73</t>
         </is>
       </c>
       <c r="Q347" s="0" t="n">
@@ -29255,12 +29255,12 @@
       </c>
       <c r="L348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#37|17012#30|17011#120|17009#300|6000124#1280</t>
+          <t>16#982|19#37|17012#30|17011#120|17009#300|6000124#1280</t>
         </is>
       </c>
       <c r="M348" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#37|17012#30|17011#120|17009#300</t>
+          <t>16#982|19#37|17012#30|17011#120|17009#300</t>
         </is>
       </c>
       <c r="Q348" s="0" t="n">
@@ -29336,12 +29336,12 @@
       </c>
       <c r="L349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#19|4#2000|6000110#2000|6000124#980</t>
+          <t>16#1047|20#8|19#19|4#2000|6000110#2000|6000124#980</t>
         </is>
       </c>
       <c r="M349" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#19|4#2000|6000110#2000</t>
+          <t>16#1047|20#8|19#19|4#2000|6000110#2000</t>
         </is>
       </c>
       <c r="Q349" s="0" t="n">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="L350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#37|6000097#30|6000098#120|6000092#120|6000124#1280</t>
+          <t>16#982|19#37|6000097#30|6000098#120|6000092#120|6000124#1280</t>
         </is>
       </c>
       <c r="M350" s="0" t="inlineStr">
         <is>
-          <t>16#1472|19#37|6000097#30|6000098#120|6000092#120</t>
+          <t>16#982|19#37|6000097#30|6000098#120|6000092#120</t>
         </is>
       </c>
       <c r="Q350" s="0" t="n">
@@ -29498,12 +29498,12 @@
       </c>
       <c r="L351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#19|60403#1|60402#1|6000124#980</t>
+          <t>16#1047|20#8|19#19|60403#1|60402#1|6000124#980</t>
         </is>
       </c>
       <c r="M351" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#8|19#19|60403#1|60402#1</t>
+          <t>16#1047|20#8|19#19|60403#1|60402#1</t>
         </is>
       </c>
       <c r="Q351" s="0" t="n">
@@ -29579,12 +29579,12 @@
       </c>
       <c r="L352" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|6000124#1980|19#49</t>
+          <t>16#3338|99000#8|10442#25|10441#150|6000110#5000|6000124#1980|19#49</t>
         </is>
       </c>
       <c r="M352" s="0" t="inlineStr">
         <is>
-          <t>16#2218|99000#8|10442#25|10441#150|6000110#5000|19#49</t>
+          <t>16#3338|99000#8|10442#25|10441#150|6000110#5000|19#49</t>
         </is>
       </c>
       <c r="Q352" s="0" t="n">
@@ -29660,12 +29660,12 @@
       </c>
       <c r="L353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#27|60403#1|60402#2|6000124#1280</t>
+          <t>16#982|20#10|19#27|60403#1|60402#2|6000124#1280</t>
         </is>
       </c>
       <c r="M353" s="0" t="inlineStr">
         <is>
-          <t>16#1472|20#10|19#27|60403#1|60402#2</t>
+          <t>16#982|20#10|19#27|60403#1|60402#2</t>
         </is>
       </c>
       <c r="Q353" s="0" t="n">
@@ -29741,12 +29741,12 @@
       </c>
       <c r="L354" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#49|10423#5|10428#5|10424#30|6000124#1980</t>
+          <t>16#3338|20#49|10423#5|10428#5|10424#30|6000124#1980</t>
         </is>
       </c>
       <c r="M354" s="0" t="inlineStr">
         <is>
-          <t>16#2218|20#49|10423#5|10428#5|10424#30</t>
+          <t>16#3338|20#49|10423#5|10428#5|10424#30</t>
         </is>
       </c>
       <c r="Q354" s="0" t="n">
@@ -29990,12 +29990,12 @@
       </c>
       <c r="L357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#6|60103#1|6000124#300</t>
+          <t>16#540|19#6|60103#1|6000124#300</t>
         </is>
       </c>
       <c r="M357" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#6|60103#1</t>
+          <t>16#540|19#6|60103#1</t>
         </is>
       </c>
       <c r="Q357" s="0" t="n">
@@ -30074,12 +30074,12 @@
       </c>
       <c r="L358" s="0" t="inlineStr">
         <is>
-          <t>16#1360|81148#50|19#13|6000124#680</t>
+          <t>16#1370|81148#50|19#13|6000124#680</t>
         </is>
       </c>
       <c r="M358" s="0" t="inlineStr">
         <is>
-          <t>16#1360|81148#50|19#13</t>
+          <t>16#1370|81148#50|19#13</t>
         </is>
       </c>
       <c r="Q358" s="0" t="n">
@@ -30158,12 +30158,12 @@
       </c>
       <c r="L359" s="0" t="inlineStr">
         <is>
-          <t>16#1960|14#20000000|14#10000000|14#10000000|6000124#980|19#18</t>
+          <t>16#2130|14#20000000|14#10000000|14#10000000|6000124#980|19#18</t>
         </is>
       </c>
       <c r="M359" s="0" t="inlineStr">
         <is>
-          <t>16#1960|14#20000000|14#10000000|14#10000000|19#18</t>
+          <t>16#2130|14#20000000|14#10000000|14#10000000|19#18</t>
         </is>
       </c>
       <c r="Q359" s="0" t="n">
@@ -33939,7 +33939,7 @@
       </c>
       <c r="AM399" s="0" t="inlineStr">
         <is>
-          <t>3#22003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO399" s="0" t="inlineStr">
@@ -34028,7 +34028,7 @@
       </c>
       <c r="AM400" s="0" t="inlineStr">
         <is>
-          <t>3#22003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO400" s="0" t="inlineStr">
@@ -34117,7 +34117,7 @@
       </c>
       <c r="AM401" s="0" t="inlineStr">
         <is>
-          <t>3#22003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO401" s="0" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="AM423" s="0" t="inlineStr">
         <is>
-          <t>3#35003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO423" s="0" t="inlineStr">
@@ -36188,7 +36188,7 @@
       </c>
       <c r="AM424" s="0" t="inlineStr">
         <is>
-          <t>3#35003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO424" s="0" t="inlineStr">
@@ -36277,7 +36277,7 @@
       </c>
       <c r="AM425" s="0" t="inlineStr">
         <is>
-          <t>3#35003</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AO425" s="0" t="inlineStr">
@@ -37135,12 +37135,12 @@
       </c>
       <c r="L435" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#1|6000124#680</t>
+          <t>16#1226|50007#13|20#1|60430#1|6000124#680</t>
         </is>
       </c>
       <c r="M435" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#1</t>
+          <t>16#1226|50007#13|20#1|60430#1</t>
         </is>
       </c>
       <c r="Q435" s="0" t="n">
@@ -37224,12 +37224,12 @@
       </c>
       <c r="L436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|19#10|60430#3|6000124#980</t>
+          <t>16#1367|50007#16|19#10|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M436" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#17|19#10|60430#3</t>
+          <t>16#1367|50007#16|19#10|60430#3</t>
         </is>
       </c>
       <c r="Q436" s="0" t="n">
@@ -37758,12 +37758,12 @@
       </c>
       <c r="L442" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#14|60403#1|6000110#1000|6000124#680</t>
+          <t>16#1226|50007#14|60403#1|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M442" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#14|60403#1|6000110#1000</t>
+          <t>16#1226|50007#14|60403#1|6000110#1000</t>
         </is>
       </c>
       <c r="Q442" s="0" t="n">
@@ -37847,12 +37847,12 @@
       </c>
       <c r="L443" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|6000110#1500|6000124#980</t>
+          <t>16#1367|50007#22|60402#2|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M443" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|6000110#1500</t>
+          <t>16#1367|50007#22|60402#2|6000110#1500</t>
         </is>
       </c>
       <c r="Q443" s="0" t="n">
@@ -37936,12 +37936,12 @@
       </c>
       <c r="L444" s="0" t="inlineStr">
         <is>
-          <t>16#1980|50007#27|60403#3|6000110#2000|6000124#1980</t>
+          <t>16#2010|50007#27|60403#3|6000110#2000|6000124#1980</t>
         </is>
       </c>
       <c r="M444" s="0" t="inlineStr">
         <is>
-          <t>16#1980|50007#27|60403#3|6000110#2000</t>
+          <t>16#2010|50007#27|60403#3|6000110#2000</t>
         </is>
       </c>
       <c r="Q444" s="0" t="n">
@@ -38203,12 +38203,12 @@
       </c>
       <c r="L447" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1002#20|20#30|6000110#2000|6000124#1280</t>
+          <t>16#1502|1002#20|20#30|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M447" s="0" t="inlineStr">
         <is>
-          <t>16#1472|1002#20|20#30|6000110#2000</t>
+          <t>16#1502|1002#20|20#30|6000110#2000</t>
         </is>
       </c>
       <c r="Q447" s="0" t="n">
@@ -38470,12 +38470,12 @@
       </c>
       <c r="L450" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
+          <t>16#1226|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M450" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000</t>
+          <t>16#1226|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q450" s="0" t="n">
@@ -38559,12 +38559,12 @@
       </c>
       <c r="L451" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
+          <t>16#1367|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M451" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500</t>
+          <t>16#1367|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q451" s="0" t="n">
@@ -38648,12 +38648,12 @@
       </c>
       <c r="L452" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1502|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M452" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000</t>
+          <t>16#1502|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q452" s="0" t="n">
@@ -39093,12 +39093,12 @@
       </c>
       <c r="L457" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
+          <t>16#1226|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M457" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000</t>
+          <t>16#1226|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q457" s="0" t="n">
@@ -39182,12 +39182,12 @@
       </c>
       <c r="L458" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
+          <t>16#1367|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M458" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500</t>
+          <t>16#1367|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q458" s="0" t="n">
@@ -39271,12 +39271,12 @@
       </c>
       <c r="L459" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1502|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M459" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000</t>
+          <t>16#1502|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q459" s="0" t="n">
@@ -39805,12 +39805,12 @@
       </c>
       <c r="L465" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
+          <t>16#1226|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M465" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2</t>
+          <t>16#1226|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q465" s="0" t="n">
@@ -39894,12 +39894,12 @@
       </c>
       <c r="L466" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
+          <t>16#1367|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M466" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3</t>
+          <t>16#1367|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q466" s="0" t="n">
@@ -40250,12 +40250,12 @@
       </c>
       <c r="L470" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
+          <t>16#1226|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M470" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000</t>
+          <t>16#1226|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q470" s="0" t="n">
@@ -40339,12 +40339,12 @@
       </c>
       <c r="L471" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
+          <t>16#1367|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M471" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500</t>
+          <t>16#1367|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q471" s="0" t="n">
@@ -40428,12 +40428,12 @@
       </c>
       <c r="L472" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1502|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M472" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000</t>
+          <t>16#1502|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q472" s="0" t="n">
@@ -40962,12 +40962,12 @@
       </c>
       <c r="L478" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
+          <t>16#1226|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M478" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2</t>
+          <t>16#1226|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q478" s="0" t="n">
@@ -41051,12 +41051,12 @@
       </c>
       <c r="L479" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
+          <t>16#1367|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M479" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3</t>
+          <t>16#1367|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q479" s="0" t="n">
@@ -41496,12 +41496,12 @@
       </c>
       <c r="L484" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
+          <t>16#1226|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M484" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000</t>
+          <t>16#1226|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q484" s="0" t="n">
@@ -41585,12 +41585,12 @@
       </c>
       <c r="L485" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
+          <t>16#1367|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M485" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500</t>
+          <t>16#1367|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q485" s="0" t="n">
@@ -41674,12 +41674,12 @@
       </c>
       <c r="L486" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1502|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M486" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000</t>
+          <t>16#1502|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q486" s="0" t="n">
@@ -42208,12 +42208,12 @@
       </c>
       <c r="L492" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
+          <t>16#1226|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M492" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2</t>
+          <t>16#1226|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q492" s="0" t="n">
@@ -42297,12 +42297,12 @@
       </c>
       <c r="L493" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
+          <t>16#1367|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M493" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3</t>
+          <t>16#1367|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q493" s="0" t="n">
@@ -42653,12 +42653,12 @@
       </c>
       <c r="L497" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000|6000124#680</t>
+          <t>16#1226|87#4|19#10|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M497" s="0" t="inlineStr">
         <is>
-          <t>16#816|87#4|19#10|6000110#1000</t>
+          <t>16#1226|87#4|19#10|6000110#1000</t>
         </is>
       </c>
       <c r="Q497" s="0" t="n">
@@ -42742,12 +42742,12 @@
       </c>
       <c r="L498" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500|6000124#980</t>
+          <t>16#1367|87#6|19#16|6000110#1500|6000124#980</t>
         </is>
       </c>
       <c r="M498" s="0" t="inlineStr">
         <is>
-          <t>16#1127|87#6|19#16|6000110#1500</t>
+          <t>16#1367|87#6|19#16|6000110#1500</t>
         </is>
       </c>
       <c r="Q498" s="0" t="n">
@@ -42831,12 +42831,12 @@
       </c>
       <c r="L499" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000|6000124#1280</t>
+          <t>16#1502|87#30|60403#2|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M499" s="0" t="inlineStr">
         <is>
-          <t>16#1472|87#30|60403#2|6000110#2000</t>
+          <t>16#1502|87#30|60403#2|6000110#2000</t>
         </is>
       </c>
       <c r="Q499" s="0" t="n">
@@ -43365,12 +43365,12 @@
       </c>
       <c r="L505" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2|6000124#680</t>
+          <t>16#1226|50007#13|20#1|60430#2|6000124#680</t>
         </is>
       </c>
       <c r="M505" s="0" t="inlineStr">
         <is>
-          <t>16#816|50007#13|20#1|60430#2</t>
+          <t>16#1226|50007#13|20#1|60430#2</t>
         </is>
       </c>
       <c r="Q505" s="0" t="n">
@@ -43454,12 +43454,12 @@
       </c>
       <c r="L506" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3|6000124#980</t>
+          <t>16#1367|50007#22|60402#2|60430#3|6000124#980</t>
         </is>
       </c>
       <c r="M506" s="0" t="inlineStr">
         <is>
-          <t>16#1127|50007#22|60402#2|60430#3</t>
+          <t>16#1367|50007#22|60402#2|60430#3</t>
         </is>
       </c>
       <c r="Q506" s="0" t="n">
@@ -43899,12 +43899,12 @@
       </c>
       <c r="L511" s="0" t="inlineStr">
         <is>
-          <t>16#360|81112#1|14#500000|3#1000000|6000124#180|19#2</t>
+          <t>16#580|81112#1|14#500000|3#1000000|6000124#180|19#2</t>
         </is>
       </c>
       <c r="M511" s="0" t="inlineStr">
         <is>
-          <t>16#360|81112#1|14#500000|3#1000000|19#2</t>
+          <t>16#580|81112#1|14#500000|3#1000000|19#2</t>
         </is>
       </c>
       <c r="Q511" s="0" t="n">
@@ -43988,12 +43988,12 @@
       </c>
       <c r="L512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#9|14#1000000|6000124#500</t>
+          <t>16#1290|81113#2|19#9|14#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M512" s="0" t="inlineStr">
         <is>
-          <t>16#1000|81113#2|19#9|14#1000000</t>
+          <t>16#1290|81113#2|19#9|14#1000000</t>
         </is>
       </c>
       <c r="Q512" s="0" t="n">
@@ -44166,12 +44166,12 @@
       </c>
       <c r="L514" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000127#10|6000110#200|14#500000|6000124#180|19#2</t>
+          <t>16#580|6000127#10|6000110#200|14#500000|6000124#180|19#2</t>
         </is>
       </c>
       <c r="M514" s="0" t="inlineStr">
         <is>
-          <t>16#360|6000127#10|6000110#200|14#500000|19#2</t>
+          <t>16#580|6000127#10|6000110#200|14#500000|19#2</t>
         </is>
       </c>
       <c r="Q514" s="0" t="n">
@@ -44255,12 +44255,12 @@
       </c>
       <c r="L515" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
+          <t>16#1290|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M515" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|19#7</t>
+          <t>16#1290|60435#1|6000110#1000|14#1000000|19#7</t>
         </is>
       </c>
       <c r="Q515" s="0" t="n">
@@ -44522,12 +44522,12 @@
       </c>
       <c r="L518" s="0" t="inlineStr">
         <is>
-          <t>16#360|81002#1|19#2|14#1000000|6000124#180</t>
+          <t>16#580|81002#1|19#2|14#1000000|6000124#180</t>
         </is>
       </c>
       <c r="M518" s="0" t="inlineStr">
         <is>
-          <t>16#360|81002#1|19#2|14#1000000</t>
+          <t>16#580|81002#1|19#2|14#1000000</t>
         </is>
       </c>
       <c r="Q518" s="0" t="n">
@@ -44611,12 +44611,12 @@
       </c>
       <c r="L519" s="0" t="inlineStr">
         <is>
-          <t>16#1000|99005#1|60431#1|14#2000000|6000124#500|19#7</t>
+          <t>16#1290|99005#1|60431#1|14#2000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M519" s="0" t="inlineStr">
         <is>
-          <t>16#1000|99005#1|60431#1|14#2000000|19#7</t>
+          <t>16#1290|99005#1|60431#1|14#2000000|19#7</t>
         </is>
       </c>
       <c r="Q519" s="0" t="n">
@@ -44789,12 +44789,12 @@
       </c>
       <c r="L521" s="0" t="inlineStr">
         <is>
-          <t>16#430|81002#1|19#6|14#1000000|6000124#300</t>
+          <t>16#380|81002#1|19#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M521" s="0" t="inlineStr">
         <is>
-          <t>16#430|81002#1|19#6|14#1000000</t>
+          <t>16#380|81002#1|19#6|14#1000000</t>
         </is>
       </c>
       <c r="Q521" s="0" t="n">
@@ -45056,12 +45056,12 @@
       </c>
       <c r="L524" s="0" t="inlineStr">
         <is>
-          <t>16#430|81113#2|19#6|14#1000000|6000124#300</t>
+          <t>16#380|81113#2|19#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M524" s="0" t="inlineStr">
         <is>
-          <t>16#430|81113#2|19#6|14#1000000</t>
+          <t>16#380|81113#2|19#6|14#1000000</t>
         </is>
       </c>
       <c r="Q524" s="0" t="n">
@@ -45323,12 +45323,12 @@
       </c>
       <c r="L527" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#7</t>
+          <t>16#1290|60415#1|61#2|60431#1|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M527" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|19#7</t>
+          <t>16#1290|60415#1|61#2|60431#1|19#7</t>
         </is>
       </c>
       <c r="Q527" s="0" t="n">
@@ -45590,12 +45590,12 @@
       </c>
       <c r="L530" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
+          <t>16#1290|60435#1|6000110#1000|14#1000000|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M530" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60435#1|6000110#1000|14#1000000|19#7</t>
+          <t>16#1290|60435#1|6000110#1000|14#1000000|19#7</t>
         </is>
       </c>
       <c r="Q530" s="0" t="n">
@@ -45852,12 +45852,12 @@
       </c>
       <c r="L533" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|6000124#500|19#7</t>
+          <t>16#1290|60415#1|61#2|60431#1|6000124#500|19#7</t>
         </is>
       </c>
       <c r="M533" s="0" t="inlineStr">
         <is>
-          <t>16#1000|60415#1|61#2|60431#1|19#7</t>
+          <t>16#1290|60415#1|61#2|60431#1|19#7</t>
         </is>
       </c>
       <c r="Q533" s="0" t="n">
@@ -46109,12 +46109,12 @@
       </c>
       <c r="L536" s="0" t="inlineStr">
         <is>
-          <t>16#170|50007#2|14#400000|6000124#120</t>
+          <t>16#240|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M536" s="0" t="inlineStr">
         <is>
-          <t>16#170|50007#2|14#400000</t>
+          <t>16#240|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q536" s="0" t="n">
@@ -46198,12 +46198,12 @@
       </c>
       <c r="L537" s="0" t="inlineStr">
         <is>
-          <t>16#430|50007#5|19#1|14#1000000|6000124#300</t>
+          <t>16#380|50007#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M537" s="0" t="inlineStr">
         <is>
-          <t>16#430|50007#5|19#1|14#1000000</t>
+          <t>16#380|50007#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q537" s="0" t="n">
@@ -46376,12 +46376,12 @@
       </c>
       <c r="L539" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|6000124#120|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|6000124#120|19#1</t>
         </is>
       </c>
       <c r="M539" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|19#1</t>
         </is>
       </c>
       <c r="Q539" s="0" t="n">
@@ -46465,12 +46465,12 @@
       </c>
       <c r="L540" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M540" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q540" s="0" t="n">
@@ -46554,12 +46554,12 @@
       </c>
       <c r="L541" s="0" t="inlineStr">
         <is>
-          <t>16#156|67#80|1002#2|6000124#120|19#2</t>
+          <t>16#226|67#80|1002#2|6000124#120|19#2</t>
         </is>
       </c>
       <c r="M541" s="0" t="inlineStr">
         <is>
-          <t>16#156|67#80|1002#2|19#2</t>
+          <t>16#226|67#80|1002#2|19#2</t>
         </is>
       </c>
       <c r="Q541" s="0" t="n">
@@ -46643,12 +46643,12 @@
       </c>
       <c r="L542" s="0" t="inlineStr">
         <is>
-          <t>16#234|67#120|87#3|6000124#180</t>
+          <t>16#454|67#120|87#3|6000124#180</t>
         </is>
       </c>
       <c r="M542" s="0" t="inlineStr">
         <is>
-          <t>16#234|67#120|87#3</t>
+          <t>16#454|67#120|87#3</t>
         </is>
       </c>
       <c r="Q542" s="0" t="n">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="L543" s="0" t="inlineStr">
         <is>
-          <t>16#360|67#200|20#5|6000124#300</t>
+          <t>16#310|67#200|20#5|6000124#300</t>
         </is>
       </c>
       <c r="M543" s="0" t="inlineStr">
         <is>
-          <t>16#360|67#200|20#5</t>
+          <t>16#310|67#200|20#5</t>
         </is>
       </c>
       <c r="Q543" s="0" t="n">
@@ -46910,12 +46910,12 @@
       </c>
       <c r="L545" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000|6000124#120</t>
+          <t>16#240|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M545" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000</t>
+          <t>16#240|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q545" s="0" t="n">
@@ -46999,12 +46999,12 @@
       </c>
       <c r="L546" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
+          <t>16#380|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M546" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000</t>
+          <t>16#380|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q546" s="0" t="n">
@@ -47177,12 +47177,12 @@
       </c>
       <c r="L548" s="0" t="inlineStr">
         <is>
-          <t>16#170|50005#2|50007#2|14#400000|6000124#120</t>
+          <t>16#240|50005#2|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M548" s="0" t="inlineStr">
         <is>
-          <t>16#170|50005#2|50007#2|14#400000</t>
+          <t>16#240|50005#2|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q548" s="0" t="n">
@@ -47266,12 +47266,12 @@
       </c>
       <c r="L549" s="0" t="inlineStr">
         <is>
-          <t>16#430|50005#5|50007#6|14#1000000|6000124#300</t>
+          <t>16#380|50005#5|50007#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M549" s="0" t="inlineStr">
         <is>
-          <t>16#430|50005#5|50007#6|14#1000000</t>
+          <t>16#380|50005#5|50007#6|14#1000000</t>
         </is>
       </c>
       <c r="Q549" s="0" t="n">
@@ -47444,12 +47444,12 @@
       </c>
       <c r="L551" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000|6000124#120</t>
+          <t>16#240|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M551" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000</t>
+          <t>16#240|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q551" s="0" t="n">
@@ -47533,12 +47533,12 @@
       </c>
       <c r="L552" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
+          <t>16#380|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M552" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000</t>
+          <t>16#380|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q552" s="0" t="n">
@@ -47711,12 +47711,12 @@
       </c>
       <c r="L554" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|6000124#120|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|6000124#120|19#1</t>
         </is>
       </c>
       <c r="M554" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|19#1</t>
         </is>
       </c>
       <c r="Q554" s="0" t="n">
@@ -47800,12 +47800,12 @@
       </c>
       <c r="L555" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M555" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q555" s="0" t="n">
@@ -47978,12 +47978,12 @@
       </c>
       <c r="L557" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000|6000124#120</t>
+          <t>16#240|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M557" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000</t>
+          <t>16#240|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q557" s="0" t="n">
@@ -48067,12 +48067,12 @@
       </c>
       <c r="L558" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
+          <t>16#380|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M558" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000</t>
+          <t>16#380|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q558" s="0" t="n">
@@ -48245,12 +48245,12 @@
       </c>
       <c r="L560" s="0" t="inlineStr">
         <is>
-          <t>16#170|50005#2|50007#2|14#400000|6000124#120</t>
+          <t>16#240|50005#2|50007#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M560" s="0" t="inlineStr">
         <is>
-          <t>16#170|50005#2|50007#2|14#400000</t>
+          <t>16#240|50005#2|50007#2|14#400000</t>
         </is>
       </c>
       <c r="Q560" s="0" t="n">
@@ -48334,12 +48334,12 @@
       </c>
       <c r="L561" s="0" t="inlineStr">
         <is>
-          <t>16#430|50005#5|50007#6|14#1000000|6000124#300</t>
+          <t>16#380|50005#5|50007#6|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M561" s="0" t="inlineStr">
         <is>
-          <t>16#430|50005#5|50007#6|14#1000000</t>
+          <t>16#380|50005#5|50007#6|14#1000000</t>
         </is>
       </c>
       <c r="Q561" s="0" t="n">
@@ -48512,12 +48512,12 @@
       </c>
       <c r="L563" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000|6000124#120</t>
+          <t>16#240|87#2|14#400000|6000124#120</t>
         </is>
       </c>
       <c r="M563" s="0" t="inlineStr">
         <is>
-          <t>16#170|87#2|14#400000</t>
+          <t>16#240|87#2|14#400000</t>
         </is>
       </c>
       <c r="Q563" s="0" t="n">
@@ -48601,12 +48601,12 @@
       </c>
       <c r="L564" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000|6000124#300</t>
+          <t>16#380|87#5|19#1|14#1000000|6000124#300</t>
         </is>
       </c>
       <c r="M564" s="0" t="inlineStr">
         <is>
-          <t>16#430|87#5|19#1|14#1000000</t>
+          <t>16#380|87#5|19#1|14#1000000</t>
         </is>
       </c>
       <c r="Q564" s="0" t="n">
@@ -48779,12 +48779,12 @@
       </c>
       <c r="L566" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|6000124#120|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|6000124#120|19#1</t>
         </is>
       </c>
       <c r="M566" s="0" t="inlineStr">
         <is>
-          <t>16#240|50005#2|50002#4|14#400000|19#1</t>
+          <t>16#330|50005#2|50002#4|14#400000|19#1</t>
         </is>
       </c>
       <c r="Q566" s="0" t="n">
@@ -48868,12 +48868,12 @@
       </c>
       <c r="L567" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|6000124#300|19#4</t>
         </is>
       </c>
       <c r="M567" s="0" t="inlineStr">
         <is>
-          <t>16#600|50005#5|50002#10|14#1000000|19#4</t>
+          <t>16#550|50005#5|50002#10|14#1000000|19#4</t>
         </is>
       </c>
       <c r="Q567" s="0" t="n">
@@ -49135,12 +49135,12 @@
       </c>
       <c r="L570" s="0" t="inlineStr">
         <is>
-          <t>16#720|99008#1|14#2000000|3#1000000|6000124#600|19#12</t>
+          <t>16#790|99008#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M570" s="0" t="inlineStr">
         <is>
-          <t>16#720|99008#1|14#2000000|3#1000000|19#12</t>
+          <t>16#790|99008#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q570" s="0" t="n">
@@ -49313,12 +49313,12 @@
       </c>
       <c r="L572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|6000124#1280|19#33</t>
+          <t>16#1599|72005#40|72004#150|72001#300|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M572" s="0" t="inlineStr">
         <is>
-          <t>16#1619|72005#40|72004#150|72001#300|19#33</t>
+          <t>16#1599|72005#40|72004#150|72001#300|19#33</t>
         </is>
       </c>
       <c r="Q572" s="0" t="n">
@@ -49402,12 +49402,12 @@
       </c>
       <c r="L573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|6000124#1280|19#33</t>
+          <t>16#1599|60403#2|60402#10|72001#300|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M573" s="0" t="inlineStr">
         <is>
-          <t>16#1619|60403#2|60402#10|72001#300|19#33</t>
+          <t>16#1599|60403#2|60402#10|72001#300|19#33</t>
         </is>
       </c>
       <c r="Q573" s="0" t="n">
@@ -49491,12 +49491,12 @@
       </c>
       <c r="L574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|6000124#1980|19#53</t>
+          <t>16#2674|72005#60|72004#275|72001#450|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M574" s="0" t="inlineStr">
         <is>
-          <t>16#2624|72005#60|72004#275|72001#450|19#53</t>
+          <t>16#2674|72005#60|72004#275|72001#450|19#53</t>
         </is>
       </c>
       <c r="Q574" s="0" t="n">
@@ -49580,12 +49580,12 @@
       </c>
       <c r="L575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|6000124#1980|19#53</t>
+          <t>16#2674|60403#4|60402#15|72001#450|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M575" s="0" t="inlineStr">
         <is>
-          <t>16#2624|60403#4|60402#15|72001#450|19#53</t>
+          <t>16#2674|60403#4|60402#15|72001#450|19#53</t>
         </is>
       </c>
       <c r="Q575" s="0" t="n">
@@ -49847,12 +49847,12 @@
       </c>
       <c r="L578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|6000124#6480|19#212</t>
+          <t>16#9668|60403#18|60402#18|4#10000|6000124#6480|19#212</t>
         </is>
       </c>
       <c r="M578" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|4#10000|19#212</t>
+          <t>16#9668|60403#18|60402#18|4#10000|19#212</t>
         </is>
       </c>
       <c r="Q578" s="0" t="n">
@@ -49936,12 +49936,12 @@
       </c>
       <c r="L579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|6000124#6480|19#212</t>
+          <t>16#9668|60403#18|60402#18|6000110#10000|6000124#6480|19#212</t>
         </is>
       </c>
       <c r="M579" s="0" t="inlineStr">
         <is>
-          <t>16#9558|60403#18|60402#18|6000110#10000|19#212</t>
+          <t>16#9668|60403#18|60402#18|6000110#10000|19#212</t>
         </is>
       </c>
       <c r="Q579" s="0" t="n">
@@ -50025,12 +50025,12 @@
       </c>
       <c r="L580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|6000124#6480|19#216</t>
+          <t>16#9830|60403#18|60402#18|4#10000|6000124#6480|19#216</t>
         </is>
       </c>
       <c r="M580" s="0" t="inlineStr">
         <is>
-          <t>16#9720|60403#18|60402#18|4#10000|19#216</t>
+          <t>16#9830|60403#18|60402#18|4#10000|19#216</t>
         </is>
       </c>
       <c r="Q580" s="0" t="n">
@@ -50114,12 +50114,12 @@
       </c>
       <c r="L581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|6000124#6480|19#221</t>
+          <t>16#9992|60403#18|60402#18|6000110#20000|6000124#6480|19#221</t>
         </is>
       </c>
       <c r="M581" s="0" t="inlineStr">
         <is>
-          <t>16#9882|60403#18|60402#18|6000110#20000|19#221</t>
+          <t>16#9992|60403#18|60402#18|6000110#20000|19#221</t>
         </is>
       </c>
       <c r="Q581" s="0" t="n">
@@ -50203,12 +50203,12 @@
       </c>
       <c r="L582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|6000124#6480|19#225</t>
+          <t>16#10154|60403#18|60402#18|6000110#30000|6000124#6480|19#225</t>
         </is>
       </c>
       <c r="M582" s="0" t="inlineStr">
         <is>
-          <t>16#10044|60403#18|60402#18|6000110#30000|19#225</t>
+          <t>16#10154|60403#18|60402#18|6000110#30000|19#225</t>
         </is>
       </c>
       <c r="Q582" s="0" t="n">
@@ -50559,12 +50559,12 @@
       </c>
       <c r="L586" s="0" t="inlineStr">
         <is>
-          <t>16#2475|17012#100|17011#300|19#48|6000124#1980</t>
+          <t>16#2525|17012#100|17011#300|19#48|6000124#1980</t>
         </is>
       </c>
       <c r="M586" s="0" t="inlineStr">
         <is>
-          <t>16#2475|17012#100|17011#300|19#48</t>
+          <t>16#2525|17012#100|17011#300|19#48</t>
         </is>
       </c>
       <c r="Q586" s="0" t="n">
@@ -50826,12 +50826,12 @@
       </c>
       <c r="L589" s="0" t="inlineStr">
         <is>
-          <t>16#8748|6000097#100|6000098#200|6000095#130|6000124#6480|19#189</t>
+          <t>16#8858|6000097#100|6000098#200|6000095#130|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M589" s="0" t="inlineStr">
         <is>
-          <t>16#8748|6000097#100|6000098#200|6000095#130|19#189</t>
+          <t>16#8858|6000097#100|6000098#200|6000095#130|19#189</t>
         </is>
       </c>
       <c r="Q589" s="0" t="n">
@@ -51449,12 +51449,12 @@
       </c>
       <c r="L596" s="0" t="inlineStr">
         <is>
-          <t>16#1555|10443#200|6000104#40|14#8000000|6000124#1280|19#29</t>
+          <t>16#1535|10443#200|6000104#40|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M596" s="0" t="inlineStr">
         <is>
-          <t>16#1555|10443#200|6000104#40|14#8000000|19#29</t>
+          <t>16#1535|10443#200|6000104#40|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q596" s="0" t="n">
@@ -51947,7 +51947,7 @@
       </c>
       <c r="AM601" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN601" s="0" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="L602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2540|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M602" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2540|19#32|17012#30|17011#120|17009#60|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q602" s="0" t="n">
@@ -52072,12 +52072,12 @@
       </c>
       <c r="L603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
+          <t>16#2540|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000|6000124#1280</t>
         </is>
       </c>
       <c r="M603" s="0" t="inlineStr">
         <is>
-          <t>16#2560|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
+          <t>16#2540|19#32|6000097#15|6000098#60|6000092#120|61#2|60#12|14#5000000|3#2000000</t>
         </is>
       </c>
       <c r="Q603" s="0" t="n">
@@ -52481,7 +52481,7 @@
       </c>
       <c r="AM607" s="0" t="inlineStr">
         <is>
-          <t>6#24|4#0#86400</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN607" s="0" t="n">
@@ -52784,12 +52784,12 @@
       </c>
       <c r="L611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
+          <t>16#1535|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000|6000124#1280</t>
         </is>
       </c>
       <c r="M611" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
+          <t>16#1535|20#2|19#34|4#2000|72001#150|61#1|60#12|14#5000000|3#5000000</t>
         </is>
       </c>
       <c r="Q611" s="0" t="n">
@@ -52873,12 +52873,12 @@
       </c>
       <c r="L612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
+          <t>16#2525|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000|6000124#1980</t>
         </is>
       </c>
       <c r="M612" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
+          <t>16#2525|20#5|19#54|4#3000|6000110#3000|61#2|60#24|14#10000000|3#1000000</t>
         </is>
       </c>
       <c r="Q612" s="0" t="n">
@@ -53051,12 +53051,12 @@
       </c>
       <c r="L614" s="0" t="inlineStr">
         <is>
-          <t>16#720|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000|6000124#600</t>
+          <t>16#790|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000|6000124#600</t>
         </is>
       </c>
       <c r="M614" s="0" t="inlineStr">
         <is>
-          <t>16#720|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000</t>
+          <t>16#790|6001020#50|20#1|19#13|80#10|60#24|23#6|14#5000000|3#1000000</t>
         </is>
       </c>
       <c r="Q614" s="0" t="n">
@@ -53229,12 +53229,12 @@
       </c>
       <c r="L616" s="0" t="inlineStr">
         <is>
-          <t>16#234|60404#6|60429#6|14#600000|6000124#180|19#2</t>
+          <t>16#384|60404#6|60429#6|14#600000|6000124#180|19#2</t>
         </is>
       </c>
       <c r="M616" s="0" t="inlineStr">
         <is>
-          <t>16#234|60404#6|60429#6|14#600000|19#2</t>
+          <t>16#384|60404#6|60429#6|14#600000|19#2</t>
         </is>
       </c>
       <c r="Q616" s="0" t="n">
@@ -53407,12 +53407,12 @@
       </c>
       <c r="L618" s="0" t="inlineStr">
         <is>
-          <t>16#720|60404#20|60431#5|14#2000000|6000124#600|19#12</t>
+          <t>16#790|60404#20|60431#5|14#2000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M618" s="0" t="inlineStr">
         <is>
-          <t>16#720|60404#20|60431#5|14#2000000|19#12</t>
+          <t>16#790|60404#20|60431#5|14#2000000|19#12</t>
         </is>
       </c>
       <c r="Q618" s="0" t="n">
@@ -53496,12 +53496,12 @@
       </c>
       <c r="L619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
+          <t>16#870|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M619" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
+          <t>16#870|19#9|4#2000|70034#2|80#6|60#10|23#6|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q619" s="0" t="n">
@@ -53585,12 +53585,12 @@
       </c>
       <c r="L620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
+          <t>16#870|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000|6000124#500</t>
         </is>
       </c>
       <c r="M620" s="0" t="inlineStr">
         <is>
-          <t>16#1000|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
+          <t>16#870|19#8|4#2000|20#1|61#2|60#12|65#1000|14#1000000|3#500000</t>
         </is>
       </c>
       <c r="Q620" s="0" t="n">
@@ -53727,7 +53727,7 @@
       </c>
       <c r="AM621" s="0" t="inlineStr">
         <is>
-          <t>6#8|4#0#28800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN621" s="0" t="n">
@@ -53816,7 +53816,7 @@
       </c>
       <c r="AM622" s="0" t="inlineStr">
         <is>
-          <t>6#8|4#0#28800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN622" s="0" t="n">
@@ -53852,12 +53852,12 @@
       </c>
       <c r="L623" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#470|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M623" s="0" t="inlineStr">
         <is>
-          <t>16#600|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#470|81148#50|4#2000|20#9|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q623" s="0" t="n">
@@ -53941,12 +53941,12 @@
       </c>
       <c r="L624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
+          <t>16#470|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#500</t>
         </is>
       </c>
       <c r="M624" s="0" t="inlineStr">
         <is>
-          <t>16#600|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#470|19#10|4#2000|20#1|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q624" s="0" t="n">
@@ -54083,7 +54083,7 @@
       </c>
       <c r="AM625" s="0" t="inlineStr">
         <is>
-          <t>6#8|4#0#28800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN625" s="0" t="n">
@@ -54119,12 +54119,12 @@
       </c>
       <c r="L626" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
+          <t>16#13070|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000|6000124#6480</t>
         </is>
       </c>
       <c r="M626" s="0" t="inlineStr">
         <is>
-          <t>16#12960|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
+          <t>16#13070|17014#400|20#170|6000110#10000|61#2|60#12|65#1000|14#50000000|3#1000000</t>
         </is>
       </c>
       <c r="Q626" s="0" t="n">
@@ -54261,7 +54261,7 @@
       </c>
       <c r="AM627" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN627" s="0" t="n">
@@ -54350,7 +54350,7 @@
       </c>
       <c r="AM628" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN628" s="0" t="n">
@@ -54439,7 +54439,7 @@
       </c>
       <c r="AM629" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN629" s="0" t="n">
@@ -54528,7 +54528,7 @@
       </c>
       <c r="AM630" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN630" s="0" t="n">
@@ -54617,7 +54617,7 @@
       </c>
       <c r="AM631" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN631" s="0" t="n">
@@ -54706,7 +54706,7 @@
       </c>
       <c r="AM632" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN632" s="0" t="n">
@@ -54795,7 +54795,7 @@
       </c>
       <c r="AM633" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN633" s="0" t="n">
@@ -54884,7 +54884,7 @@
       </c>
       <c r="AM634" s="0" t="inlineStr">
         <is>
-          <t>6#12|4#0#43200</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN634" s="0" t="n">
@@ -55009,12 +55009,12 @@
       </c>
       <c r="L636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|6000124#1280|19#32</t>
+          <t>16#1535|4#2500|6000110#2000|72001#250|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M636" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|6000110#2000|72001#250|19#32</t>
+          <t>16#1535|4#2500|6000110#2000|72001#250|19#32</t>
         </is>
       </c>
       <c r="Q636" s="0" t="n">
@@ -55098,12 +55098,12 @@
       </c>
       <c r="L637" s="0" t="inlineStr">
         <is>
-          <t>16#1555|81004#1|4#5000|3#5000000|6000124#1280|19#29</t>
+          <t>16#1535|81004#1|4#5000|3#5000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M637" s="0" t="inlineStr">
         <is>
-          <t>16#1555|81004#1|4#5000|3#5000000|19#29</t>
+          <t>16#1535|81004#1|4#5000|3#5000000|19#29</t>
         </is>
       </c>
       <c r="Q637" s="0" t="n">
@@ -55187,12 +55187,12 @@
       </c>
       <c r="L638" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|20#3|19#45|6000124#1980</t>
+          <t>16#2525|60415#1|20#3|19#45|6000124#1980</t>
         </is>
       </c>
       <c r="M638" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|20#3|19#45</t>
+          <t>16#2525|60415#1|20#3|19#45</t>
         </is>
       </c>
       <c r="Q638" s="0" t="n">
@@ -55276,12 +55276,12 @@
       </c>
       <c r="L639" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
+          <t>16#2525|60415#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M639" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|6000110#5000|19#48</t>
+          <t>16#2525|60415#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q639" s="0" t="n">
@@ -55418,7 +55418,7 @@
       </c>
       <c r="AM640" s="0" t="inlineStr">
         <is>
-          <t>6#24|4#0#86400</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN640" s="0" t="n">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AM641" s="0" t="inlineStr">
         <is>
-          <t>6#48|4#0#172800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN641" s="0" t="n">
@@ -55596,7 +55596,7 @@
       </c>
       <c r="AM642" s="0" t="inlineStr">
         <is>
-          <t>6#48|4#0#172800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN642" s="0" t="n">
@@ -55685,7 +55685,7 @@
       </c>
       <c r="AM643" s="0" t="inlineStr">
         <is>
-          <t>6#48|4#0#172800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN643" s="0" t="n">
@@ -55863,7 +55863,7 @@
       </c>
       <c r="AM645" s="0" t="inlineStr">
         <is>
-          <t>6#48|4#0#172800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN645" s="0" t="n">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="AM646" s="0" t="inlineStr">
         <is>
-          <t>6#48|4#0#172800</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AN646" s="0" t="n">
@@ -56166,12 +56166,12 @@
       </c>
       <c r="L649" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#3|60411#15|14#8000000|6000124#1280|19#29</t>
+          <t>16#1535|60412#3|60411#15|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M649" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#3|60411#15|14#8000000|19#29</t>
+          <t>16#1535|60412#3|60411#15|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q649" s="0" t="n">
@@ -56255,12 +56255,12 @@
       </c>
       <c r="L650" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60412#5|60411#20|14#15000000|6000124#1980|19#48</t>
+          <t>16#2525|60412#5|60411#20|14#15000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M650" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60412#5|60411#20|14#15000000|19#48</t>
+          <t>16#2525|60412#5|60411#20|14#15000000|19#48</t>
         </is>
       </c>
       <c r="Q650" s="0" t="n">
@@ -56344,12 +56344,12 @@
       </c>
       <c r="L651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|6000124#1280|19#31</t>
+          <t>16#1535|99005#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M651" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99005#1|3#4000000|4#2000|19#31</t>
+          <t>16#1535|99005#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q651" s="0" t="n">
@@ -56522,12 +56522,12 @@
       </c>
       <c r="L653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|6000124#6480|19#193</t>
+          <t>16#8858|99005#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M653" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99005#1|3#15000000|4#10000|19#193</t>
+          <t>16#8858|99005#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q653" s="0" t="n">
@@ -56611,12 +56611,12 @@
       </c>
       <c r="L654" s="0" t="inlineStr">
         <is>
-          <t>16#720|99006#1|14#2000000|3#1000000|6000124#600|19#12</t>
+          <t>16#790|99006#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M654" s="0" t="inlineStr">
         <is>
-          <t>16#720|99006#1|14#2000000|3#1000000|19#12</t>
+          <t>16#790|99006#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q654" s="0" t="n">
@@ -56700,12 +56700,12 @@
       </c>
       <c r="L655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|6000124#1280|19#31</t>
+          <t>16#1535|99006#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M655" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99006#1|3#4000000|4#2000|19#31</t>
+          <t>16#1535|99006#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q655" s="0" t="n">
@@ -56878,12 +56878,12 @@
       </c>
       <c r="L657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|6000124#6480|19#193</t>
+          <t>16#8858|99006#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M657" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99006#1|3#15000000|4#10000|19#193</t>
+          <t>16#8858|99006#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q657" s="0" t="n">
@@ -56967,12 +56967,12 @@
       </c>
       <c r="L658" s="0" t="inlineStr">
         <is>
-          <t>16#720|99007#1|14#2000000|3#1000000|6000124#600|19#12</t>
+          <t>16#790|99007#1|14#2000000|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M658" s="0" t="inlineStr">
         <is>
-          <t>16#720|99007#1|14#2000000|3#1000000|19#12</t>
+          <t>16#790|99007#1|14#2000000|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q658" s="0" t="n">
@@ -57056,12 +57056,12 @@
       </c>
       <c r="L659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|6000124#1280|19#31</t>
+          <t>16#1535|99007#1|3#4000000|4#2000|6000124#1280|19#31</t>
         </is>
       </c>
       <c r="M659" s="0" t="inlineStr">
         <is>
-          <t>16#1555|99007#1|3#4000000|4#2000|19#31</t>
+          <t>16#1535|99007#1|3#4000000|4#2000|19#31</t>
         </is>
       </c>
       <c r="Q659" s="0" t="n">
@@ -57234,12 +57234,12 @@
       </c>
       <c r="L661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|6000124#6480|19#193</t>
+          <t>16#8858|99007#1|3#15000000|4#10000|6000124#6480|19#193</t>
         </is>
       </c>
       <c r="M661" s="0" t="inlineStr">
         <is>
-          <t>16#8748|99007#1|3#15000000|4#10000|19#193</t>
+          <t>16#8858|99007#1|3#15000000|4#10000|19#193</t>
         </is>
       </c>
       <c r="Q661" s="0" t="n">
@@ -57323,12 +57323,12 @@
       </c>
       <c r="L662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|6000124#1280|19#32</t>
+          <t>16#1535|4#3000|6000088#1|6000110#3000|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M662" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|6000088#1|6000110#3000|19#32</t>
+          <t>16#1535|4#3000|6000088#1|6000110#3000|19#32</t>
         </is>
       </c>
       <c r="Q662" s="0" t="n">
@@ -57412,12 +57412,12 @@
       </c>
       <c r="L663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|6000124#1980|19#51</t>
+          <t>16#2525|4#3000|6000110#2000|72001#200|6000124#1980|19#51</t>
         </is>
       </c>
       <c r="M663" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|6000110#2000|72001#200|19#51</t>
+          <t>16#2525|4#3000|6000110#2000|72001#200|19#51</t>
         </is>
       </c>
       <c r="Q663" s="0" t="n">
@@ -57590,12 +57590,12 @@
       </c>
       <c r="L665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|6000124#1280|19#32</t>
+          <t>16#1535|4#3000|99000#1|6000110#3000|6000124#1280|19#32</t>
         </is>
       </c>
       <c r="M665" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#3000|99000#1|6000110#3000|19#32</t>
+          <t>16#1535|4#3000|99000#1|6000110#3000|19#32</t>
         </is>
       </c>
       <c r="Q665" s="0" t="n">
@@ -57679,12 +57679,12 @@
       </c>
       <c r="L666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|6000124#1980|19#51</t>
+          <t>16#2525|4#4000|99001#1|6000110#4000|6000124#1980|19#51</t>
         </is>
       </c>
       <c r="M666" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#4000|99001#1|6000110#4000|19#51</t>
+          <t>16#2525|4#4000|99001#1|6000110#4000|19#51</t>
         </is>
       </c>
       <c r="Q666" s="0" t="n">
@@ -57946,12 +57946,12 @@
       </c>
       <c r="L669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|6000124#1280|19#33</t>
+          <t>16#1535|4#2500|60411#10|60412#3|6000124#1280|19#33</t>
         </is>
       </c>
       <c r="M669" s="0" t="inlineStr">
         <is>
-          <t>16#1555|4#2500|60411#10|60412#3|19#33</t>
+          <t>16#1535|4#2500|60411#10|60412#3|19#33</t>
         </is>
       </c>
       <c r="Q669" s="0" t="n">
@@ -58035,12 +58035,12 @@
       </c>
       <c r="L670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|6000124#1980|19#52</t>
+          <t>16#2525|4#3000|60411#12|6000088#1|6000124#1980|19#52</t>
         </is>
       </c>
       <c r="M670" s="0" t="inlineStr">
         <is>
-          <t>16#2475|4#3000|60411#12|6000088#1|19#52</t>
+          <t>16#2525|4#3000|60411#12|6000088#1|19#52</t>
         </is>
       </c>
       <c r="Q670" s="0" t="n">
@@ -58213,12 +58213,12 @@
       </c>
       <c r="L672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|6000124#4880|19#148</t>
+          <t>16#5866|4#4500|60411#20|6000089#1|6000124#4880|19#148</t>
         </is>
       </c>
       <c r="M672" s="0" t="inlineStr">
         <is>
-          <t>16#6466|4#4500|60411#20|6000089#1|19#148</t>
+          <t>16#5866|4#4500|60411#20|6000089#1|19#148</t>
         </is>
       </c>
       <c r="Q672" s="0" t="n">
@@ -58302,12 +58302,12 @@
       </c>
       <c r="L673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|6000124#6480|19#202</t>
+          <t>16#8858|4#5000|60412#3|6000090#1|6000124#6480|19#202</t>
         </is>
       </c>
       <c r="M673" s="0" t="inlineStr">
         <is>
-          <t>16#8748|4#5000|60412#3|6000090#1|19#202</t>
+          <t>16#8858|4#5000|60412#3|6000090#1|19#202</t>
         </is>
       </c>
       <c r="Q673" s="0" t="n">
@@ -58391,12 +58391,12 @@
       </c>
       <c r="L674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|6000124#1280|19#34</t>
+          <t>16#1535|72001#200|60411#10|60412#3|6000124#1280|19#34</t>
         </is>
       </c>
       <c r="M674" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72001#200|60411#10|60412#3|19#34</t>
+          <t>16#1535|72001#200|60411#10|60412#3|19#34</t>
         </is>
       </c>
       <c r="Q674" s="0" t="n">
@@ -58480,12 +58480,12 @@
       </c>
       <c r="L675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|6000124#1980|19#53</t>
+          <t>16#2525|72001#300|60411#15|60412#4|6000124#1980|19#53</t>
         </is>
       </c>
       <c r="M675" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72001#300|60411#15|60412#4|19#53</t>
+          <t>16#2525|72001#300|60411#15|60412#4|19#53</t>
         </is>
       </c>
       <c r="Q675" s="0" t="n">
@@ -58747,12 +58747,12 @@
       </c>
       <c r="L678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|6000124#4880|19#150</t>
+          <t>16#5866|72001#500|60411#20|60412#5|6000124#4880|19#150</t>
         </is>
       </c>
       <c r="M678" s="0" t="inlineStr">
         <is>
-          <t>16#6466|72001#500|60411#20|60412#5|19#150</t>
+          <t>16#5866|72001#500|60411#20|60412#5|19#150</t>
         </is>
       </c>
       <c r="Q678" s="0" t="n">
@@ -58836,12 +58836,12 @@
       </c>
       <c r="L679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|6000124#6480|19#207</t>
+          <t>16#8858|72001#550|60411#25|60412#5|6000124#6480|19#207</t>
         </is>
       </c>
       <c r="M679" s="0" t="inlineStr">
         <is>
-          <t>16#8748|72001#550|60411#25|60412#5|19#207</t>
+          <t>16#8858|72001#550|60411#25|60412#5|19#207</t>
         </is>
       </c>
       <c r="Q679" s="0" t="n">
@@ -58925,12 +58925,12 @@
       </c>
       <c r="L680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|6000124#1280|19#35</t>
+          <t>16#1535|60417#1|60411#8|60412#2|6000124#1280|19#35</t>
         </is>
       </c>
       <c r="M680" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60417#1|60411#8|60412#2|19#35</t>
+          <t>16#1535|60417#1|60411#8|60412#2|19#35</t>
         </is>
       </c>
       <c r="Q680" s="0" t="n">
@@ -59014,12 +59014,12 @@
       </c>
       <c r="L681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|6000124#1980|19#56</t>
+          <t>16#2525|60417#1|60411#15|60412#4|6000124#1980|19#56</t>
         </is>
       </c>
       <c r="M681" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60417#1|60411#15|60412#4|19#56</t>
+          <t>16#2525|60417#1|60411#15|60412#4|19#56</t>
         </is>
       </c>
       <c r="Q681" s="0" t="n">
@@ -59192,12 +59192,12 @@
       </c>
       <c r="L683" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|6000124#1280|19#29</t>
+          <t>16#1535|17012#30|17011#120|17009#60|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M683" s="0" t="inlineStr">
         <is>
-          <t>16#1555|17012#30|17011#120|17009#60|19#29</t>
+          <t>16#1535|17012#30|17011#120|17009#60|19#29</t>
         </is>
       </c>
       <c r="Q683" s="0" t="n">
@@ -59281,12 +59281,12 @@
       </c>
       <c r="L684" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|3#8000000|6000124#1980|19#48</t>
+          <t>16#2525|60415#1|6000089#1|3#8000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M684" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60415#1|6000089#1|3#8000000|19#48</t>
+          <t>16#2525|60415#1|6000089#1|3#8000000|19#48</t>
         </is>
       </c>
       <c r="Q684" s="0" t="n">
@@ -59370,12 +59370,12 @@
       </c>
       <c r="L685" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|6000124#1280|19#29</t>
+          <t>16#1535|6000097#15|6000098#60|6000092#120|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M685" s="0" t="inlineStr">
         <is>
-          <t>16#1555|6000097#15|6000098#60|6000092#120|19#29</t>
+          <t>16#1535|6000097#15|6000098#60|6000092#120|19#29</t>
         </is>
       </c>
       <c r="Q685" s="0" t="n">
@@ -59459,12 +59459,12 @@
       </c>
       <c r="L686" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
+          <t>16#2525|60416#1|6000089#1|6000110#5000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M686" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|6000089#1|6000110#5000|19#48</t>
+          <t>16#2525|60416#1|6000089#1|6000110#5000|19#48</t>
         </is>
       </c>
       <c r="Q686" s="0" t="n">
@@ -59815,12 +59815,12 @@
       </c>
       <c r="L690" s="0" t="inlineStr">
         <is>
-          <t>16#8748|60406#1|10423#10|10425#600|6000124#6480|19#189</t>
+          <t>16#8858|60406#1|10423#10|10425#600|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M690" s="0" t="inlineStr">
         <is>
-          <t>16#8748|60406#1|10423#10|10425#600|19#189</t>
+          <t>16#8858|60406#1|10423#10|10425#600|19#189</t>
         </is>
       </c>
       <c r="Q690" s="0" t="n">
@@ -59904,12 +59904,12 @@
       </c>
       <c r="L691" s="0" t="inlineStr">
         <is>
-          <t>16#720|81114#1|3#1000000|6000124#600|19#12</t>
+          <t>16#790|81114#1|3#1000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M691" s="0" t="inlineStr">
         <is>
-          <t>16#720|81114#1|3#1000000|19#12</t>
+          <t>16#790|81114#1|3#1000000|19#12</t>
         </is>
       </c>
       <c r="Q691" s="0" t="n">
@@ -60240,12 +60240,12 @@
       </c>
       <c r="L695" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60415#1|19#29|3#1000000|6000124#1280</t>
+          <t>16#1535|60415#1|19#29|3#1000000|6000124#1280</t>
         </is>
       </c>
       <c r="M695" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60415#1|19#29|3#1000000</t>
+          <t>16#1535|60415#1|19#29|3#1000000</t>
         </is>
       </c>
       <c r="Q695" s="0" t="n">
@@ -60324,12 +60324,12 @@
       </c>
       <c r="L696" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#29|6000110#2000|6000124#1280</t>
+          <t>16#1535|20#29|6000110#2000|6000124#1280</t>
         </is>
       </c>
       <c r="M696" s="0" t="inlineStr">
         <is>
-          <t>16#1555|20#29|6000110#2000</t>
+          <t>16#1535|20#29|6000110#2000</t>
         </is>
       </c>
       <c r="Q696" s="0" t="n">
@@ -60408,12 +60408,12 @@
       </c>
       <c r="L697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#36|3#2000000|14#4000000|6000124#1280</t>
+          <t>16#1535|19#36|3#2000000|14#4000000|6000124#1280</t>
         </is>
       </c>
       <c r="M697" s="0" t="inlineStr">
         <is>
-          <t>16#1555|19#36|3#2000000|14#4000000</t>
+          <t>16#1535|19#36|3#2000000|14#4000000</t>
         </is>
       </c>
       <c r="Q697" s="0" t="n">
@@ -60492,12 +60492,12 @@
       </c>
       <c r="L698" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|19#48|3#2000000|6000124#1980</t>
+          <t>16#2525|60416#1|19#48|3#2000000|6000124#1980</t>
         </is>
       </c>
       <c r="M698" s="0" t="inlineStr">
         <is>
-          <t>16#2475|60416#1|19#48|3#2000000</t>
+          <t>16#2525|60416#1|19#48|3#2000000</t>
         </is>
       </c>
       <c r="Q698" s="0" t="n">
@@ -60576,12 +60576,12 @@
       </c>
       <c r="L699" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#48|6000110#3000|6000124#1980</t>
+          <t>16#2525|20#48|6000110#3000|6000124#1980</t>
         </is>
       </c>
       <c r="M699" s="0" t="inlineStr">
         <is>
-          <t>16#2475|20#48|6000110#3000</t>
+          <t>16#2525|20#48|6000110#3000</t>
         </is>
       </c>
       <c r="Q699" s="0" t="n">
@@ -60744,12 +60744,12 @@
       </c>
       <c r="L701" s="0" t="inlineStr">
         <is>
-          <t>16#234|60411#1|60410#2|14#800000|6000124#180|19#2</t>
+          <t>16#384|60411#1|60410#2|14#800000|6000124#180|19#2</t>
         </is>
       </c>
       <c r="M701" s="0" t="inlineStr">
         <is>
-          <t>16#234|60411#1|60410#2|14#800000|19#2</t>
+          <t>16#384|60411#1|60410#2|14#800000|19#2</t>
         </is>
       </c>
       <c r="Q701" s="0" t="n">
@@ -60922,12 +60922,12 @@
       </c>
       <c r="L703" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60410#5|14#3000000|6000124#600|19#12</t>
+          <t>16#790|60411#4|60410#5|14#3000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M703" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60410#5|14#3000000|19#12</t>
+          <t>16#790|60411#4|60410#5|14#3000000|19#12</t>
         </is>
       </c>
       <c r="Q703" s="0" t="n">
@@ -61189,12 +61189,12 @@
       </c>
       <c r="L706" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|14#10000000|60412#4|6000124#6480|19#189</t>
+          <t>16#8858|3#20000000|14#10000000|60412#4|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M706" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|14#10000000|60412#4|19#189</t>
+          <t>16#8858|3#20000000|14#10000000|60412#4|19#189</t>
         </is>
       </c>
       <c r="Q706" s="0" t="n">
@@ -61278,12 +61278,12 @@
       </c>
       <c r="L707" s="0" t="inlineStr">
         <is>
-          <t>16#234|60411#1|60418#2|14#800000|6000124#180|19#2</t>
+          <t>16#384|60411#1|60418#2|14#800000|6000124#180|19#2</t>
         </is>
       </c>
       <c r="M707" s="0" t="inlineStr">
         <is>
-          <t>16#234|60411#1|60418#2|14#800000|19#2</t>
+          <t>16#384|60411#1|60418#2|14#800000|19#2</t>
         </is>
       </c>
       <c r="Q707" s="0" t="n">
@@ -61456,12 +61456,12 @@
       </c>
       <c r="L709" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60418#5|14#3000000|6000124#600|19#12</t>
+          <t>16#790|60411#4|60418#5|14#3000000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M709" s="0" t="inlineStr">
         <is>
-          <t>16#720|60411#4|60418#5|14#3000000|19#12</t>
+          <t>16#790|60411#4|60418#5|14#3000000|19#12</t>
         </is>
       </c>
       <c r="Q709" s="0" t="n">
@@ -61634,12 +61634,12 @@
       </c>
       <c r="L711" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#6|60418#12|14#8000000|6000124#1280|19#29</t>
+          <t>16#1535|60412#6|60418#12|14#8000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M711" s="0" t="inlineStr">
         <is>
-          <t>16#1555|60412#6|60418#12|14#8000000|19#29</t>
+          <t>16#1535|60412#6|60418#12|14#8000000|19#29</t>
         </is>
       </c>
       <c r="Q711" s="0" t="n">
@@ -61723,12 +61723,12 @@
       </c>
       <c r="L712" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|6000110#2000|99001#1|6000124#6480|19#189</t>
+          <t>16#8858|3#20000000|6000110#2000|99001#1|6000124#6480|19#189</t>
         </is>
       </c>
       <c r="M712" s="0" t="inlineStr">
         <is>
-          <t>16#8748|3#20000000|6000110#2000|99001#1|19#189</t>
+          <t>16#8858|3#20000000|6000110#2000|99001#1|19#189</t>
         </is>
       </c>
       <c r="Q712" s="0" t="n">
@@ -61901,12 +61901,12 @@
       </c>
       <c r="L714" s="0" t="inlineStr">
         <is>
-          <t>16#720|72003#20|4#1000|3#1600000|6000124#600|19#12</t>
+          <t>16#790|72003#20|4#1000|3#1600000|6000124#600|19#12</t>
         </is>
       </c>
       <c r="M714" s="0" t="inlineStr">
         <is>
-          <t>16#720|72003#20|4#1000|3#1600000|19#12</t>
+          <t>16#790|72003#20|4#1000|3#1600000|19#12</t>
         </is>
       </c>
       <c r="Q714" s="0" t="n">
@@ -62079,12 +62079,12 @@
       </c>
       <c r="L716" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72003#40|4#2000|3#5000000|6000124#1280|19#29</t>
+          <t>16#1535|72003#40|4#2000|3#5000000|6000124#1280|19#29</t>
         </is>
       </c>
       <c r="M716" s="0" t="inlineStr">
         <is>
-          <t>16#1555|72003#40|4#2000|3#5000000|19#29</t>
+          <t>16#1535|72003#40|4#2000|3#5000000|19#29</t>
         </is>
       </c>
       <c r="Q716" s="0" t="n">
@@ -62168,12 +62168,12 @@
       </c>
       <c r="L717" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72003#60|4#3000|3#8000000|6000124#1980|19#48</t>
+          <t>16#2525|72003#60|4#3000|3#8000000|6000124#1980|19#48</t>
         </is>
       </c>
       <c r="M717" s="0" t="inlineStr">
         <is>
-          <t>16#2475|72003#60|4#3000|3#8000000|19#48</t>
+          <t>16#2525|72003#60|4#3000|3#8000000|19#48</t>
         </is>
       </c>
       <c r="Q717" s="0" t="n">
@@ -66417,12 +66417,12 @@
       </c>
       <c r="L766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M766" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q766" s="0" t="n">
@@ -66504,12 +66504,12 @@
       </c>
       <c r="L767" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M767" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q767" s="0" t="n">
@@ -66591,12 +66591,12 @@
       </c>
       <c r="L768" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M768" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q768" s="0" t="n">
@@ -67374,12 +67374,12 @@
       </c>
       <c r="L777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M777" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q777" s="0" t="n">
@@ -67461,12 +67461,12 @@
       </c>
       <c r="L778" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M778" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q778" s="0" t="n">
@@ -67548,12 +67548,12 @@
       </c>
       <c r="L779" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M779" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q779" s="0" t="n">
@@ -68331,12 +68331,12 @@
       </c>
       <c r="L788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M788" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q788" s="0" t="n">
@@ -68418,12 +68418,12 @@
       </c>
       <c r="L789" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M789" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q789" s="0" t="n">
@@ -68505,12 +68505,12 @@
       </c>
       <c r="L790" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001025#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M790" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#30|6000110#1500</t>
+          <t>16#1542|6001025#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q790" s="0" t="n">
@@ -69288,12 +69288,12 @@
       </c>
       <c r="L799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M799" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q799" s="0" t="n">
@@ -69375,12 +69375,12 @@
       </c>
       <c r="L800" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M800" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q800" s="0" t="n">
@@ -69462,12 +69462,12 @@
       </c>
       <c r="L801" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M801" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q801" s="0" t="n">
@@ -70245,12 +70245,12 @@
       </c>
       <c r="L810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M810" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q810" s="0" t="n">
@@ -70332,12 +70332,12 @@
       </c>
       <c r="L811" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M811" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q811" s="0" t="n">
@@ -70419,12 +70419,12 @@
       </c>
       <c r="L812" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001025#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M812" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001025#100|19#30|6000110#1500</t>
+          <t>16#1542|6001025#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q812" s="0" t="n">
@@ -71202,12 +71202,12 @@
       </c>
       <c r="L821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000|6000124#680</t>
+          <t>16#586|19#17|4#1000|6000110#1000|6000124#680</t>
         </is>
       </c>
       <c r="M821" s="0" t="inlineStr">
         <is>
-          <t>16#816|19#17|4#1000|6000110#1000</t>
+          <t>16#586|19#17|4#1000|6000110#1000</t>
         </is>
       </c>
       <c r="Q821" s="0" t="n">
@@ -71289,12 +71289,12 @@
       </c>
       <c r="L822" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000|6000124#980</t>
+          <t>16#1397|20#17|19#5|6000110#1000|6000124#980</t>
         </is>
       </c>
       <c r="M822" s="0" t="inlineStr">
         <is>
-          <t>16#1127|20#17|19#5|6000110#1000</t>
+          <t>16#1397|20#17|19#5|6000110#1000</t>
         </is>
       </c>
       <c r="Q822" s="0" t="n">
@@ -71376,12 +71376,12 @@
       </c>
       <c r="L823" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500|6000124#1280</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500|6000124#1280</t>
         </is>
       </c>
       <c r="M823" s="0" t="inlineStr">
         <is>
-          <t>16#1472|6001024#100|19#30|6000110#1500</t>
+          <t>16#1542|6001024#100|19#30|6000110#1500</t>
         </is>
       </c>
       <c r="Q823" s="0" t="n">
@@ -71784,7 +71784,7 @@
       </c>
       <c r="AM827" s="0" t="inlineStr">
         <is>
-          <t>2#1503|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ827" s="0" t="n">
@@ -71962,7 +71962,7 @@
       </c>
       <c r="AM829" s="0" t="inlineStr">
         <is>
-          <t>2#1503|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ829" s="0" t="n">
@@ -72051,7 +72051,7 @@
       </c>
       <c r="AM830" s="0" t="inlineStr">
         <is>
-          <t>2#1503|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ830" s="0" t="n">
@@ -72140,7 +72140,7 @@
       </c>
       <c r="AM831" s="0" t="inlineStr">
         <is>
-          <t>2#1503|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ831" s="0" t="n">
@@ -72229,7 +72229,7 @@
       </c>
       <c r="AM832" s="0" t="inlineStr">
         <is>
-          <t>2#1503|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ832" s="0" t="n">
@@ -72674,7 +72674,7 @@
       </c>
       <c r="AM837" s="0" t="inlineStr">
         <is>
-          <t>2#1506|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ837" s="0" t="n">
@@ -72763,7 +72763,7 @@
       </c>
       <c r="AM838" s="0" t="inlineStr">
         <is>
-          <t>2#1506|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ838" s="0" t="n">
@@ -72852,7 +72852,7 @@
       </c>
       <c r="AM839" s="0" t="inlineStr">
         <is>
-          <t>2#1506|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ839" s="0" t="n">
@@ -72941,7 +72941,7 @@
       </c>
       <c r="AM840" s="0" t="inlineStr">
         <is>
-          <t>2#1506|4#0#0</t>
+          <t>1#999#999</t>
         </is>
       </c>
       <c r="AQ840" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -21328,7 +21328,7 @@
       </c>
       <c r="K257" s="0" t="inlineStr">
         <is>
-          <t>16#1100</t>
+          <t>16#600</t>
         </is>
       </c>
       <c r="L257" s="0" t="inlineStr">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -21494,17 +21494,17 @@
       </c>
       <c r="K259" s="0" t="inlineStr">
         <is>
-          <t>16#1127</t>
+          <t>16#1130</t>
         </is>
       </c>
       <c r="L259" s="0" t="inlineStr">
         <is>
-          <t>16#1127|6000124#980</t>
+          <t>16#1130|6000124#980</t>
         </is>
       </c>
       <c r="M259" s="0" t="inlineStr">
         <is>
-          <t>16#1127</t>
+          <t>16#1130</t>
         </is>
       </c>
       <c r="Q259" s="0" t="n">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="K260" s="0" t="inlineStr">
         <is>
-          <t>16#2376</t>
+          <t>16#2380</t>
         </is>
       </c>
       <c r="L260" s="0" t="inlineStr">
         <is>
-          <t>16#2376|6000124#1980</t>
+          <t>16#2380|6000124#1980</t>
         </is>
       </c>
       <c r="M260" s="0" t="inlineStr">
         <is>
-          <t>16#2376</t>
+          <t>16#2380</t>
         </is>
       </c>
       <c r="Q260" s="0" t="n">
@@ -21743,17 +21743,17 @@
       </c>
       <c r="K262" s="0" t="inlineStr">
         <is>
-          <t>16#8424</t>
+          <t>16#8420</t>
         </is>
       </c>
       <c r="L262" s="0" t="inlineStr">
         <is>
-          <t>16#8424|6000124#6480</t>
+          <t>16#8420|6000124#6480</t>
         </is>
       </c>
       <c r="M262" s="0" t="inlineStr">
         <is>
-          <t>16#8424</t>
+          <t>16#8420</t>
         </is>
       </c>
       <c r="Q262" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -21411,17 +21411,17 @@
       </c>
       <c r="K258" s="0" t="inlineStr">
         <is>
-          <t>16#330</t>
+          <t>16#350</t>
         </is>
       </c>
       <c r="L258" s="0" t="inlineStr">
         <is>
-          <t>16#330|6000124#300</t>
+          <t>16#350|6000124#300</t>
         </is>
       </c>
       <c r="M258" s="0" t="inlineStr">
         <is>
-          <t>16#330</t>
+          <t>16#350</t>
         </is>
       </c>
       <c r="Q258" s="0" t="n">
@@ -21494,17 +21494,17 @@
       </c>
       <c r="K259" s="0" t="inlineStr">
         <is>
-          <t>16#1130</t>
+          <t>16#1200</t>
         </is>
       </c>
       <c r="L259" s="0" t="inlineStr">
         <is>
-          <t>16#1130|6000124#980</t>
+          <t>16#1200|6000124#980</t>
         </is>
       </c>
       <c r="M259" s="0" t="inlineStr">
         <is>
-          <t>16#1130</t>
+          <t>16#1200</t>
         </is>
       </c>
       <c r="Q259" s="0" t="n">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="K260" s="0" t="inlineStr">
         <is>
-          <t>16#2380</t>
+          <t>16#2500</t>
         </is>
       </c>
       <c r="L260" s="0" t="inlineStr">
         <is>
-          <t>16#2380|6000124#1980</t>
+          <t>16#2500|6000124#1980</t>
         </is>
       </c>
       <c r="M260" s="0" t="inlineStr">
         <is>
-          <t>16#2380</t>
+          <t>16#2500</t>
         </is>
       </c>
       <c r="Q260" s="0" t="n">
@@ -21660,17 +21660,17 @@
       </c>
       <c r="K261" s="0" t="inlineStr">
         <is>
-          <t>16#4100</t>
+          <t>16#4300</t>
         </is>
       </c>
       <c r="L261" s="0" t="inlineStr">
         <is>
-          <t>16#4100|6000124#3280</t>
+          <t>16#4300|6000124#3280</t>
         </is>
       </c>
       <c r="M261" s="0" t="inlineStr">
         <is>
-          <t>16#4100</t>
+          <t>16#4300</t>
         </is>
       </c>
       <c r="Q261" s="0" t="n">
@@ -21743,17 +21743,17 @@
       </c>
       <c r="K262" s="0" t="inlineStr">
         <is>
-          <t>16#8420</t>
+          <t>16#8800</t>
         </is>
       </c>
       <c r="L262" s="0" t="inlineStr">
         <is>
-          <t>16#8420|6000124#6480</t>
+          <t>16#8800|6000124#6480</t>
         </is>
       </c>
       <c r="M262" s="0" t="inlineStr">
         <is>
-          <t>16#8420</t>
+          <t>16#8800</t>
         </is>
       </c>
       <c r="Q262" s="0" t="n">

--- a/data_execl/base_data/RechargeCommodityConfig.xlsx
+++ b/data_execl/base_data/RechargeCommodityConfig.xlsx
@@ -26532,12 +26532,12 @@
       </c>
       <c r="L317" s="0" t="inlineStr">
         <is>
-          <t>16#300|20#3|4#500|14#500000|6000124#300</t>
+          <t>16#300|20#3|4#500|14#500000|6000124#300|19#1</t>
         </is>
       </c>
       <c r="M317" s="0" t="inlineStr">
         <is>
-          <t>16#300|20#3|4#500|14#500000</t>
+          <t>16#300|20#3|4#500|14#500000|19#1</t>
         </is>
       </c>
       <c r="Q317" s="0" t="n">
@@ -27324,12 +27324,12 @@
       </c>
       <c r="L325" s="0" t="inlineStr">
         <is>
-          <t>16#2560|6000124#1280</t>
+          <t>16#2560|6000124#1280|19#7</t>
         </is>
       </c>
       <c r="M325" s="0" t="inlineStr">
         <is>
-          <t>16#2560</t>
+          <t>16#2560|19#7</t>
         </is>
       </c>
       <c r="Q325" s="0" t="n">
@@ -27409,12 +27409,12 @@
       </c>
       <c r="L326" s="0" t="inlineStr">
         <is>
-          <t>16#5760|6000124#2880</t>
+          <t>16#5760|6000124#2880|19#16</t>
         </is>
       </c>
       <c r="M326" s="0" t="inlineStr">
         <is>
-          <t>16#5760</t>
+          <t>16#5760|19#16</t>
         </is>
       </c>
       <c r="Q326" s="0" t="n">
@@ -27761,12 +27761,12 @@
       </c>
       <c r="L330" s="0" t="inlineStr">
         <is>
-          <t>16#680|6000124#680</t>
+          <t>16#680|6000124#680|19#5</t>
         </is>
       </c>
       <c r="M330" s="0" t="inlineStr">
         <is>
-          <t>16#680</t>
+          <t>16#680|19#5</t>
         </is>
       </c>
       <c r="Q330" s="0" t="n">
@@ -27849,12 +27849,12 @@
       </c>
       <c r="L331" s="0" t="inlineStr">
         <is>
-          <t>16#680|6000124#680</t>
+          <t>16#680|6000124#680|19#5</t>
         </is>
       </c>
       <c r="M331" s="0" t="inlineStr">
         <is>
-          <t>16#680</t>
+          <t>16#680|19#5</t>
         </is>
       </c>
       <c r="Q331" s="0" t="n">
@@ -28025,12 +28025,12 @@
       </c>
       <c r="L333" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M333" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q333" s="0" t="inlineStr">
@@ -28111,12 +28111,12 @@
       </c>
       <c r="L334" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M334" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q334" s="0" t="inlineStr">
@@ -28197,12 +28197,12 @@
       </c>
       <c r="L335" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M335" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q335" s="0" t="inlineStr">
@@ -28283,12 +28283,12 @@
       </c>
       <c r="L336" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M336" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q336" s="0" t="inlineStr">
@@ -28364,12 +28364,12 @@
       </c>
       <c r="L337" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M337" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q337" s="0" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="L338" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M338" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q338" s="0" t="inlineStr">
@@ -28526,12 +28526,12 @@
       </c>
       <c r="L339" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M339" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q339" s="0" t="inlineStr">
@@ -28607,12 +28607,12 @@
       </c>
       <c r="L340" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M340" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q340" s="0" t="inlineStr">
@@ -28688,12 +28688,12 @@
       </c>
       <c r="L341" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|6000124#1980|19#21</t>
         </is>
       </c>
       <c r="M341" s="0" t="inlineStr">
         <is>
-          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000</t>
+          <t>16#1980|80008#1|20008#1|81148#50|61#5|68#10000|19#21</t>
         </is>
       </c>
       <c r="Q341" s="0" t="inlineStr">
